--- a/Financial Analysis/NVDA.xlsx
+++ b/Financial Analysis/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8120D1FF-7920-4BAF-AF9C-603D113E866A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7270B018-5ACD-44CA-B627-05013AB8E82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{07368E55-E692-488D-959E-E8519263B1F7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{07368E55-E692-488D-959E-E8519263B1F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>Price</t>
   </si>
@@ -190,7 +190,10 @@
     <t>Q424 8K</t>
   </si>
   <si>
-    <t>Undervalued</t>
+    <t>Fairly valued</t>
+  </si>
+  <si>
+    <t>Net Margin</t>
   </si>
 </sst>
 </file>
@@ -712,17 +715,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>100.63</v>
+        <v>138.85</v>
       </c>
       <c r="E3" s="3">
-        <v>45755</v>
+        <v>45806</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45756</v>
+        <v>45806</v>
       </c>
       <c r="G3" s="3">
-        <v>45804</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -742,7 +745,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>2464328.0699999998</v>
+        <v>3400297.65</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -784,7 +787,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>2429581.0699999998</v>
+        <v>3365550.65</v>
       </c>
     </row>
   </sheetData>
@@ -993,19 +996,16 @@
         <v>39331</v>
       </c>
       <c r="O3" s="8">
-        <v>43000</v>
+        <v>44062</v>
       </c>
       <c r="P3" s="8">
-        <f>L3*1.6</f>
         <v>48064</v>
       </c>
       <c r="Q3" s="8">
-        <f>M3*1.5</f>
         <v>52623</v>
       </c>
       <c r="R3" s="8">
-        <f>N3*1.4</f>
-        <v>55063.399999999994</v>
+        <v>55063</v>
       </c>
       <c r="S3" s="8"/>
       <c r="U3" s="8">
@@ -1025,47 +1025,47 @@
       </c>
       <c r="Y3" s="8">
         <f>SUM(O3:R3)</f>
-        <v>198750.4</v>
+        <v>199812</v>
       </c>
       <c r="Z3" s="8">
         <f>Y3*1.28</f>
-        <v>254400.51199999999</v>
+        <v>255759.36000000002</v>
       </c>
       <c r="AA3" s="8">
         <f>Z3*1.12</f>
-        <v>284928.57344000001</v>
+        <v>286450.48320000002</v>
       </c>
       <c r="AB3" s="8">
         <f>AA3*1.08</f>
-        <v>307722.85931520001</v>
+        <v>309366.52185600006</v>
       </c>
       <c r="AC3" s="8">
         <f>AB3*1.05</f>
-        <v>323109.00228096003</v>
+        <v>324834.84794880007</v>
       </c>
       <c r="AD3" s="8">
         <f>AC3*1.04</f>
-        <v>336033.36237219843</v>
+        <v>337828.2418667521</v>
       </c>
       <c r="AE3" s="8">
         <f>AD3*1.03</f>
-        <v>346114.36324336438</v>
+        <v>347963.0891227547</v>
       </c>
       <c r="AF3" s="8">
         <f t="shared" ref="AF3:AI3" si="0">AE3*1.02</f>
-        <v>353036.65050823166</v>
+        <v>354922.35090520978</v>
       </c>
       <c r="AG3" s="8">
         <f t="shared" si="0"/>
-        <v>360097.38351839629</v>
+        <v>362020.79792331398</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" si="0"/>
-        <v>367299.33118876425</v>
+        <v>369261.21388178028</v>
       </c>
       <c r="AI3" s="8">
         <f t="shared" si="0"/>
-        <v>374645.31781253952</v>
+        <v>376646.43815941591</v>
       </c>
     </row>
     <row r="4" spans="1:147" x14ac:dyDescent="0.3">
@@ -1109,20 +1109,16 @@
         <v>10608</v>
       </c>
       <c r="O4" s="4">
-        <f>O3-O5</f>
-        <v>12642</v>
+        <v>17394</v>
       </c>
       <c r="P4" s="4">
-        <f>P3-P5</f>
-        <v>13457.919999999998</v>
+        <v>13458</v>
       </c>
       <c r="Q4" s="4">
-        <f t="shared" ref="Q4:R4" si="1">Q3-Q5</f>
-        <v>14208.21</v>
+        <v>14208</v>
       </c>
       <c r="R4" s="4">
-        <f t="shared" si="1"/>
-        <v>15417.752</v>
+        <v>15418</v>
       </c>
       <c r="U4" s="4">
         <v>9439</v>
@@ -1141,47 +1137,47 @@
       </c>
       <c r="Y4" s="4">
         <f>SUM(O4:R4)</f>
-        <v>55725.881999999998</v>
+        <v>60478</v>
       </c>
       <c r="Z4" s="4">
-        <f t="shared" ref="Z4:AI4" si="2">Z3-Z5</f>
-        <v>66144.133120000013</v>
+        <f t="shared" ref="Z4:AI4" si="1">Z3-Z5</f>
+        <v>71612.620800000004</v>
       </c>
       <c r="AA4" s="4">
-        <f t="shared" si="2"/>
-        <v>74081.429094399995</v>
+        <f t="shared" si="1"/>
+        <v>80206.135296000022</v>
       </c>
       <c r="AB4" s="4">
-        <f t="shared" si="2"/>
-        <v>80007.943421952019</v>
+        <f t="shared" si="1"/>
+        <v>86622.626119680033</v>
       </c>
       <c r="AC4" s="4">
-        <f t="shared" si="2"/>
-        <v>84008.340593049623</v>
+        <f t="shared" si="1"/>
+        <v>90953.757425664022</v>
       </c>
       <c r="AD4" s="4">
-        <f t="shared" si="2"/>
-        <v>87368.674216771586</v>
+        <f t="shared" si="1"/>
+        <v>94591.907722690608</v>
       </c>
       <c r="AE4" s="4">
-        <f t="shared" si="2"/>
-        <v>89989.734443274734</v>
+        <f t="shared" si="1"/>
+        <v>97429.664954371314</v>
       </c>
       <c r="AF4" s="4">
-        <f t="shared" si="2"/>
-        <v>91789.529132140247</v>
+        <f t="shared" si="1"/>
+        <v>99378.258253458742</v>
       </c>
       <c r="AG4" s="4">
-        <f t="shared" si="2"/>
-        <v>93625.319714783051</v>
+        <f t="shared" si="1"/>
+        <v>101365.82341852793</v>
       </c>
       <c r="AH4" s="4">
-        <f t="shared" si="2"/>
-        <v>95497.826109078713</v>
+        <f t="shared" si="1"/>
+        <v>103393.13988689851</v>
       </c>
       <c r="AI4" s="4">
-        <f t="shared" si="2"/>
-        <v>97407.782631260285</v>
+        <f t="shared" si="1"/>
+        <v>105461.00268463645</v>
       </c>
     </row>
     <row r="5" spans="1:147" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1190,68 +1186,64 @@
         <v>20</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:N5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:N5" si="2">C3-C4</f>
         <v>5431</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>2915</v>
       </c>
       <c r="E5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3177</v>
       </c>
       <c r="F5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3833</v>
       </c>
       <c r="G5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>4648</v>
       </c>
       <c r="H5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>9462</v>
       </c>
       <c r="I5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>13400</v>
       </c>
       <c r="J5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>16791</v>
       </c>
       <c r="K5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>20406</v>
       </c>
       <c r="L5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>22574</v>
       </c>
       <c r="M5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>26156</v>
       </c>
       <c r="N5" s="8">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>28723</v>
       </c>
       <c r="O5" s="8">
-        <f>O3*0.706</f>
-        <v>30358</v>
+        <v>26668</v>
       </c>
       <c r="P5" s="8">
-        <f>P3*0.72</f>
-        <v>34606.080000000002</v>
+        <v>34606</v>
       </c>
       <c r="Q5" s="8">
-        <f>Q3*0.73</f>
-        <v>38414.79</v>
+        <v>38415</v>
       </c>
       <c r="R5" s="8">
-        <f>R3*0.72</f>
-        <v>39645.647999999994</v>
+        <v>39646</v>
       </c>
       <c r="U5" s="8">
         <f>U3-U4</f>
@@ -1271,47 +1263,47 @@
       </c>
       <c r="Y5" s="8">
         <f>Y3-Y4</f>
-        <v>143024.51799999998</v>
+        <v>139334</v>
       </c>
       <c r="Z5" s="8">
-        <f>Z3*0.74</f>
-        <v>188256.37887999997</v>
+        <f>Z3*0.72</f>
+        <v>184146.73920000001</v>
       </c>
       <c r="AA5" s="8">
-        <f>AA3*0.74</f>
-        <v>210847.14434560001</v>
+        <f t="shared" ref="AA5:AI5" si="3">AA3*0.72</f>
+        <v>206244.34790399999</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" ref="AB5:AI5" si="4">AB3*0.74</f>
-        <v>227714.91589324799</v>
+        <f t="shared" si="3"/>
+        <v>222743.89573632003</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="4"/>
-        <v>239100.66168791041</v>
+        <f t="shared" si="3"/>
+        <v>233881.09052313605</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" si="4"/>
-        <v>248664.68815542685</v>
+        <f t="shared" si="3"/>
+        <v>243236.33414406149</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" si="4"/>
-        <v>256124.62880008965</v>
+        <f t="shared" si="3"/>
+        <v>250533.42416838338</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" si="4"/>
-        <v>261247.12137609141</v>
+        <f t="shared" si="3"/>
+        <v>255544.09265175104</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" si="4"/>
-        <v>266472.06380361324</v>
+        <f t="shared" si="3"/>
+        <v>260654.97450478605</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" si="4"/>
-        <v>271801.50507968554</v>
+        <f t="shared" si="3"/>
+        <v>265868.07399488176</v>
       </c>
       <c r="AI5" s="8">
-        <f t="shared" si="4"/>
-        <v>277237.53518127924</v>
+        <f t="shared" si="3"/>
+        <v>271185.43547477946</v>
       </c>
     </row>
     <row r="6" spans="1:147" x14ac:dyDescent="0.3">
@@ -1355,12 +1347,17 @@
         <v>3714</v>
       </c>
       <c r="O6" s="4">
-        <f>K6*1.5</f>
-        <v>4080</v>
-      </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
+        <v>3989</v>
+      </c>
+      <c r="P6" s="4">
+        <v>4481</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>4916</v>
+      </c>
+      <c r="R6" s="4">
+        <v>5200</v>
+      </c>
       <c r="U6" s="4">
         <v>5268</v>
       </c>
@@ -1377,48 +1374,48 @@
         <v>12914</v>
       </c>
       <c r="Y6" s="4">
-        <f>X6*1.4</f>
-        <v>18079.599999999999</v>
+        <f t="shared" ref="Y6:Y7" si="4">SUM(O6:R6)</f>
+        <v>18586</v>
       </c>
       <c r="Z6" s="4">
         <f>Y6*1.25</f>
-        <v>22599.5</v>
+        <v>23232.5</v>
       </c>
       <c r="AA6" s="4">
         <f>Z6*1.15</f>
-        <v>25989.424999999999</v>
+        <v>26717.374999999996</v>
       </c>
       <c r="AB6" s="4">
         <f>AA6*1.08</f>
-        <v>28068.579000000002</v>
+        <v>28854.764999999999</v>
       </c>
       <c r="AC6" s="4">
         <f>AB6*1.05</f>
-        <v>29472.007950000003</v>
+        <v>30297.503250000002</v>
       </c>
       <c r="AD6" s="4">
         <f>AC6*1.04</f>
-        <v>30650.888268000002</v>
+        <v>31509.403380000003</v>
       </c>
       <c r="AE6" s="4">
         <f t="shared" ref="AE6:AI6" si="5">AD6*1.02</f>
-        <v>31263.906033360003</v>
+        <v>32139.591447600003</v>
       </c>
       <c r="AF6" s="4">
         <f t="shared" si="5"/>
-        <v>31889.184154027203</v>
+        <v>32782.383276552006</v>
       </c>
       <c r="AG6" s="4">
         <f t="shared" si="5"/>
-        <v>32526.96783710775</v>
+        <v>33438.030942083045</v>
       </c>
       <c r="AH6" s="4">
         <f t="shared" si="5"/>
-        <v>33177.507193849902</v>
+        <v>34106.791560924707</v>
       </c>
       <c r="AI6" s="4">
         <f t="shared" si="5"/>
-        <v>33841.057337726903</v>
+        <v>34788.927392143203</v>
       </c>
     </row>
     <row r="7" spans="1:147" x14ac:dyDescent="0.3">
@@ -1462,12 +1459,17 @@
         <v>975</v>
       </c>
       <c r="O7" s="4">
-        <f>O3*0.025</f>
-        <v>1075</v>
-      </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
+        <v>1041</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1057</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>1105</v>
+      </c>
+      <c r="R7" s="4">
+        <v>1156</v>
+      </c>
       <c r="U7" s="4">
         <v>2166</v>
       </c>
@@ -1484,48 +1486,48 @@
         <v>3491</v>
       </c>
       <c r="Y7" s="4">
-        <f t="shared" ref="Y7:AI7" si="6">Y3*0.025</f>
-        <v>4968.76</v>
+        <f t="shared" si="4"/>
+        <v>4359</v>
       </c>
       <c r="Z7" s="4">
-        <f t="shared" si="6"/>
-        <v>6360.0128000000004</v>
+        <f>Z3*0.021</f>
+        <v>5370.9465600000003</v>
       </c>
       <c r="AA7" s="4">
-        <f t="shared" si="6"/>
-        <v>7123.2143360000009</v>
+        <f t="shared" ref="AA7:AI7" si="6">AA3*0.021</f>
+        <v>6015.4601472000004</v>
       </c>
       <c r="AB7" s="4">
         <f t="shared" si="6"/>
-        <v>7693.071482880001</v>
+        <v>6496.696958976002</v>
       </c>
       <c r="AC7" s="4">
         <f t="shared" si="6"/>
-        <v>8077.7250570240012</v>
+        <v>6821.5318069248024</v>
       </c>
       <c r="AD7" s="4">
         <f t="shared" si="6"/>
-        <v>8400.8340593049616</v>
+        <v>7094.3930792017945</v>
       </c>
       <c r="AE7" s="4">
         <f t="shared" si="6"/>
-        <v>8652.8590810841106</v>
+        <v>7307.2248715778487</v>
       </c>
       <c r="AF7" s="4">
         <f t="shared" si="6"/>
-        <v>8825.9162627057922</v>
+        <v>7453.369369009406</v>
       </c>
       <c r="AG7" s="4">
         <f t="shared" si="6"/>
-        <v>9002.4345879599077</v>
+        <v>7602.4367563895939</v>
       </c>
       <c r="AH7" s="4">
         <f t="shared" si="6"/>
-        <v>9182.4832797191066</v>
+        <v>7754.4854915173864</v>
       </c>
       <c r="AI7" s="4">
         <f t="shared" si="6"/>
-        <v>9366.1329453134877</v>
+        <v>7909.5752013477349</v>
       </c>
     </row>
     <row r="8" spans="1:147" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1570,7 +1572,7 @@
         <v>16909</v>
       </c>
       <c r="L8" s="8">
-        <f t="shared" ref="L8:O8" si="8">L5-L6-L7</f>
+        <f t="shared" ref="L8:N8" si="8">L5-L6-L7</f>
         <v>18642</v>
       </c>
       <c r="M8" s="8">
@@ -1582,12 +1584,17 @@
         <v>24034</v>
       </c>
       <c r="O8" s="8">
-        <f t="shared" si="8"/>
-        <v>25203</v>
-      </c>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
+        <v>21638</v>
+      </c>
+      <c r="P8" s="8">
+        <v>29068</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>32394</v>
+      </c>
+      <c r="R8" s="8">
+        <v>33290</v>
+      </c>
       <c r="U8" s="8">
         <f>U5-U6-U7</f>
         <v>10041</v>
@@ -1606,47 +1613,47 @@
       </c>
       <c r="Y8" s="8">
         <f t="shared" ref="Y8:AI8" si="9">Y5-Y6-Y7</f>
-        <v>119976.15799999998</v>
+        <v>116389</v>
       </c>
       <c r="Z8" s="8">
         <f t="shared" si="9"/>
-        <v>159296.86607999998</v>
+        <v>155543.29264</v>
       </c>
       <c r="AA8" s="8">
         <f t="shared" si="9"/>
-        <v>177734.50500960002</v>
+        <v>173511.51275679999</v>
       </c>
       <c r="AB8" s="8">
         <f t="shared" si="9"/>
-        <v>191953.26541036798</v>
+        <v>187392.43377734403</v>
       </c>
       <c r="AC8" s="8">
         <f t="shared" si="9"/>
-        <v>201550.9286808864</v>
+        <v>196762.05546621123</v>
       </c>
       <c r="AD8" s="8">
         <f t="shared" si="9"/>
-        <v>209612.96582812187</v>
+        <v>204632.53768485968</v>
       </c>
       <c r="AE8" s="8">
         <f t="shared" si="9"/>
-        <v>216207.86368564554</v>
+        <v>211086.60784920552</v>
       </c>
       <c r="AF8" s="8">
         <f t="shared" si="9"/>
-        <v>220532.02095935843</v>
+        <v>215308.34000618965</v>
       </c>
       <c r="AG8" s="8">
         <f t="shared" si="9"/>
-        <v>224942.6613785456</v>
+        <v>219614.50680631341</v>
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="9"/>
-        <v>229441.51460611654</v>
+        <v>224006.79694243969</v>
       </c>
       <c r="AI8" s="8">
         <f t="shared" si="9"/>
-        <v>234030.34489823884</v>
+        <v>228486.93288128852</v>
       </c>
     </row>
     <row r="9" spans="1:147" x14ac:dyDescent="0.3">
@@ -1690,12 +1697,17 @@
         <v>-511</v>
       </c>
       <c r="O9" s="4">
-        <f>N9*1.05</f>
-        <v>-536.55000000000007</v>
-      </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
+        <v>-515</v>
+      </c>
+      <c r="P9" s="4">
+        <v>-525</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>-536</v>
+      </c>
+      <c r="R9" s="4">
+        <v>-547</v>
+      </c>
       <c r="U9" s="4">
         <v>-29</v>
       </c>
@@ -1712,48 +1724,48 @@
         <v>-1786</v>
       </c>
       <c r="Y9" s="4">
-        <f>X9*1.02</f>
-        <v>-1821.72</v>
+        <f t="shared" ref="Y9:Y11" si="10">SUM(O9:R9)</f>
+        <v>-2123</v>
       </c>
       <c r="Z9" s="4">
-        <f t="shared" ref="Z9:AI9" si="10">Y9*1.02</f>
-        <v>-1858.1544000000001</v>
+        <f t="shared" ref="Z9:AI9" si="11">Y9*1.02</f>
+        <v>-2165.46</v>
       </c>
       <c r="AA9" s="4">
-        <f t="shared" si="10"/>
-        <v>-1895.3174880000001</v>
+        <f t="shared" si="11"/>
+        <v>-2208.7692000000002</v>
       </c>
       <c r="AB9" s="4">
-        <f t="shared" si="10"/>
-        <v>-1933.2238377600002</v>
+        <f t="shared" si="11"/>
+        <v>-2252.9445840000003</v>
       </c>
       <c r="AC9" s="4">
-        <f t="shared" si="10"/>
-        <v>-1971.8883145152001</v>
+        <f t="shared" si="11"/>
+        <v>-2298.0034756800005</v>
       </c>
       <c r="AD9" s="4">
-        <f t="shared" si="10"/>
-        <v>-2011.3260808055043</v>
+        <f t="shared" si="11"/>
+        <v>-2343.9635451936006</v>
       </c>
       <c r="AE9" s="4">
-        <f t="shared" si="10"/>
-        <v>-2051.5526024216142</v>
+        <f t="shared" si="11"/>
+        <v>-2390.8428160974727</v>
       </c>
       <c r="AF9" s="4">
-        <f t="shared" si="10"/>
-        <v>-2092.5836544700464</v>
+        <f t="shared" si="11"/>
+        <v>-2438.6596724194223</v>
       </c>
       <c r="AG9" s="4">
-        <f t="shared" si="10"/>
-        <v>-2134.4353275594476</v>
+        <f t="shared" si="11"/>
+        <v>-2487.432865867811</v>
       </c>
       <c r="AH9" s="4">
-        <f t="shared" si="10"/>
-        <v>-2177.1240341106368</v>
+        <f t="shared" si="11"/>
+        <v>-2537.1815231851674</v>
       </c>
       <c r="AI9" s="4">
-        <f t="shared" si="10"/>
-        <v>-2220.6665147928497</v>
+        <f t="shared" si="11"/>
+        <v>-2587.9251536488709</v>
       </c>
     </row>
     <row r="10" spans="1:147" x14ac:dyDescent="0.3">
@@ -1797,11 +1809,17 @@
         <v>61</v>
       </c>
       <c r="O10" s="4">
-        <v>61</v>
-      </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="P10" s="4">
+        <v>63</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>63</v>
+      </c>
+      <c r="R10" s="4">
+        <v>63</v>
+      </c>
       <c r="U10" s="4">
         <v>236</v>
       </c>
@@ -1818,48 +1836,48 @@
         <v>247</v>
       </c>
       <c r="Y10" s="4">
-        <f>X10*1.01</f>
-        <v>249.47</v>
+        <f t="shared" si="10"/>
+        <v>252</v>
       </c>
       <c r="Z10" s="4">
-        <f t="shared" ref="Z10:AI10" si="11">Y10*1.01</f>
-        <v>251.96469999999999</v>
+        <f t="shared" ref="Z10:AI10" si="12">Y10*1.01</f>
+        <v>254.52</v>
       </c>
       <c r="AA10" s="4">
-        <f t="shared" si="11"/>
-        <v>254.48434699999999</v>
+        <f t="shared" si="12"/>
+        <v>257.0652</v>
       </c>
       <c r="AB10" s="4">
-        <f t="shared" si="11"/>
-        <v>257.02919047</v>
+        <f t="shared" si="12"/>
+        <v>259.635852</v>
       </c>
       <c r="AC10" s="4">
-        <f t="shared" si="11"/>
-        <v>259.59948237470002</v>
+        <f t="shared" si="12"/>
+        <v>262.23221052000002</v>
       </c>
       <c r="AD10" s="4">
-        <f t="shared" si="11"/>
-        <v>262.19547719844701</v>
+        <f t="shared" si="12"/>
+        <v>264.85453262520002</v>
       </c>
       <c r="AE10" s="4">
-        <f t="shared" si="11"/>
-        <v>264.81743197043147</v>
+        <f t="shared" si="12"/>
+        <v>267.50307795145204</v>
       </c>
       <c r="AF10" s="4">
-        <f t="shared" si="11"/>
-        <v>267.46560629013578</v>
+        <f t="shared" si="12"/>
+        <v>270.17810873096658</v>
       </c>
       <c r="AG10" s="4">
-        <f t="shared" si="11"/>
-        <v>270.14026235303714</v>
+        <f t="shared" si="12"/>
+        <v>272.87988981827624</v>
       </c>
       <c r="AH10" s="4">
-        <f t="shared" si="11"/>
-        <v>272.84166497656753</v>
+        <f t="shared" si="12"/>
+        <v>275.60868871645903</v>
       </c>
       <c r="AI10" s="4">
-        <f t="shared" si="11"/>
-        <v>275.57008162633321</v>
+        <f t="shared" si="12"/>
+        <v>278.36477560362363</v>
       </c>
     </row>
     <row r="11" spans="1:147" x14ac:dyDescent="0.3">
@@ -1904,11 +1922,17 @@
         <v>-733</v>
       </c>
       <c r="O11" s="4">
+        <v>180</v>
+      </c>
+      <c r="P11" s="4">
         <v>0</v>
       </c>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
+      <c r="Q11" s="4">
+        <v>0</v>
+      </c>
+      <c r="R11" s="4">
+        <v>0</v>
+      </c>
       <c r="U11" s="4">
         <v>-107</v>
       </c>
@@ -1925,7 +1949,8 @@
         <v>-1033</v>
       </c>
       <c r="Y11" s="4">
-        <v>0</v>
+        <f t="shared" si="10"/>
+        <v>180</v>
       </c>
       <c r="Z11" s="4">
         <v>0</v>
@@ -1964,60 +1989,65 @@
         <v>27</v>
       </c>
       <c r="C12" s="8">
-        <f t="shared" ref="C12:K12" si="12">C8-C9-C10-C11</f>
+        <f t="shared" ref="C12:K12" si="13">C8-C9-C10-C11</f>
         <v>1805</v>
       </c>
       <c r="D12" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>475</v>
       </c>
       <c r="E12" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>613</v>
       </c>
       <c r="F12" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1289</v>
       </c>
       <c r="G12" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2209</v>
       </c>
       <c r="H12" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>6981</v>
       </c>
       <c r="I12" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10522</v>
       </c>
       <c r="J12" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>14106</v>
       </c>
       <c r="K12" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>17279</v>
       </c>
       <c r="L12" s="8">
-        <f t="shared" ref="L12:O12" si="13">L8-L9-L10-L11</f>
+        <f t="shared" ref="L12:N12" si="14">L8-L9-L10-L11</f>
         <v>19214</v>
       </c>
       <c r="M12" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>22316</v>
       </c>
       <c r="N12" s="8">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>25217</v>
       </c>
       <c r="O12" s="8">
-        <f t="shared" si="13"/>
-        <v>25678.55</v>
-      </c>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
+        <v>21910</v>
+      </c>
+      <c r="P12" s="8">
+        <v>29530</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>32867</v>
+      </c>
+      <c r="R12" s="8">
+        <v>33773</v>
+      </c>
       <c r="U12" s="8">
         <f>U8-U9-U10-U11</f>
         <v>9941</v>
@@ -2035,48 +2065,48 @@
         <v>84026</v>
       </c>
       <c r="Y12" s="8">
-        <f t="shared" ref="Y12:AI12" si="14">Y8-Y9-Y10-Y11</f>
-        <v>121548.40799999998</v>
+        <f t="shared" ref="Y12:AI12" si="15">Y8-Y9-Y10-Y11</f>
+        <v>118080</v>
       </c>
       <c r="Z12" s="8">
-        <f t="shared" si="14"/>
-        <v>160903.05577999997</v>
+        <f t="shared" si="15"/>
+        <v>157454.23264</v>
       </c>
       <c r="AA12" s="8">
-        <f t="shared" si="14"/>
-        <v>179375.33815060003</v>
+        <f t="shared" si="15"/>
+        <v>175463.21675679999</v>
       </c>
       <c r="AB12" s="8">
-        <f t="shared" si="14"/>
-        <v>193629.46005765797</v>
+        <f t="shared" si="15"/>
+        <v>189385.74250934404</v>
       </c>
       <c r="AC12" s="8">
-        <f t="shared" si="14"/>
-        <v>203263.2175130269</v>
+        <f t="shared" si="15"/>
+        <v>198797.82673137123</v>
       </c>
       <c r="AD12" s="8">
-        <f t="shared" si="14"/>
-        <v>211362.09643172892</v>
+        <f t="shared" si="15"/>
+        <v>206711.64669742808</v>
       </c>
       <c r="AE12" s="8">
-        <f t="shared" si="14"/>
-        <v>217994.59885609671</v>
+        <f t="shared" si="15"/>
+        <v>213209.94758735152</v>
       </c>
       <c r="AF12" s="8">
-        <f t="shared" si="14"/>
-        <v>222357.13900753832</v>
+        <f t="shared" si="15"/>
+        <v>217476.82156987811</v>
       </c>
       <c r="AG12" s="8">
-        <f t="shared" si="14"/>
-        <v>226806.95644375202</v>
+        <f t="shared" si="15"/>
+        <v>221829.05978236292</v>
       </c>
       <c r="AH12" s="8">
-        <f t="shared" si="14"/>
-        <v>231345.79697525062</v>
+        <f t="shared" si="15"/>
+        <v>226268.3697769084</v>
       </c>
       <c r="AI12" s="8">
-        <f t="shared" si="14"/>
-        <v>235975.44133140537</v>
+        <f t="shared" si="15"/>
+        <v>230796.49325933374</v>
       </c>
     </row>
     <row r="13" spans="1:147" x14ac:dyDescent="0.3">
@@ -2120,12 +2150,17 @@
         <v>3126</v>
       </c>
       <c r="O13" s="4">
-        <f>O12*0.17</f>
-        <v>4365.3535000000002</v>
-      </c>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
+        <v>3135</v>
+      </c>
+      <c r="P13" s="4">
+        <v>4134</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>4601</v>
+      </c>
+      <c r="R13" s="4">
+        <v>4728</v>
+      </c>
       <c r="U13" s="4">
         <v>189</v>
       </c>
@@ -2142,48 +2177,48 @@
         <v>11146</v>
       </c>
       <c r="Y13" s="4">
-        <f>Y12*0.14</f>
-        <v>17016.777119999999</v>
+        <f>SUM(O13:R13)</f>
+        <v>16598</v>
       </c>
       <c r="Z13" s="4">
-        <f t="shared" ref="Z13:AI13" si="15">Z12*0.14</f>
-        <v>22526.427809199999</v>
+        <f t="shared" ref="Z13:AI13" si="16">Z12*0.14</f>
+        <v>22043.592569600001</v>
       </c>
       <c r="AA13" s="4">
-        <f t="shared" si="15"/>
-        <v>25112.547341084006</v>
+        <f t="shared" si="16"/>
+        <v>24564.850345952</v>
       </c>
       <c r="AB13" s="4">
-        <f t="shared" si="15"/>
-        <v>27108.124408072119</v>
+        <f t="shared" si="16"/>
+        <v>26514.003951308168</v>
       </c>
       <c r="AC13" s="4">
-        <f t="shared" si="15"/>
-        <v>28456.850451823768</v>
+        <f t="shared" si="16"/>
+        <v>27831.695742391974</v>
       </c>
       <c r="AD13" s="4">
-        <f t="shared" si="15"/>
-        <v>29590.693500442052</v>
+        <f t="shared" si="16"/>
+        <v>28939.630537639932</v>
       </c>
       <c r="AE13" s="4">
-        <f t="shared" si="15"/>
-        <v>30519.243839853541</v>
+        <f t="shared" si="16"/>
+        <v>29849.392662229217</v>
       </c>
       <c r="AF13" s="4">
-        <f t="shared" si="15"/>
-        <v>31129.999461055369</v>
+        <f t="shared" si="16"/>
+        <v>30446.755019782941</v>
       </c>
       <c r="AG13" s="4">
-        <f t="shared" si="15"/>
-        <v>31752.973902125286</v>
+        <f t="shared" si="16"/>
+        <v>31056.068369530811</v>
       </c>
       <c r="AH13" s="4">
-        <f t="shared" si="15"/>
-        <v>32388.411576535091</v>
+        <f t="shared" si="16"/>
+        <v>31677.571768767179</v>
       </c>
       <c r="AI13" s="4">
-        <f t="shared" si="15"/>
-        <v>33036.561786396756</v>
+        <f t="shared" si="16"/>
+        <v>32311.509056306728</v>
       </c>
     </row>
     <row r="14" spans="1:147" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2192,60 +2227,65 @@
         <v>29</v>
       </c>
       <c r="C14" s="8">
-        <f t="shared" ref="C14:K14" si="16">C12-C13</f>
+        <f t="shared" ref="C14:K14" si="17">C12-C13</f>
         <v>1618</v>
       </c>
       <c r="D14" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>656</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>680</v>
       </c>
       <c r="F14" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1414</v>
       </c>
       <c r="G14" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2043</v>
       </c>
       <c r="H14" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>6188</v>
       </c>
       <c r="I14" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9243</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>12285</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>14881</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" ref="L14:O14" si="17">L12-L13</f>
+        <f t="shared" ref="L14:N14" si="18">L12-L13</f>
         <v>16599</v>
       </c>
       <c r="M14" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>19309</v>
       </c>
       <c r="N14" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>22091</v>
       </c>
       <c r="O14" s="8">
-        <f t="shared" si="17"/>
-        <v>21313.196499999998</v>
-      </c>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
+        <v>18775</v>
+      </c>
+      <c r="P14" s="8">
+        <v>25396</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>28266</v>
+      </c>
+      <c r="R14" s="8">
+        <v>29045</v>
+      </c>
       <c r="U14" s="8">
         <f>U12-U13</f>
         <v>9752</v>
@@ -2263,496 +2303,496 @@
         <v>72880</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" ref="Y14:AI14" si="18">Y12-Y13</f>
-        <v>104531.63087999998</v>
+        <f t="shared" ref="Y14:AI14" si="19">Y12-Y13</f>
+        <v>101482</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" si="18"/>
-        <v>138376.62797079998</v>
+        <f t="shared" si="19"/>
+        <v>135410.6400704</v>
       </c>
       <c r="AA14" s="8">
-        <f t="shared" si="18"/>
-        <v>154262.79080951604</v>
+        <f t="shared" si="19"/>
+        <v>150898.36641084799</v>
       </c>
       <c r="AB14" s="8">
-        <f t="shared" si="18"/>
-        <v>166521.33564958585</v>
+        <f t="shared" si="19"/>
+        <v>162871.73855803587</v>
       </c>
       <c r="AC14" s="8">
-        <f t="shared" si="18"/>
-        <v>174806.36706120314</v>
+        <f t="shared" si="19"/>
+        <v>170966.13098897925</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" si="18"/>
-        <v>181771.40293128687</v>
+        <f t="shared" si="19"/>
+        <v>177772.01615978815</v>
       </c>
       <c r="AE14" s="8">
-        <f t="shared" si="18"/>
-        <v>187475.35501624318</v>
+        <f t="shared" si="19"/>
+        <v>183360.5549251223</v>
       </c>
       <c r="AF14" s="8">
-        <f t="shared" si="18"/>
-        <v>191227.13954648294</v>
+        <f t="shared" si="19"/>
+        <v>187030.06655009516</v>
       </c>
       <c r="AG14" s="8">
-        <f t="shared" si="18"/>
-        <v>195053.98254162673</v>
+        <f t="shared" si="19"/>
+        <v>190772.99141283211</v>
       </c>
       <c r="AH14" s="8">
-        <f t="shared" si="18"/>
-        <v>198957.38539871553</v>
+        <f t="shared" si="19"/>
+        <v>194590.79800814122</v>
       </c>
       <c r="AI14" s="8">
-        <f t="shared" si="18"/>
-        <v>202938.87954500862</v>
+        <f t="shared" si="19"/>
+        <v>198484.98420302701</v>
       </c>
       <c r="AJ14" s="7">
         <f>AI14*($AL$19+1)</f>
-        <v>200909.49074955852</v>
+        <v>196500.13436099674</v>
       </c>
       <c r="AK14" s="7">
-        <f t="shared" ref="AK14:CV14" si="19">AJ14*($AL$19+1)</f>
-        <v>198900.39584206292</v>
+        <f t="shared" ref="AK14:CV14" si="20">AJ14*($AL$19+1)</f>
+        <v>194535.13301738678</v>
       </c>
       <c r="AL14" s="7">
-        <f t="shared" si="19"/>
-        <v>196911.3918836423</v>
+        <f t="shared" si="20"/>
+        <v>192589.7816872129</v>
       </c>
       <c r="AM14" s="7">
-        <f t="shared" si="19"/>
-        <v>194942.27796480586</v>
+        <f t="shared" si="20"/>
+        <v>190663.88387034077</v>
       </c>
       <c r="AN14" s="7">
-        <f t="shared" si="19"/>
-        <v>192992.85518515779</v>
+        <f t="shared" si="20"/>
+        <v>188757.24503163737</v>
       </c>
       <c r="AO14" s="7">
-        <f t="shared" si="19"/>
-        <v>191062.92663330623</v>
+        <f t="shared" si="20"/>
+        <v>186869.67258132101</v>
       </c>
       <c r="AP14" s="7">
-        <f t="shared" si="19"/>
-        <v>189152.29736697316</v>
+        <f t="shared" si="20"/>
+        <v>185000.9758555078</v>
       </c>
       <c r="AQ14" s="7">
-        <f t="shared" si="19"/>
-        <v>187260.77439330344</v>
+        <f t="shared" si="20"/>
+        <v>183150.96609695273</v>
       </c>
       <c r="AR14" s="7">
-        <f t="shared" si="19"/>
-        <v>185388.1666493704</v>
+        <f t="shared" si="20"/>
+        <v>181319.45643598321</v>
       </c>
       <c r="AS14" s="7">
-        <f t="shared" si="19"/>
-        <v>183534.28498287668</v>
+        <f t="shared" si="20"/>
+        <v>179506.26187162337</v>
       </c>
       <c r="AT14" s="7">
-        <f t="shared" si="19"/>
-        <v>181698.94213304791</v>
+        <f t="shared" si="20"/>
+        <v>177711.19925290713</v>
       </c>
       <c r="AU14" s="7">
-        <f t="shared" si="19"/>
-        <v>179881.95271171743</v>
+        <f t="shared" si="20"/>
+        <v>175934.08726037806</v>
       </c>
       <c r="AV14" s="7">
-        <f t="shared" si="19"/>
-        <v>178083.13318460024</v>
+        <f t="shared" si="20"/>
+        <v>174174.74638777427</v>
       </c>
       <c r="AW14" s="7">
-        <f t="shared" si="19"/>
-        <v>176302.30185275423</v>
+        <f t="shared" si="20"/>
+        <v>172432.99892389652</v>
       </c>
       <c r="AX14" s="7">
-        <f t="shared" si="19"/>
-        <v>174539.27883422669</v>
+        <f t="shared" si="20"/>
+        <v>170708.66893465756</v>
       </c>
       <c r="AY14" s="7">
-        <f t="shared" si="19"/>
-        <v>172793.88604588443</v>
+        <f t="shared" si="20"/>
+        <v>169001.58224531097</v>
       </c>
       <c r="AZ14" s="7">
-        <f t="shared" si="19"/>
-        <v>171065.94718542558</v>
+        <f t="shared" si="20"/>
+        <v>167311.56642285787</v>
       </c>
       <c r="BA14" s="7">
-        <f t="shared" si="19"/>
-        <v>169355.28771357134</v>
+        <f t="shared" si="20"/>
+        <v>165638.45075862927</v>
       </c>
       <c r="BB14" s="7">
-        <f t="shared" si="19"/>
-        <v>167661.73483643561</v>
+        <f t="shared" si="20"/>
+        <v>163982.06625104297</v>
       </c>
       <c r="BC14" s="7">
-        <f t="shared" si="19"/>
-        <v>165985.11748807126</v>
+        <f t="shared" si="20"/>
+        <v>162342.24558853253</v>
       </c>
       <c r="BD14" s="7">
-        <f t="shared" si="19"/>
-        <v>164325.26631319054</v>
+        <f t="shared" si="20"/>
+        <v>160718.8231326472</v>
       </c>
       <c r="BE14" s="7">
-        <f t="shared" si="19"/>
-        <v>162682.01365005862</v>
+        <f t="shared" si="20"/>
+        <v>159111.63490132074</v>
       </c>
       <c r="BF14" s="7">
-        <f t="shared" si="19"/>
-        <v>161055.19351355804</v>
+        <f t="shared" si="20"/>
+        <v>157520.51855230753</v>
       </c>
       <c r="BG14" s="7">
-        <f t="shared" si="19"/>
-        <v>159444.64157842245</v>
+        <f t="shared" si="20"/>
+        <v>155945.31336678445</v>
       </c>
       <c r="BH14" s="7">
-        <f t="shared" si="19"/>
-        <v>157850.19516263824</v>
+        <f t="shared" si="20"/>
+        <v>154385.8602331166</v>
       </c>
       <c r="BI14" s="7">
-        <f t="shared" si="19"/>
-        <v>156271.69321101185</v>
+        <f t="shared" si="20"/>
+        <v>152842.00163078544</v>
       </c>
       <c r="BJ14" s="7">
-        <f t="shared" si="19"/>
-        <v>154708.97627890174</v>
+        <f t="shared" si="20"/>
+        <v>151313.58161447759</v>
       </c>
       <c r="BK14" s="7">
-        <f t="shared" si="19"/>
-        <v>153161.88651611272</v>
+        <f t="shared" si="20"/>
+        <v>149800.4457983328</v>
       </c>
       <c r="BL14" s="7">
-        <f t="shared" si="19"/>
-        <v>151630.2676509516</v>
+        <f t="shared" si="20"/>
+        <v>148302.44134034947</v>
       </c>
       <c r="BM14" s="7">
-        <f t="shared" si="19"/>
-        <v>150113.96497444209</v>
+        <f t="shared" si="20"/>
+        <v>146819.41692694597</v>
       </c>
       <c r="BN14" s="7">
-        <f t="shared" si="19"/>
-        <v>148612.82532469765</v>
+        <f t="shared" si="20"/>
+        <v>145351.2227576765</v>
       </c>
       <c r="BO14" s="7">
-        <f t="shared" si="19"/>
-        <v>147126.69707145068</v>
+        <f t="shared" si="20"/>
+        <v>143897.71053009972</v>
       </c>
       <c r="BP14" s="7">
-        <f t="shared" si="19"/>
-        <v>145655.43010073618</v>
+        <f t="shared" si="20"/>
+        <v>142458.73342479873</v>
       </c>
       <c r="BQ14" s="7">
-        <f t="shared" si="19"/>
-        <v>144198.87579972882</v>
+        <f t="shared" si="20"/>
+        <v>141034.14609055076</v>
       </c>
       <c r="BR14" s="7">
-        <f t="shared" si="19"/>
-        <v>142756.88704173153</v>
+        <f t="shared" si="20"/>
+        <v>139623.80462964525</v>
       </c>
       <c r="BS14" s="7">
-        <f t="shared" si="19"/>
-        <v>141329.31817131423</v>
+        <f t="shared" si="20"/>
+        <v>138227.56658334879</v>
       </c>
       <c r="BT14" s="7">
-        <f t="shared" si="19"/>
-        <v>139916.02498960108</v>
+        <f t="shared" si="20"/>
+        <v>136845.29091751529</v>
       </c>
       <c r="BU14" s="7">
-        <f t="shared" si="19"/>
-        <v>138516.86473970508</v>
+        <f t="shared" si="20"/>
+        <v>135476.83800834013</v>
       </c>
       <c r="BV14" s="7">
-        <f t="shared" si="19"/>
-        <v>137131.69609230803</v>
+        <f t="shared" si="20"/>
+        <v>134122.06962825672</v>
       </c>
       <c r="BW14" s="7">
-        <f t="shared" si="19"/>
-        <v>135760.37913138495</v>
+        <f t="shared" si="20"/>
+        <v>132780.84893197415</v>
       </c>
       <c r="BX14" s="7">
-        <f t="shared" si="19"/>
-        <v>134402.77534007109</v>
+        <f t="shared" si="20"/>
+        <v>131453.0404426544</v>
       </c>
       <c r="BY14" s="7">
-        <f t="shared" si="19"/>
-        <v>133058.74758667039</v>
+        <f t="shared" si="20"/>
+        <v>130138.51003822785</v>
       </c>
       <c r="BZ14" s="7">
-        <f t="shared" si="19"/>
-        <v>131728.16011080367</v>
+        <f t="shared" si="20"/>
+        <v>128837.12493784557</v>
       </c>
       <c r="CA14" s="7">
-        <f t="shared" si="19"/>
-        <v>130410.87850969563</v>
+        <f t="shared" si="20"/>
+        <v>127548.75368846711</v>
       </c>
       <c r="CB14" s="7">
-        <f t="shared" si="19"/>
-        <v>129106.76972459866</v>
+        <f t="shared" si="20"/>
+        <v>126273.26615158244</v>
       </c>
       <c r="CC14" s="7">
-        <f t="shared" si="19"/>
-        <v>127815.70202735267</v>
+        <f t="shared" si="20"/>
+        <v>125010.53349006662</v>
       </c>
       <c r="CD14" s="7">
-        <f t="shared" si="19"/>
-        <v>126537.54500707914</v>
+        <f t="shared" si="20"/>
+        <v>123760.42815516595</v>
       </c>
       <c r="CE14" s="7">
-        <f t="shared" si="19"/>
-        <v>125272.16955700835</v>
+        <f t="shared" si="20"/>
+        <v>122522.8238736143</v>
       </c>
       <c r="CF14" s="7">
-        <f t="shared" si="19"/>
-        <v>124019.44786143827</v>
+        <f t="shared" si="20"/>
+        <v>121297.59563487815</v>
       </c>
       <c r="CG14" s="7">
-        <f t="shared" si="19"/>
-        <v>122779.25338282388</v>
+        <f t="shared" si="20"/>
+        <v>120084.61967852936</v>
       </c>
       <c r="CH14" s="7">
-        <f t="shared" si="19"/>
-        <v>121551.46084899564</v>
+        <f t="shared" si="20"/>
+        <v>118883.77348174407</v>
       </c>
       <c r="CI14" s="7">
-        <f t="shared" si="19"/>
-        <v>120335.94624050568</v>
+        <f t="shared" si="20"/>
+        <v>117694.93574692663</v>
       </c>
       <c r="CJ14" s="7">
-        <f t="shared" si="19"/>
-        <v>119132.58677810062</v>
+        <f t="shared" si="20"/>
+        <v>116517.98638945736</v>
       </c>
       <c r="CK14" s="7">
-        <f t="shared" si="19"/>
-        <v>117941.26091031962</v>
+        <f t="shared" si="20"/>
+        <v>115352.80652556279</v>
       </c>
       <c r="CL14" s="7">
-        <f t="shared" si="19"/>
-        <v>116761.84830121642</v>
+        <f t="shared" si="20"/>
+        <v>114199.27846030716</v>
       </c>
       <c r="CM14" s="7">
-        <f t="shared" si="19"/>
-        <v>115594.22981820426</v>
+        <f t="shared" si="20"/>
+        <v>113057.28567570409</v>
       </c>
       <c r="CN14" s="7">
-        <f t="shared" si="19"/>
-        <v>114438.28752002222</v>
+        <f t="shared" si="20"/>
+        <v>111926.71281894704</v>
       </c>
       <c r="CO14" s="7">
-        <f t="shared" si="19"/>
-        <v>113293.90464482199</v>
+        <f t="shared" si="20"/>
+        <v>110807.44569075757</v>
       </c>
       <c r="CP14" s="7">
-        <f t="shared" si="19"/>
-        <v>112160.96559837376</v>
+        <f t="shared" si="20"/>
+        <v>109699.37123384999</v>
       </c>
       <c r="CQ14" s="7">
-        <f t="shared" si="19"/>
-        <v>111039.35594239003</v>
+        <f t="shared" si="20"/>
+        <v>108602.37752151149</v>
       </c>
       <c r="CR14" s="7">
-        <f t="shared" si="19"/>
-        <v>109928.96238296613</v>
+        <f t="shared" si="20"/>
+        <v>107516.35374629637</v>
       </c>
       <c r="CS14" s="7">
-        <f t="shared" si="19"/>
-        <v>108829.67275913646</v>
+        <f t="shared" si="20"/>
+        <v>106441.1902088334</v>
       </c>
       <c r="CT14" s="7">
-        <f t="shared" si="19"/>
-        <v>107741.37603154509</v>
+        <f t="shared" si="20"/>
+        <v>105376.77830674507</v>
       </c>
       <c r="CU14" s="7">
-        <f t="shared" si="19"/>
-        <v>106663.96227122964</v>
+        <f t="shared" si="20"/>
+        <v>104323.01052367761</v>
       </c>
       <c r="CV14" s="7">
-        <f t="shared" si="19"/>
-        <v>105597.32264851734</v>
+        <f t="shared" si="20"/>
+        <v>103279.78041844083</v>
       </c>
       <c r="CW14" s="7">
-        <f t="shared" ref="CW14:EQ14" si="20">CV14*($AL$19+1)</f>
-        <v>104541.34942203216</v>
+        <f t="shared" ref="CW14:EQ14" si="21">CV14*($AL$19+1)</f>
+        <v>102246.98261425643</v>
       </c>
       <c r="CX14" s="7">
-        <f t="shared" si="20"/>
-        <v>103495.93592781184</v>
+        <f t="shared" si="21"/>
+        <v>101224.51278811386</v>
       </c>
       <c r="CY14" s="7">
-        <f t="shared" si="20"/>
-        <v>102460.97656853372</v>
+        <f t="shared" si="21"/>
+        <v>100212.26766023273</v>
       </c>
       <c r="CZ14" s="7">
-        <f t="shared" si="20"/>
-        <v>101436.36680284838</v>
+        <f t="shared" si="21"/>
+        <v>99210.144983630395</v>
       </c>
       <c r="DA14" s="7">
-        <f t="shared" si="20"/>
-        <v>100422.0031348199</v>
+        <f t="shared" si="21"/>
+        <v>98218.043533794087</v>
       </c>
       <c r="DB14" s="7">
-        <f t="shared" si="20"/>
-        <v>99417.783103471695</v>
+        <f t="shared" si="21"/>
+        <v>97235.863098456146</v>
       </c>
       <c r="DC14" s="7">
-        <f t="shared" si="20"/>
-        <v>98423.60527243698</v>
+        <f t="shared" si="21"/>
+        <v>96263.50446747159</v>
       </c>
       <c r="DD14" s="7">
-        <f t="shared" si="20"/>
-        <v>97439.369219712607</v>
+        <f t="shared" si="21"/>
+        <v>95300.869422796866</v>
       </c>
       <c r="DE14" s="7">
-        <f t="shared" si="20"/>
-        <v>96464.975527515475</v>
+        <f t="shared" si="21"/>
+        <v>94347.860728568892</v>
       </c>
       <c r="DF14" s="7">
-        <f t="shared" si="20"/>
-        <v>95500.325772240321</v>
+        <f t="shared" si="21"/>
+        <v>93404.382121283197</v>
       </c>
       <c r="DG14" s="7">
-        <f t="shared" si="20"/>
-        <v>94545.322514517917</v>
+        <f t="shared" si="21"/>
+        <v>92470.338300070362</v>
       </c>
       <c r="DH14" s="7">
-        <f t="shared" si="20"/>
-        <v>93599.869289372742</v>
+        <f t="shared" si="21"/>
+        <v>91545.634917069663</v>
       </c>
       <c r="DI14" s="7">
-        <f t="shared" si="20"/>
-        <v>92663.870596479013</v>
+        <f t="shared" si="21"/>
+        <v>90630.178567898969</v>
       </c>
       <c r="DJ14" s="7">
-        <f t="shared" si="20"/>
-        <v>91737.231890514217</v>
+        <f t="shared" si="21"/>
+        <v>89723.876782219973</v>
       </c>
       <c r="DK14" s="7">
-        <f t="shared" si="20"/>
-        <v>90819.859571609079</v>
+        <f t="shared" si="21"/>
+        <v>88826.638014397773</v>
       </c>
       <c r="DL14" s="7">
-        <f t="shared" si="20"/>
-        <v>89911.660975892984</v>
+        <f t="shared" si="21"/>
+        <v>87938.371634253795</v>
       </c>
       <c r="DM14" s="7">
-        <f t="shared" si="20"/>
-        <v>89012.544366134054</v>
+        <f t="shared" si="21"/>
+        <v>87058.987917911261</v>
       </c>
       <c r="DN14" s="7">
-        <f t="shared" si="20"/>
-        <v>88122.418922472716</v>
+        <f t="shared" si="21"/>
+        <v>86188.39803873215</v>
       </c>
       <c r="DO14" s="7">
-        <f t="shared" si="20"/>
-        <v>87241.19473324799</v>
+        <f t="shared" si="21"/>
+        <v>85326.514058344823</v>
       </c>
       <c r="DP14" s="7">
-        <f t="shared" si="20"/>
-        <v>86368.782785915508</v>
+        <f t="shared" si="21"/>
+        <v>84473.248917761375</v>
       </c>
       <c r="DQ14" s="7">
-        <f t="shared" si="20"/>
-        <v>85505.094958056347</v>
+        <f t="shared" si="21"/>
+        <v>83628.516428583767</v>
       </c>
       <c r="DR14" s="7">
-        <f t="shared" si="20"/>
-        <v>84650.044008475787</v>
+        <f t="shared" si="21"/>
+        <v>82792.231264297923</v>
       </c>
       <c r="DS14" s="7">
-        <f t="shared" si="20"/>
-        <v>83803.543568391033</v>
+        <f t="shared" si="21"/>
+        <v>81964.308951654937</v>
       </c>
       <c r="DT14" s="7">
-        <f t="shared" si="20"/>
-        <v>82965.508132707124</v>
+        <f t="shared" si="21"/>
+        <v>81144.665862138383</v>
       </c>
       <c r="DU14" s="7">
-        <f t="shared" si="20"/>
-        <v>82135.853051380051</v>
+        <f t="shared" si="21"/>
+        <v>80333.219203517001</v>
       </c>
       <c r="DV14" s="7">
-        <f t="shared" si="20"/>
-        <v>81314.494520866254</v>
+        <f t="shared" si="21"/>
+        <v>79529.887011481827</v>
       </c>
       <c r="DW14" s="7">
-        <f t="shared" si="20"/>
-        <v>80501.349575657587</v>
+        <f t="shared" si="21"/>
+        <v>78734.588141367014</v>
       </c>
       <c r="DX14" s="7">
-        <f t="shared" si="20"/>
-        <v>79696.336079901012</v>
+        <f t="shared" si="21"/>
+        <v>77947.242259953346</v>
       </c>
       <c r="DY14" s="7">
-        <f t="shared" si="20"/>
-        <v>78899.372719102001</v>
+        <f t="shared" si="21"/>
+        <v>77167.769837353815</v>
       </c>
       <c r="DZ14" s="7">
-        <f t="shared" si="20"/>
-        <v>78110.378991910984</v>
+        <f t="shared" si="21"/>
+        <v>76396.092138980282</v>
       </c>
       <c r="EA14" s="7">
-        <f t="shared" si="20"/>
-        <v>77329.27520199187</v>
+        <f t="shared" si="21"/>
+        <v>75632.131217590475</v>
       </c>
       <c r="EB14" s="7">
-        <f t="shared" si="20"/>
-        <v>76555.982449971954</v>
+        <f t="shared" si="21"/>
+        <v>74875.809905414571</v>
       </c>
       <c r="EC14" s="7">
-        <f t="shared" si="20"/>
-        <v>75790.422625472231</v>
+        <f t="shared" si="21"/>
+        <v>74127.051806360425</v>
       </c>
       <c r="ED14" s="7">
-        <f t="shared" si="20"/>
-        <v>75032.518399217501</v>
+        <f t="shared" si="21"/>
+        <v>73385.781288296814</v>
       </c>
       <c r="EE14" s="7">
-        <f t="shared" si="20"/>
-        <v>74282.193215225328</v>
+        <f t="shared" si="21"/>
+        <v>72651.923475413845</v>
       </c>
       <c r="EF14" s="7">
-        <f t="shared" si="20"/>
-        <v>73539.37128307308</v>
+        <f t="shared" si="21"/>
+        <v>71925.4042406597</v>
       </c>
       <c r="EG14" s="7">
-        <f t="shared" si="20"/>
-        <v>72803.97757024235</v>
+        <f t="shared" si="21"/>
+        <v>71206.150198253104</v>
       </c>
       <c r="EH14" s="7">
-        <f t="shared" si="20"/>
-        <v>72075.937794539932</v>
+        <f t="shared" si="21"/>
+        <v>70494.08869627057</v>
       </c>
       <c r="EI14" s="7">
-        <f t="shared" si="20"/>
-        <v>71355.178416594528</v>
+        <f t="shared" si="21"/>
+        <v>69789.147809307862</v>
       </c>
       <c r="EJ14" s="7">
-        <f t="shared" si="20"/>
-        <v>70641.626632428583</v>
+        <f t="shared" si="21"/>
+        <v>69091.256331214783</v>
       </c>
       <c r="EK14" s="7">
-        <f t="shared" si="20"/>
-        <v>69935.210366104293</v>
+        <f t="shared" si="21"/>
+        <v>68400.343767902639</v>
       </c>
       <c r="EL14" s="7">
-        <f t="shared" si="20"/>
-        <v>69235.858262443246</v>
+        <f t="shared" si="21"/>
+        <v>67716.340330223611</v>
       </c>
       <c r="EM14" s="7">
-        <f t="shared" si="20"/>
-        <v>68543.499679818808</v>
+        <f t="shared" si="21"/>
+        <v>67039.176926921369</v>
       </c>
       <c r="EN14" s="7">
-        <f t="shared" si="20"/>
-        <v>67858.064683020624</v>
+        <f t="shared" si="21"/>
+        <v>66368.78515765215</v>
       </c>
       <c r="EO14" s="7">
-        <f t="shared" si="20"/>
-        <v>67179.484036190421</v>
+        <f t="shared" si="21"/>
+        <v>65705.097306075622</v>
       </c>
       <c r="EP14" s="7">
-        <f t="shared" si="20"/>
-        <v>66507.689195828512</v>
+        <f t="shared" si="21"/>
+        <v>65048.046333014863</v>
       </c>
       <c r="EQ14" s="7">
-        <f t="shared" si="20"/>
-        <v>65842.612303870221</v>
+        <f t="shared" si="21"/>
+        <v>64397.565869684717</v>
       </c>
     </row>
     <row r="15" spans="1:147" x14ac:dyDescent="0.3">
@@ -2796,11 +2836,17 @@
         <v>24490</v>
       </c>
       <c r="O15" s="4">
-        <v>24489</v>
-      </c>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
+        <v>24441</v>
+      </c>
+      <c r="P15" s="4">
+        <v>24441</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>24441</v>
+      </c>
+      <c r="R15" s="4">
+        <v>24441</v>
+      </c>
       <c r="U15" s="4">
         <v>2462</v>
       </c>
@@ -2814,37 +2860,48 @@
         <v>24489</v>
       </c>
       <c r="Y15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
       <c r="Z15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
       <c r="AA15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
       <c r="AB15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
       <c r="AC15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
       <c r="AD15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
       <c r="AE15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
       <c r="AF15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
       <c r="AG15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
       <c r="AH15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
       <c r="AI15" s="4">
-        <v>24489</v>
+        <f>24441</f>
+        <v>24441</v>
       </c>
     </row>
     <row r="16" spans="1:147" x14ac:dyDescent="0.3">
@@ -2852,60 +2909,65 @@
         <v>30</v>
       </c>
       <c r="C16" s="6">
-        <f t="shared" ref="C16:K16" si="21">C14/C15</f>
+        <f t="shared" ref="C16:K16" si="22">C14/C15</f>
         <v>0.65506072874493926</v>
       </c>
       <c r="D16" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.26558704453441295</v>
       </c>
       <c r="E16" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.27530364372469635</v>
       </c>
       <c r="F16" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.57246963562753039</v>
       </c>
       <c r="G16" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.82712550607287449</v>
       </c>
       <c r="H16" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2.5052631578947366</v>
       </c>
       <c r="I16" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3.7421052631578946</v>
       </c>
       <c r="J16" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4.9736842105263159</v>
       </c>
       <c r="K16" s="6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.0442729488220959</v>
       </c>
       <c r="L16" s="6">
-        <f t="shared" ref="L16:O16" si="22">L14/L15</f>
+        <f t="shared" ref="L16:N16" si="23">L14/L15</f>
         <v>0.67668161434977581</v>
       </c>
       <c r="M16" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.78844426296447534</v>
       </c>
       <c r="N16" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.90204164965291955</v>
       </c>
       <c r="O16" s="6">
-        <f t="shared" si="22"/>
-        <v>0.87031714239046098</v>
-      </c>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
+        <v>0.77</v>
+      </c>
+      <c r="P16" s="6">
+        <v>1.04</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="R16" s="6">
+        <v>1.19</v>
+      </c>
       <c r="U16" s="6">
         <f>U14/U15</f>
         <v>3.9610073111291633</v>
@@ -2923,48 +2985,48 @@
         <v>2.9760300543100984</v>
       </c>
       <c r="Y16" s="6">
-        <f t="shared" ref="Y16:AI16" si="23">Y14/Y15</f>
-        <v>4.2685136542937636</v>
+        <f t="shared" ref="Y16:AI16" si="24">Y14/Y15</f>
+        <v>4.1521214352931546</v>
       </c>
       <c r="Z16" s="6">
-        <f t="shared" si="23"/>
-        <v>5.6505626187594418</v>
+        <f t="shared" si="24"/>
+        <v>5.5403068643017876</v>
       </c>
       <c r="AA16" s="6">
-        <f t="shared" si="23"/>
-        <v>6.2992686842874779</v>
+        <f t="shared" si="24"/>
+        <v>6.1739849601427101</v>
       </c>
       <c r="AB16" s="6">
-        <f t="shared" si="23"/>
-        <v>6.7998422005629404</v>
+        <f t="shared" si="24"/>
+        <v>6.6638737595857727</v>
       </c>
       <c r="AC16" s="6">
-        <f t="shared" si="23"/>
-        <v>7.1381586451550962</v>
+        <f t="shared" si="24"/>
+        <v>6.9950546617969493</v>
       </c>
       <c r="AD16" s="6">
-        <f t="shared" si="23"/>
-        <v>7.42257352000028</v>
+        <f t="shared" si="24"/>
+        <v>7.2735164747673231</v>
       </c>
       <c r="AE16" s="6">
-        <f t="shared" si="23"/>
-        <v>7.6554924666684299</v>
+        <f t="shared" si="24"/>
+        <v>7.502170734631247</v>
       </c>
       <c r="AF16" s="6">
-        <f t="shared" si="23"/>
-        <v>7.8086953140790945</v>
+        <f t="shared" si="24"/>
+        <v>7.6523082750335565</v>
       </c>
       <c r="AG16" s="6">
-        <f t="shared" si="23"/>
-        <v>7.9649631484187484</v>
+        <f t="shared" si="24"/>
+        <v>7.8054495075010069</v>
       </c>
       <c r="AH16" s="6">
-        <f t="shared" si="23"/>
-        <v>8.1243572787257765</v>
+        <f t="shared" si="24"/>
+        <v>7.9616545152874769</v>
       </c>
       <c r="AI16" s="6">
-        <f t="shared" si="23"/>
-        <v>8.2869402403123296</v>
+        <f t="shared" si="24"/>
+        <v>8.1209845834060399</v>
       </c>
     </row>
     <row r="18" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2977,48 +3039,48 @@
         <v>-0.13223938223938225</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" ref="H18:N18" si="24">H3/D3-1</f>
+        <f t="shared" ref="H18:N18" si="25">H3/D3-1</f>
         <v>1.0147673031026252</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.0551340414769852</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.6527846636919516</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2.6212458286985538</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1.2240319834160065</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.93609271523178816</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.77944170474596208</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" ref="O18" si="25">O3/K3-1</f>
-        <v>0.65105206573491015</v>
+        <f t="shared" ref="O18" si="26">O3/K3-1</f>
+        <v>0.69182921210259551</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" ref="P18" si="26">P3/L3-1</f>
+        <f t="shared" ref="P18" si="27">P3/L3-1</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" ref="Q18" si="27">Q3/M3-1</f>
+        <f t="shared" ref="Q18" si="28">Q3/M3-1</f>
         <v>0.5</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" ref="R18" si="28">R3/N3-1</f>
-        <v>0.39999999999999991</v>
+        <f t="shared" ref="R18" si="29">R3/N3-1</f>
+        <v>0.39998982990516385</v>
       </c>
       <c r="U18" s="9"/>
       <c r="V18" s="9">
@@ -3026,55 +3088,55 @@
         <v>2.2293230289069932E-3</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" ref="W18:AI18" si="29">W3/V3-1</f>
+        <f t="shared" ref="W18:AI18" si="30">W3/V3-1</f>
         <v>1.2585452658115224</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1.1420340763599355</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" si="29"/>
-        <v>0.52302658298658211</v>
+        <f t="shared" si="30"/>
+        <v>0.5311616358996758</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -3083,19 +3145,19 @@
         <v>32</v>
       </c>
       <c r="C19" s="10">
-        <f t="shared" ref="C19:F19" si="30">C5/C3</f>
+        <f t="shared" ref="C19:F19" si="31">C5/C3</f>
         <v>0.65528474903474898</v>
       </c>
       <c r="D19" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.43481503579952269</v>
       </c>
       <c r="E19" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.53566009104704093</v>
       </c>
       <c r="F19" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.63344901669145592</v>
       </c>
       <c r="G19" s="10">
@@ -3103,108 +3165,108 @@
         <v>0.64627363737486099</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" ref="H19:N19" si="31">H5/H3</f>
+        <f t="shared" ref="H19:N19" si="32">H5/H3</f>
         <v>0.7005256533649219</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.73951434878587197</v>
       </c>
       <c r="J19" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.75967063294575399</v>
       </c>
       <c r="K19" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.78352019659038552</v>
       </c>
       <c r="L19" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.75146471371504664</v>
       </c>
       <c r="M19" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.74556752750698363</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.73028908494571709</v>
       </c>
       <c r="O19" s="10">
-        <f t="shared" ref="O19:R19" si="32">O5/O3</f>
-        <v>0.70599999999999996</v>
+        <f t="shared" ref="O19:R19" si="33">O5/O3</f>
+        <v>0.60523807362353044</v>
       </c>
       <c r="P19" s="10">
-        <f t="shared" si="32"/>
-        <v>0.72000000000000008</v>
+        <f t="shared" si="33"/>
+        <v>0.71999833555259651</v>
       </c>
       <c r="Q19" s="10">
-        <f t="shared" si="32"/>
-        <v>0.73</v>
+        <f t="shared" si="33"/>
+        <v>0.73000399065047605</v>
       </c>
       <c r="R19" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
+        <v>0.72001162304996091</v>
+      </c>
+      <c r="U19" s="10">
+        <f t="shared" ref="U19:V19" si="34">U5/U3</f>
+        <v>0.64929033216913135</v>
+      </c>
+      <c r="V19" s="10">
+        <f t="shared" si="34"/>
+        <v>0.56928894490991322</v>
+      </c>
+      <c r="W19" s="10">
+        <f t="shared" ref="W19:AI19" si="35">W5/W3</f>
+        <v>0.72717573290436954</v>
+      </c>
+      <c r="X19" s="10">
+        <f t="shared" si="35"/>
+        <v>0.74989463359310937</v>
+      </c>
+      <c r="Y19" s="10">
+        <f t="shared" si="35"/>
+        <v>0.69732548595679944</v>
+      </c>
+      <c r="Z19" s="10">
+        <f t="shared" si="35"/>
         <v>0.72</v>
       </c>
-      <c r="U19" s="10">
-        <f t="shared" ref="U19:V19" si="33">U5/U3</f>
-        <v>0.64929033216913135</v>
-      </c>
-      <c r="V19" s="10">
-        <f t="shared" si="33"/>
-        <v>0.56928894490991322</v>
-      </c>
-      <c r="W19" s="10">
-        <f t="shared" ref="W19:AI19" si="34">W5/W3</f>
-        <v>0.72717573290436954</v>
-      </c>
-      <c r="X19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74989463359310937</v>
-      </c>
-      <c r="Y19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.71961876806285663</v>
-      </c>
-      <c r="Z19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74</v>
-      </c>
       <c r="AA19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74</v>
+        <f t="shared" si="35"/>
+        <v>0.72</v>
       </c>
       <c r="AB19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74</v>
+        <f t="shared" si="35"/>
+        <v>0.72</v>
       </c>
       <c r="AC19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74</v>
+        <f t="shared" si="35"/>
+        <v>0.72</v>
       </c>
       <c r="AD19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74</v>
+        <f t="shared" si="35"/>
+        <v>0.72</v>
       </c>
       <c r="AE19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74</v>
+        <f t="shared" si="35"/>
+        <v>0.72</v>
       </c>
       <c r="AF19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74</v>
+        <f t="shared" si="35"/>
+        <v>0.72</v>
       </c>
       <c r="AG19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74</v>
+        <f t="shared" si="35"/>
+        <v>0.72</v>
       </c>
       <c r="AH19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74</v>
+        <f t="shared" si="35"/>
+        <v>0.71999999999999986</v>
       </c>
       <c r="AI19" s="10">
-        <f t="shared" si="34"/>
-        <v>0.74</v>
+        <f t="shared" si="35"/>
+        <v>0.72</v>
       </c>
       <c r="AK19" t="s">
         <v>36</v>
@@ -3226,48 +3288,48 @@
         <v>0.15883807169344877</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" ref="H20:N20" si="35">H6/D6-1</f>
+        <f t="shared" ref="H20:N20" si="36">H6/D6-1</f>
         <v>0.11842105263157898</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.17943444730077118</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.26345463864684771</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.45066666666666677</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.51470588235294112</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.47776809067131643</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.50669371196754565</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" ref="O20" si="36">O6/K6-1</f>
-        <v>0.5</v>
+        <f t="shared" ref="O20" si="37">O6/K6-1</f>
+        <v>0.46654411764705883</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" ref="P20" si="37">P6/L6-1</f>
-        <v>-1</v>
+        <f t="shared" ref="P20" si="38">P6/L6-1</f>
+        <v>0.45016181229773466</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" ref="Q20" si="38">Q6/M6-1</f>
-        <v>-1</v>
+        <f t="shared" ref="Q20" si="39">Q6/M6-1</f>
+        <v>0.45014749262536879</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" ref="R20" si="39">R6/N6-1</f>
-        <v>-1</v>
+        <f t="shared" ref="R20" si="40">R6/N6-1</f>
+        <v>0.40010770059235323</v>
       </c>
       <c r="U20" s="10"/>
       <c r="V20" s="10">
@@ -3275,55 +3337,55 @@
         <v>0.3929384965831435</v>
       </c>
       <c r="W20" s="10">
-        <f t="shared" ref="W20:AI20" si="40">W6/V6-1</f>
+        <f t="shared" ref="W20:AI20" si="41">W6/V6-1</f>
         <v>0.18206595802671033</v>
       </c>
       <c r="X20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.4888171547152409</v>
       </c>
       <c r="Y20" s="10">
-        <f t="shared" si="40"/>
-        <v>0.39999999999999991</v>
+        <f t="shared" si="41"/>
+        <v>0.43921325693046298</v>
       </c>
       <c r="Z20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.25</v>
       </c>
       <c r="AA20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AB20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AC20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AD20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AE20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI20" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK20" t="s">
@@ -3338,19 +3400,19 @@
         <v>34</v>
       </c>
       <c r="C21" s="10">
-        <f t="shared" ref="C21:F21" si="41">C7/C3</f>
+        <f t="shared" ref="C21:F21" si="42">C7/C3</f>
         <v>7.1428571428571425E-2</v>
       </c>
       <c r="D21" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>8.83054892601432E-2</v>
       </c>
       <c r="E21" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.1063901534311246</v>
       </c>
       <c r="F21" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.10328871260948604</v>
       </c>
       <c r="G21" s="10">
@@ -3358,115 +3420,115 @@
         <v>8.8014460511679646E-2</v>
       </c>
       <c r="H21" s="10">
-        <f t="shared" ref="H21:N21" si="42">H7/H3</f>
+        <f t="shared" ref="H21:N21" si="43">H7/H3</f>
         <v>4.6050196194565782E-2</v>
       </c>
       <c r="I21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3.8024282560706404E-2</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>3.2167579061665834E-2</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.9834126862233145E-2</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.8029294274300932E-2</v>
       </c>
       <c r="M21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.5568667692833932E-2</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>2.478960616307747E-2</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" ref="O21:R21" si="43">O7/O3</f>
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" ref="O21:R21" si="44">O7/O3</f>
+        <v>2.3625800009078116E-2</v>
       </c>
       <c r="P21" s="10">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="44"/>
+        <v>2.1991511318242344E-2</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="44"/>
+        <v>2.0998422742907093E-2</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="43"/>
-        <v>0</v>
+        <f t="shared" si="44"/>
+        <v>2.0994133991972832E-2</v>
       </c>
       <c r="U21" s="10">
-        <f t="shared" ref="U21:V21" si="44">U7/U3</f>
+        <f t="shared" ref="U21:V21" si="45">U7/U3</f>
         <v>8.0478561343538674E-2</v>
       </c>
       <c r="V21" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>9.0457477570994288E-2</v>
       </c>
       <c r="W21" s="10">
-        <f t="shared" ref="W21:AI21" si="45">W7/W3</f>
+        <f t="shared" ref="W21:AI21" si="46">W7/W3</f>
         <v>4.3580315813663374E-2</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.6751572833091947E-2</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1815506576181611E-2</v>
       </c>
       <c r="Z21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="AD21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="AE21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.5000000000000005E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="AF21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="AG21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="AH21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.5000000000000001E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="AI21" s="10">
-        <f t="shared" si="45"/>
-        <v>2.4999999999999998E-2</v>
+        <f t="shared" si="46"/>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="AK21" t="s">
         <v>38</v>
       </c>
       <c r="AL21" s="4">
         <f>NPV(AL20,Y14:EQ14)</f>
-        <v>3352226.5886356286</v>
+        <v>3278011.7097029299</v>
       </c>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.3">
@@ -3474,19 +3536,19 @@
         <v>35</v>
       </c>
       <c r="C22" s="10">
-        <f t="shared" ref="C22:F22" si="46">C8/C3</f>
+        <f t="shared" ref="C22:F22" si="47">C8/C3</f>
         <v>0.38863416988416988</v>
       </c>
       <c r="D22" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>7.4433174224343673E-2</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.10133198448828191</v>
       </c>
       <c r="F22" s="10">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.2077342588001983</v>
       </c>
       <c r="G22" s="10">
@@ -3494,108 +3556,108 @@
         <v>0.29755283648498332</v>
       </c>
       <c r="H22" s="10">
-        <f t="shared" ref="H22:N22" si="47">H8/H3</f>
+        <f t="shared" ref="H22:N22" si="48">H8/H3</f>
         <v>0.50344265936181243</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.5748896247240618</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.61597973125820027</v>
       </c>
       <c r="K22" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.64924742743050223</v>
       </c>
       <c r="L22" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.62057256990679099</v>
       </c>
       <c r="M22" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.62336810900176731</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.61107014822913219</v>
       </c>
       <c r="O22" s="10">
-        <f t="shared" ref="O22:R22" si="48">O8/O3</f>
-        <v>0.58611627906976749</v>
+        <f t="shared" ref="O22:R22" si="49">O8/O3</f>
+        <v>0.49108074985248057</v>
       </c>
       <c r="P22" s="10">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="49"/>
+        <v>0.60477696404793613</v>
       </c>
       <c r="Q22" s="10">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="49"/>
+        <v>0.61558634057351347</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" si="48"/>
-        <v>0</v>
+        <f t="shared" si="49"/>
+        <v>0.60458020812523838</v>
       </c>
       <c r="U22" s="10">
-        <f t="shared" ref="U22:V22" si="49">U8/U3</f>
+        <f t="shared" ref="U22:V22" si="50">U8/U3</f>
         <v>0.37307720888756779</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.20679172536516646</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" ref="W22:AI22" si="50">W8/W3</f>
+        <f t="shared" ref="W22:AI22" si="51">W8/W3</f>
         <v>0.54121663766783756</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.62418293140838488</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.60365241025930005</v>
+        <f t="shared" si="51"/>
+        <v>0.58249254299041098</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.62616566620746417</v>
+        <f t="shared" si="51"/>
+        <v>0.60816265977518869</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.62378617512373569</v>
+        <f t="shared" si="51"/>
+        <v>0.60572951673345254</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.62378617512373546</v>
+        <f t="shared" si="51"/>
+        <v>0.60572951673345266</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.62378617512373558</v>
+        <f t="shared" si="51"/>
+        <v>0.60572951673345266</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.62378617512373558</v>
+        <f t="shared" si="51"/>
+        <v>0.60572951673345254</v>
       </c>
       <c r="AE22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.62467174623903921</v>
+        <f t="shared" si="51"/>
+        <v>0.60663505540594342</v>
       </c>
       <c r="AF22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.62467174623903909</v>
+        <f t="shared" si="51"/>
+        <v>0.60663505540594354</v>
       </c>
       <c r="AG22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.62467174623903909</v>
+        <f t="shared" si="51"/>
+        <v>0.60663505540594342</v>
       </c>
       <c r="AH22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.62467174623903921</v>
+        <f t="shared" si="51"/>
+        <v>0.60663505540594342</v>
       </c>
       <c r="AI22" s="10">
-        <f t="shared" si="50"/>
-        <v>0.62467174623903909</v>
+        <f t="shared" si="51"/>
+        <v>0.60663505540594342</v>
       </c>
       <c r="AK22" t="s">
         <v>39</v>
@@ -3610,19 +3672,19 @@
         <v>28</v>
       </c>
       <c r="C23" s="10">
-        <f t="shared" ref="C23:F23" si="51">C13/C12</f>
+        <f t="shared" ref="C23:F23" si="52">C13/C12</f>
         <v>0.10360110803324099</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-0.38105263157894737</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-0.10929853181076672</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>-9.6974398758727695E-2</v>
       </c>
       <c r="G23" s="10">
@@ -3630,107 +3692,107 @@
         <v>7.5147125396106837E-2</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" ref="H23:N23" si="52">H13/H12</f>
+        <f t="shared" ref="H23:N23" si="53">H13/H12</f>
         <v>0.11359404096834265</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.12155483748336818</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.12909400255210549</v>
       </c>
       <c r="K23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.13878117946640431</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.1360986780472572</v>
       </c>
       <c r="M23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.13474637031726117</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.1239639925447119</v>
       </c>
       <c r="O23" s="10">
-        <f t="shared" ref="O23:R23" si="53">O13/O12</f>
-        <v>0.17</v>
-      </c>
-      <c r="P23" s="10" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q23" s="10" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R23" s="10" t="e">
-        <f t="shared" si="53"/>
-        <v>#DIV/0!</v>
+        <f t="shared" ref="O23:R23" si="54">O13/O12</f>
+        <v>0.1430853491556367</v>
+      </c>
+      <c r="P23" s="10">
+        <f t="shared" si="54"/>
+        <v>0.13999322722654928</v>
+      </c>
+      <c r="Q23" s="10">
+        <f t="shared" si="54"/>
+        <v>0.13998843825113336</v>
+      </c>
+      <c r="R23" s="10">
+        <f t="shared" si="54"/>
+        <v>0.1399934859207059</v>
       </c>
       <c r="U23" s="10">
-        <f t="shared" ref="U23:V23" si="54">U13/U12</f>
+        <f t="shared" ref="U23:V23" si="55">U13/U12</f>
         <v>1.9012171813700834E-2</v>
       </c>
       <c r="V23" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>-4.4476327116212341E-2</v>
       </c>
       <c r="W23" s="10">
-        <f t="shared" ref="W23:AI23" si="55">W13/W12</f>
+        <f t="shared" ref="W23:AI23" si="56">W13/W12</f>
         <v>0.12002483884321959</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13264941803727417</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
+        <v>0.14056571815718158</v>
+      </c>
+      <c r="Z23" s="10">
+        <f t="shared" si="56"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="Z23" s="10">
-        <f t="shared" si="55"/>
+      <c r="AA23" s="10">
+        <f t="shared" si="56"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AA23" s="10">
-        <f t="shared" si="55"/>
+      <c r="AB23" s="10">
+        <f t="shared" si="56"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AB23" s="10">
-        <f t="shared" si="55"/>
+      <c r="AC23" s="10">
+        <f t="shared" si="56"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AC23" s="10">
-        <f t="shared" si="55"/>
+      <c r="AD23" s="10">
+        <f t="shared" si="56"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AD23" s="10">
-        <f t="shared" si="55"/>
+      <c r="AE23" s="10">
+        <f t="shared" si="56"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AE23" s="10">
-        <f t="shared" si="55"/>
+      <c r="AF23" s="10">
+        <f t="shared" si="56"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AF23" s="10">
-        <f t="shared" si="55"/>
+      <c r="AG23" s="10">
+        <f t="shared" si="56"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AG23" s="10">
-        <f t="shared" si="55"/>
+      <c r="AH23" s="10">
+        <f t="shared" si="56"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AH23" s="10">
-        <f t="shared" si="55"/>
-        <v>0.14000000000000001</v>
-      </c>
       <c r="AI23" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="AK23" t="s">
@@ -3738,16 +3800,143 @@
       </c>
       <c r="AL23" s="4">
         <f>AL21+AL22</f>
-        <v>3386973.5886356286</v>
+        <v>3312758.7097029299</v>
       </c>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="10">
+        <f>C14/C3</f>
+        <v>0.19522200772200773</v>
+      </c>
+      <c r="D24" s="10">
+        <f t="shared" ref="D24:R24" si="57">D14/D3</f>
+        <v>9.7852028639618144E-2</v>
+      </c>
+      <c r="E24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.11465182937110099</v>
+      </c>
+      <c r="F24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.2336803834077012</v>
+      </c>
+      <c r="G24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.28406562847608452</v>
+      </c>
+      <c r="H24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.45813282001924927</v>
+      </c>
+      <c r="I24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.51009933774834437</v>
+      </c>
+      <c r="J24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.55580690404017552</v>
+      </c>
+      <c r="K24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.57137920442328372</v>
+      </c>
+      <c r="L24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.55256324900133158</v>
+      </c>
+      <c r="M24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.55039621458297705</v>
+      </c>
+      <c r="N24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.56166891256260965</v>
+      </c>
+      <c r="O24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.42610412600426673</v>
+      </c>
+      <c r="P24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.52837882822902793</v>
+      </c>
+      <c r="Q24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.53714155407331399</v>
+      </c>
+      <c r="R24" s="10">
+        <f t="shared" si="57"/>
+        <v>0.52748669705609941</v>
+      </c>
+      <c r="U24" s="10">
+        <f t="shared" ref="U24:AI24" si="58">U14/U3</f>
+        <v>0.36233930296499961</v>
+      </c>
+      <c r="V24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.16193371394676356</v>
+      </c>
+      <c r="W24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.48847706903909915</v>
+      </c>
+      <c r="X24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.55848027157712443</v>
+      </c>
+      <c r="Y24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.50788741416931915</v>
+      </c>
+      <c r="Z24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.52944549153704479</v>
+      </c>
+      <c r="AA24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.52678691522922161</v>
+      </c>
+      <c r="AB24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.52646853182726505</v>
+      </c>
+      <c r="AC24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.52631708718618342</v>
+      </c>
+      <c r="AD24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.5262201146282669</v>
+      </c>
+      <c r="AE24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.52695403810614005</v>
+      </c>
+      <c r="AF24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.52696051988015224</v>
+      </c>
+      <c r="AG24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.52696693810736006</v>
+      </c>
+      <c r="AH24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.52697329341077193</v>
+      </c>
+      <c r="AI24" s="10">
+        <f t="shared" si="58"/>
+        <v>0.52697958640728759</v>
+      </c>
       <c r="AK24" t="s">
         <v>41</v>
       </c>
       <c r="AL24" s="11">
         <f>AL23/AI15</f>
-        <v>138.30591647824036</v>
+        <v>135.54104618071804</v>
       </c>
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.3">
@@ -3756,7 +3945,7 @@
       </c>
       <c r="AL25" s="11">
         <f>Main!D3</f>
-        <v>100.63</v>
+        <v>138.85</v>
       </c>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.3">
@@ -3765,7 +3954,7 @@
       </c>
       <c r="AL26" s="9">
         <f>AL24/AL25-1</f>
-        <v>0.37440044199781752</v>
+        <v>-2.3831140218091185E-2</v>
       </c>
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.3">

--- a/Financial Analysis/NVDA.xlsx
+++ b/Financial Analysis/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7270B018-5ACD-44CA-B627-05013AB8E82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AF800A-EB86-4389-9D3B-3107987B5CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{07368E55-E692-488D-959E-E8519263B1F7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{07368E55-E692-488D-959E-E8519263B1F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>Price</t>
   </si>
@@ -187,13 +187,10 @@
     <t>Q426</t>
   </si>
   <si>
-    <t>Q424 8K</t>
-  </si>
-  <si>
-    <t>Fairly valued</t>
-  </si>
-  <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -294,13 +291,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
@@ -318,7 +315,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10363200" y="0"/>
+          <a:off x="11811000" y="0"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -715,17 +712,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>138.85</v>
+        <v>173.91</v>
       </c>
       <c r="E3" s="3">
-        <v>45806</v>
+        <v>45925</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45806</v>
+        <v>45925</v>
       </c>
       <c r="G3" s="3">
-        <v>45889</v>
+        <v>45973</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -733,10 +730,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <v>24489</v>
+        <v>24366</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -745,7 +742,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>3400297.65</v>
+        <v>4237491.0599999996</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -753,11 +750,11 @@
         <v>6</v>
       </c>
       <c r="D6" s="4">
-        <f>43210</f>
-        <v>43210</v>
+        <f>11639+45152</f>
+        <v>56791</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
@@ -765,11 +762,11 @@
         <v>7</v>
       </c>
       <c r="D7" s="4">
-        <f>8463</f>
-        <v>8463</v>
+        <f>8466</f>
+        <v>8466</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
@@ -778,7 +775,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>34747</v>
+        <v>48325</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.3">
@@ -787,7 +784,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>3365550.65</v>
+        <v>4189166.0599999996</v>
       </c>
     </row>
   </sheetData>
@@ -999,13 +996,15 @@
         <v>44062</v>
       </c>
       <c r="P3" s="8">
-        <v>48064</v>
+        <v>46743</v>
       </c>
       <c r="Q3" s="8">
-        <v>52623</v>
+        <f>M3*1.52</f>
+        <v>53324.639999999999</v>
       </c>
       <c r="R3" s="8">
-        <v>55063</v>
+        <f>N3*1.45</f>
+        <v>57029.95</v>
       </c>
       <c r="S3" s="8"/>
       <c r="U3" s="8">
@@ -1025,47 +1024,47 @@
       </c>
       <c r="Y3" s="8">
         <f>SUM(O3:R3)</f>
-        <v>199812</v>
+        <v>201159.59000000003</v>
       </c>
       <c r="Z3" s="8">
-        <f>Y3*1.28</f>
-        <v>255759.36000000002</v>
+        <f>Y3*1.3</f>
+        <v>261507.46700000003</v>
       </c>
       <c r="AA3" s="8">
-        <f>Z3*1.12</f>
-        <v>286450.48320000002</v>
+        <f>Z3*1.15</f>
+        <v>300733.58705000003</v>
       </c>
       <c r="AB3" s="8">
-        <f>AA3*1.08</f>
-        <v>309366.52185600006</v>
+        <f>AA3*1.09</f>
+        <v>327799.60988450004</v>
       </c>
       <c r="AC3" s="8">
-        <f>AB3*1.05</f>
-        <v>324834.84794880007</v>
+        <f>AB3*1.06</f>
+        <v>347467.58647757006</v>
       </c>
       <c r="AD3" s="8">
-        <f>AC3*1.04</f>
-        <v>337828.2418667521</v>
+        <f>AC3*1.05</f>
+        <v>364840.96580144856</v>
       </c>
       <c r="AE3" s="8">
-        <f>AD3*1.03</f>
-        <v>347963.0891227547</v>
+        <f>AD3*1.04</f>
+        <v>379434.60443350649</v>
       </c>
       <c r="AF3" s="8">
-        <f t="shared" ref="AF3:AI3" si="0">AE3*1.02</f>
-        <v>354922.35090520978</v>
+        <f>AE3*1.03</f>
+        <v>390817.6425665117</v>
       </c>
       <c r="AG3" s="8">
-        <f t="shared" si="0"/>
-        <v>362020.79792331398</v>
+        <f t="shared" ref="AG3:AI3" si="0">AF3*1.02</f>
+        <v>398633.99541784194</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" si="0"/>
-        <v>369261.21388178028</v>
+        <v>406606.67532619881</v>
       </c>
       <c r="AI3" s="8">
         <f t="shared" si="0"/>
-        <v>376646.43815941591</v>
+        <v>414738.80883272277</v>
       </c>
     </row>
     <row r="4" spans="1:147" x14ac:dyDescent="0.3">
@@ -1112,7 +1111,7 @@
         <v>17394</v>
       </c>
       <c r="P4" s="4">
-        <v>13458</v>
+        <v>12890</v>
       </c>
       <c r="Q4" s="4">
         <v>14208</v>
@@ -1137,47 +1136,47 @@
       </c>
       <c r="Y4" s="4">
         <f>SUM(O4:R4)</f>
-        <v>60478</v>
+        <v>59910</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" ref="Z4:AI4" si="1">Z3-Z5</f>
-        <v>71612.620800000004</v>
+        <v>73222.090760000021</v>
       </c>
       <c r="AA4" s="4">
         <f t="shared" si="1"/>
-        <v>80206.135296000022</v>
+        <v>84205.404374000005</v>
       </c>
       <c r="AB4" s="4">
         <f t="shared" si="1"/>
-        <v>86622.626119680033</v>
+        <v>91783.890767660021</v>
       </c>
       <c r="AC4" s="4">
         <f t="shared" si="1"/>
-        <v>90953.757425664022</v>
+        <v>97290.924213719612</v>
       </c>
       <c r="AD4" s="4">
         <f t="shared" si="1"/>
-        <v>94591.907722690608</v>
+        <v>102155.47042440559</v>
       </c>
       <c r="AE4" s="4">
         <f t="shared" si="1"/>
-        <v>97429.664954371314</v>
+        <v>106241.68924138183</v>
       </c>
       <c r="AF4" s="4">
         <f t="shared" si="1"/>
-        <v>99378.258253458742</v>
+        <v>109428.93991862331</v>
       </c>
       <c r="AG4" s="4">
         <f t="shared" si="1"/>
-        <v>101365.82341852793</v>
+        <v>111617.51871699578</v>
       </c>
       <c r="AH4" s="4">
         <f t="shared" si="1"/>
-        <v>103393.13988689851</v>
+        <v>113849.86909133568</v>
       </c>
       <c r="AI4" s="4">
         <f t="shared" si="1"/>
-        <v>105461.00268463645</v>
+        <v>116126.86647316237</v>
       </c>
     </row>
     <row r="5" spans="1:147" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1186,7 +1185,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:N5" si="2">C3-C4</f>
+        <f t="shared" ref="C5:R5" si="2">C3-C4</f>
         <v>5431</v>
       </c>
       <c r="D5" s="8">
@@ -1234,16 +1233,20 @@
         <v>28723</v>
       </c>
       <c r="O5" s="8">
+        <f t="shared" si="2"/>
         <v>26668</v>
       </c>
       <c r="P5" s="8">
-        <v>34606</v>
+        <f t="shared" si="2"/>
+        <v>33853</v>
       </c>
       <c r="Q5" s="8">
-        <v>38415</v>
+        <f t="shared" si="2"/>
+        <v>39116.639999999999</v>
       </c>
       <c r="R5" s="8">
-        <v>39646</v>
+        <f t="shared" si="2"/>
+        <v>41611.949999999997</v>
       </c>
       <c r="U5" s="8">
         <f>U3-U4</f>
@@ -1263,47 +1266,47 @@
       </c>
       <c r="Y5" s="8">
         <f>Y3-Y4</f>
-        <v>139334</v>
+        <v>141249.59000000003</v>
       </c>
       <c r="Z5" s="8">
         <f>Z3*0.72</f>
-        <v>184146.73920000001</v>
+        <v>188285.37624000001</v>
       </c>
       <c r="AA5" s="8">
         <f t="shared" ref="AA5:AI5" si="3">AA3*0.72</f>
-        <v>206244.34790399999</v>
+        <v>216528.18267600003</v>
       </c>
       <c r="AB5" s="8">
         <f t="shared" si="3"/>
-        <v>222743.89573632003</v>
+        <v>236015.71911684002</v>
       </c>
       <c r="AC5" s="8">
         <f t="shared" si="3"/>
-        <v>233881.09052313605</v>
+        <v>250176.66226385045</v>
       </c>
       <c r="AD5" s="8">
         <f t="shared" si="3"/>
-        <v>243236.33414406149</v>
+        <v>262685.49537704297</v>
       </c>
       <c r="AE5" s="8">
         <f t="shared" si="3"/>
-        <v>250533.42416838338</v>
+        <v>273192.91519212467</v>
       </c>
       <c r="AF5" s="8">
         <f t="shared" si="3"/>
-        <v>255544.09265175104</v>
+        <v>281388.70264788839</v>
       </c>
       <c r="AG5" s="8">
         <f t="shared" si="3"/>
-        <v>260654.97450478605</v>
+        <v>287016.47670084616</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="3"/>
-        <v>265868.07399488176</v>
+        <v>292756.80623486312</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="3"/>
-        <v>271185.43547477946</v>
+        <v>298611.9423595604</v>
       </c>
     </row>
     <row r="6" spans="1:147" x14ac:dyDescent="0.3">
@@ -1350,10 +1353,11 @@
         <v>3989</v>
       </c>
       <c r="P6" s="4">
-        <v>4481</v>
+        <v>4291</v>
       </c>
       <c r="Q6" s="4">
-        <v>4916</v>
+        <f>M6*1.4</f>
+        <v>4746</v>
       </c>
       <c r="R6" s="4">
         <v>5200</v>
@@ -1375,47 +1379,47 @@
       </c>
       <c r="Y6" s="4">
         <f t="shared" ref="Y6:Y7" si="4">SUM(O6:R6)</f>
-        <v>18586</v>
+        <v>18226</v>
       </c>
       <c r="Z6" s="4">
         <f>Y6*1.25</f>
-        <v>23232.5</v>
+        <v>22782.5</v>
       </c>
       <c r="AA6" s="4">
         <f>Z6*1.15</f>
-        <v>26717.374999999996</v>
+        <v>26199.874999999996</v>
       </c>
       <c r="AB6" s="4">
         <f>AA6*1.08</f>
-        <v>28854.764999999999</v>
+        <v>28295.864999999998</v>
       </c>
       <c r="AC6" s="4">
         <f>AB6*1.05</f>
-        <v>30297.503250000002</v>
+        <v>29710.65825</v>
       </c>
       <c r="AD6" s="4">
-        <f>AC6*1.04</f>
-        <v>31509.403380000003</v>
+        <f>AC6*1.03</f>
+        <v>30601.977997500002</v>
       </c>
       <c r="AE6" s="4">
         <f t="shared" ref="AE6:AI6" si="5">AD6*1.02</f>
-        <v>32139.591447600003</v>
+        <v>31214.017557450003</v>
       </c>
       <c r="AF6" s="4">
         <f t="shared" si="5"/>
-        <v>32782.383276552006</v>
+        <v>31838.297908599005</v>
       </c>
       <c r="AG6" s="4">
         <f t="shared" si="5"/>
-        <v>33438.030942083045</v>
+        <v>32475.063866770986</v>
       </c>
       <c r="AH6" s="4">
         <f t="shared" si="5"/>
-        <v>34106.791560924707</v>
+        <v>33124.565144106404</v>
       </c>
       <c r="AI6" s="4">
         <f t="shared" si="5"/>
-        <v>34788.927392143203</v>
+        <v>33787.056446988536</v>
       </c>
     </row>
     <row r="7" spans="1:147" x14ac:dyDescent="0.3">
@@ -1462,13 +1466,15 @@
         <v>1041</v>
       </c>
       <c r="P7" s="4">
-        <v>1057</v>
+        <v>1122</v>
       </c>
       <c r="Q7" s="4">
-        <v>1105</v>
+        <f>Q3*0.023</f>
+        <v>1226.4667199999999</v>
       </c>
       <c r="R7" s="4">
-        <v>1156</v>
+        <f>R3*0.023</f>
+        <v>1311.68885</v>
       </c>
       <c r="U7" s="4">
         <v>2166</v>
@@ -1487,47 +1493,47 @@
       </c>
       <c r="Y7" s="4">
         <f t="shared" si="4"/>
-        <v>4359</v>
+        <v>4701.1555699999999</v>
       </c>
       <c r="Z7" s="4">
         <f>Z3*0.021</f>
-        <v>5370.9465600000003</v>
+        <v>5491.6568070000012</v>
       </c>
       <c r="AA7" s="4">
         <f t="shared" ref="AA7:AI7" si="6">AA3*0.021</f>
-        <v>6015.4601472000004</v>
+        <v>6315.4053280500011</v>
       </c>
       <c r="AB7" s="4">
         <f t="shared" si="6"/>
-        <v>6496.696958976002</v>
+        <v>6883.791807574501</v>
       </c>
       <c r="AC7" s="4">
         <f t="shared" si="6"/>
-        <v>6821.5318069248024</v>
+        <v>7296.819316028972</v>
       </c>
       <c r="AD7" s="4">
         <f t="shared" si="6"/>
-        <v>7094.3930792017945</v>
+        <v>7661.66028183042</v>
       </c>
       <c r="AE7" s="4">
         <f t="shared" si="6"/>
-        <v>7307.2248715778487</v>
+        <v>7968.1266931036371</v>
       </c>
       <c r="AF7" s="4">
         <f t="shared" si="6"/>
-        <v>7453.369369009406</v>
+        <v>8207.1704938967468</v>
       </c>
       <c r="AG7" s="4">
         <f t="shared" si="6"/>
-        <v>7602.4367563895939</v>
+        <v>8371.3139037746805</v>
       </c>
       <c r="AH7" s="4">
         <f t="shared" si="6"/>
-        <v>7754.4854915173864</v>
+        <v>8538.7401818501748</v>
       </c>
       <c r="AI7" s="4">
         <f t="shared" si="6"/>
-        <v>7909.5752013477349</v>
+        <v>8709.5149854871779</v>
       </c>
     </row>
     <row r="8" spans="1:147" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1572,7 +1578,7 @@
         <v>16909</v>
       </c>
       <c r="L8" s="8">
-        <f t="shared" ref="L8:N8" si="8">L5-L6-L7</f>
+        <f t="shared" ref="L8:R8" si="8">L5-L6-L7</f>
         <v>18642</v>
       </c>
       <c r="M8" s="8">
@@ -1584,16 +1590,20 @@
         <v>24034</v>
       </c>
       <c r="O8" s="8">
+        <f t="shared" si="8"/>
         <v>21638</v>
       </c>
       <c r="P8" s="8">
-        <v>29068</v>
+        <f t="shared" si="8"/>
+        <v>28440</v>
       </c>
       <c r="Q8" s="8">
-        <v>32394</v>
+        <f t="shared" si="8"/>
+        <v>33144.173280000003</v>
       </c>
       <c r="R8" s="8">
-        <v>33290</v>
+        <f t="shared" si="8"/>
+        <v>35100.261149999998</v>
       </c>
       <c r="U8" s="8">
         <f>U5-U6-U7</f>
@@ -1613,47 +1623,47 @@
       </c>
       <c r="Y8" s="8">
         <f t="shared" ref="Y8:AI8" si="9">Y5-Y6-Y7</f>
-        <v>116389</v>
+        <v>118322.43443000002</v>
       </c>
       <c r="Z8" s="8">
         <f t="shared" si="9"/>
-        <v>155543.29264</v>
+        <v>160011.21943300002</v>
       </c>
       <c r="AA8" s="8">
         <f t="shared" si="9"/>
-        <v>173511.51275679999</v>
+        <v>184012.90234795003</v>
       </c>
       <c r="AB8" s="8">
         <f t="shared" si="9"/>
-        <v>187392.43377734403</v>
+        <v>200836.06230926552</v>
       </c>
       <c r="AC8" s="8">
         <f t="shared" si="9"/>
-        <v>196762.05546621123</v>
+        <v>213169.18469782147</v>
       </c>
       <c r="AD8" s="8">
         <f t="shared" si="9"/>
-        <v>204632.53768485968</v>
+        <v>224421.85709771255</v>
       </c>
       <c r="AE8" s="8">
         <f t="shared" si="9"/>
-        <v>211086.60784920552</v>
+        <v>234010.77094157104</v>
       </c>
       <c r="AF8" s="8">
         <f t="shared" si="9"/>
-        <v>215308.34000618965</v>
+        <v>241343.23424539264</v>
       </c>
       <c r="AG8" s="8">
         <f t="shared" si="9"/>
-        <v>219614.50680631341</v>
+        <v>246170.09893030048</v>
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="9"/>
-        <v>224006.79694243969</v>
+        <v>251093.50090890654</v>
       </c>
       <c r="AI8" s="8">
         <f t="shared" si="9"/>
-        <v>228486.93288128852</v>
+        <v>256115.37092708467</v>
       </c>
     </row>
     <row r="9" spans="1:147" x14ac:dyDescent="0.3">
@@ -1700,7 +1710,7 @@
         <v>-515</v>
       </c>
       <c r="P9" s="4">
-        <v>-525</v>
+        <v>-592</v>
       </c>
       <c r="Q9" s="4">
         <v>-536</v>
@@ -1725,47 +1735,47 @@
       </c>
       <c r="Y9" s="4">
         <f t="shared" ref="Y9:Y11" si="10">SUM(O9:R9)</f>
-        <v>-2123</v>
+        <v>-2190</v>
       </c>
       <c r="Z9" s="4">
         <f t="shared" ref="Z9:AI9" si="11">Y9*1.02</f>
-        <v>-2165.46</v>
+        <v>-2233.8000000000002</v>
       </c>
       <c r="AA9" s="4">
         <f t="shared" si="11"/>
-        <v>-2208.7692000000002</v>
+        <v>-2278.4760000000001</v>
       </c>
       <c r="AB9" s="4">
         <f t="shared" si="11"/>
-        <v>-2252.9445840000003</v>
+        <v>-2324.0455200000001</v>
       </c>
       <c r="AC9" s="4">
         <f t="shared" si="11"/>
-        <v>-2298.0034756800005</v>
+        <v>-2370.5264304000002</v>
       </c>
       <c r="AD9" s="4">
         <f t="shared" si="11"/>
-        <v>-2343.9635451936006</v>
+        <v>-2417.936959008</v>
       </c>
       <c r="AE9" s="4">
         <f t="shared" si="11"/>
-        <v>-2390.8428160974727</v>
+        <v>-2466.2956981881603</v>
       </c>
       <c r="AF9" s="4">
         <f t="shared" si="11"/>
-        <v>-2438.6596724194223</v>
+        <v>-2515.6216121519237</v>
       </c>
       <c r="AG9" s="4">
         <f t="shared" si="11"/>
-        <v>-2487.432865867811</v>
+        <v>-2565.9340443949623</v>
       </c>
       <c r="AH9" s="4">
         <f t="shared" si="11"/>
-        <v>-2537.1815231851674</v>
+        <v>-2617.2527252828613</v>
       </c>
       <c r="AI9" s="4">
         <f t="shared" si="11"/>
-        <v>-2587.9251536488709</v>
+        <v>-2669.5977797885184</v>
       </c>
     </row>
     <row r="10" spans="1:147" x14ac:dyDescent="0.3">
@@ -1812,7 +1822,7 @@
         <v>63</v>
       </c>
       <c r="P10" s="4">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q10" s="4">
         <v>63</v>
@@ -1837,47 +1847,47 @@
       </c>
       <c r="Y10" s="4">
         <f t="shared" si="10"/>
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Z10" s="4">
         <f t="shared" ref="Z10:AI10" si="12">Y10*1.01</f>
-        <v>254.52</v>
+        <v>253.51</v>
       </c>
       <c r="AA10" s="4">
         <f t="shared" si="12"/>
-        <v>257.0652</v>
+        <v>256.04509999999999</v>
       </c>
       <c r="AB10" s="4">
         <f t="shared" si="12"/>
-        <v>259.635852</v>
+        <v>258.60555099999999</v>
       </c>
       <c r="AC10" s="4">
         <f t="shared" si="12"/>
-        <v>262.23221052000002</v>
+        <v>261.19160650999999</v>
       </c>
       <c r="AD10" s="4">
         <f t="shared" si="12"/>
-        <v>264.85453262520002</v>
+        <v>263.80352257509998</v>
       </c>
       <c r="AE10" s="4">
         <f t="shared" si="12"/>
-        <v>267.50307795145204</v>
+        <v>266.441557800851</v>
       </c>
       <c r="AF10" s="4">
         <f t="shared" si="12"/>
-        <v>270.17810873096658</v>
+        <v>269.10597337885952</v>
       </c>
       <c r="AG10" s="4">
         <f t="shared" si="12"/>
-        <v>272.87988981827624</v>
+        <v>271.79703311264814</v>
       </c>
       <c r="AH10" s="4">
         <f t="shared" si="12"/>
-        <v>275.60868871645903</v>
+        <v>274.51500344377462</v>
       </c>
       <c r="AI10" s="4">
         <f t="shared" si="12"/>
-        <v>278.36477560362363</v>
+        <v>277.26015347821237</v>
       </c>
     </row>
     <row r="11" spans="1:147" x14ac:dyDescent="0.3">
@@ -1925,7 +1935,7 @@
         <v>180</v>
       </c>
       <c r="P11" s="4">
-        <v>0</v>
+        <v>-2236</v>
       </c>
       <c r="Q11" s="4">
         <v>0</v>
@@ -1950,7 +1960,7 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" si="10"/>
-        <v>180</v>
+        <v>-2056</v>
       </c>
       <c r="Z11" s="4">
         <v>0</v>
@@ -2025,7 +2035,7 @@
         <v>17279</v>
       </c>
       <c r="L12" s="8">
-        <f t="shared" ref="L12:N12" si="14">L8-L9-L10-L11</f>
+        <f t="shared" ref="L12:R12" si="14">L8-L9-L10-L11</f>
         <v>19214</v>
       </c>
       <c r="M12" s="8">
@@ -2037,16 +2047,20 @@
         <v>25217</v>
       </c>
       <c r="O12" s="8">
+        <f t="shared" si="14"/>
         <v>21910</v>
       </c>
       <c r="P12" s="8">
-        <v>29530</v>
+        <f t="shared" si="14"/>
+        <v>31206</v>
       </c>
       <c r="Q12" s="8">
-        <v>32867</v>
+        <f t="shared" si="14"/>
+        <v>33617.173280000003</v>
       </c>
       <c r="R12" s="8">
-        <v>33773</v>
+        <f t="shared" si="14"/>
+        <v>35584.261149999998</v>
       </c>
       <c r="U12" s="8">
         <f>U8-U9-U10-U11</f>
@@ -2066,47 +2080,47 @@
       </c>
       <c r="Y12" s="8">
         <f t="shared" ref="Y12:AI12" si="15">Y8-Y9-Y10-Y11</f>
-        <v>118080</v>
+        <v>122317.43443000002</v>
       </c>
       <c r="Z12" s="8">
         <f t="shared" si="15"/>
-        <v>157454.23264</v>
+        <v>161991.509433</v>
       </c>
       <c r="AA12" s="8">
         <f t="shared" si="15"/>
-        <v>175463.21675679999</v>
+        <v>186035.33324795004</v>
       </c>
       <c r="AB12" s="8">
         <f t="shared" si="15"/>
-        <v>189385.74250934404</v>
+        <v>202901.50227826554</v>
       </c>
       <c r="AC12" s="8">
         <f t="shared" si="15"/>
-        <v>198797.82673137123</v>
+        <v>215278.51952171148</v>
       </c>
       <c r="AD12" s="8">
         <f t="shared" si="15"/>
-        <v>206711.64669742808</v>
+        <v>226575.99053414544</v>
       </c>
       <c r="AE12" s="8">
         <f t="shared" si="15"/>
-        <v>213209.94758735152</v>
+        <v>236210.62508195834</v>
       </c>
       <c r="AF12" s="8">
         <f t="shared" si="15"/>
-        <v>217476.82156987811</v>
+        <v>243589.74988416568</v>
       </c>
       <c r="AG12" s="8">
         <f t="shared" si="15"/>
-        <v>221829.05978236292</v>
+        <v>248464.2359415828</v>
       </c>
       <c r="AH12" s="8">
         <f t="shared" si="15"/>
-        <v>226268.3697769084</v>
+        <v>253436.23863074562</v>
       </c>
       <c r="AI12" s="8">
         <f t="shared" si="15"/>
-        <v>230796.49325933374</v>
+        <v>258507.70855339497</v>
       </c>
     </row>
     <row r="13" spans="1:147" x14ac:dyDescent="0.3">
@@ -2153,7 +2167,7 @@
         <v>3135</v>
       </c>
       <c r="P13" s="4">
-        <v>4134</v>
+        <v>4784</v>
       </c>
       <c r="Q13" s="4">
         <v>4601</v>
@@ -2178,47 +2192,47 @@
       </c>
       <c r="Y13" s="4">
         <f>SUM(O13:R13)</f>
-        <v>16598</v>
+        <v>17248</v>
       </c>
       <c r="Z13" s="4">
         <f t="shared" ref="Z13:AI13" si="16">Z12*0.14</f>
-        <v>22043.592569600001</v>
+        <v>22678.811320620003</v>
       </c>
       <c r="AA13" s="4">
         <f t="shared" si="16"/>
-        <v>24564.850345952</v>
+        <v>26044.946654713007</v>
       </c>
       <c r="AB13" s="4">
         <f t="shared" si="16"/>
-        <v>26514.003951308168</v>
+        <v>28406.210318957179</v>
       </c>
       <c r="AC13" s="4">
         <f t="shared" si="16"/>
-        <v>27831.695742391974</v>
+        <v>30138.992733039609</v>
       </c>
       <c r="AD13" s="4">
         <f t="shared" si="16"/>
-        <v>28939.630537639932</v>
+        <v>31720.638674780366</v>
       </c>
       <c r="AE13" s="4">
         <f t="shared" si="16"/>
-        <v>29849.392662229217</v>
+        <v>33069.487511474174</v>
       </c>
       <c r="AF13" s="4">
         <f t="shared" si="16"/>
-        <v>30446.755019782941</v>
+        <v>34102.564983783195</v>
       </c>
       <c r="AG13" s="4">
         <f t="shared" si="16"/>
-        <v>31056.068369530811</v>
+        <v>34784.993031821592</v>
       </c>
       <c r="AH13" s="4">
         <f t="shared" si="16"/>
-        <v>31677.571768767179</v>
+        <v>35481.073408304394</v>
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="16"/>
-        <v>32311.509056306728</v>
+        <v>36191.079197475301</v>
       </c>
     </row>
     <row r="14" spans="1:147" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2263,7 +2277,7 @@
         <v>14881</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" ref="L14:N14" si="18">L12-L13</f>
+        <f t="shared" ref="L14:R14" si="18">L12-L13</f>
         <v>16599</v>
       </c>
       <c r="M14" s="8">
@@ -2275,16 +2289,20 @@
         <v>22091</v>
       </c>
       <c r="O14" s="8">
+        <f t="shared" si="18"/>
         <v>18775</v>
       </c>
       <c r="P14" s="8">
-        <v>25396</v>
+        <f t="shared" si="18"/>
+        <v>26422</v>
       </c>
       <c r="Q14" s="8">
-        <v>28266</v>
+        <f t="shared" si="18"/>
+        <v>29016.173280000003</v>
       </c>
       <c r="R14" s="8">
-        <v>29045</v>
+        <f t="shared" si="18"/>
+        <v>30856.261149999998</v>
       </c>
       <c r="U14" s="8">
         <f>U12-U13</f>
@@ -2304,495 +2322,495 @@
       </c>
       <c r="Y14" s="8">
         <f t="shared" ref="Y14:AI14" si="19">Y12-Y13</f>
-        <v>101482</v>
+        <v>105069.43443000002</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="19"/>
-        <v>135410.6400704</v>
+        <v>139312.69811237999</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="19"/>
-        <v>150898.36641084799</v>
+        <v>159990.38659323702</v>
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="19"/>
-        <v>162871.73855803587</v>
+        <v>174495.29195930838</v>
       </c>
       <c r="AC14" s="8">
         <f t="shared" si="19"/>
-        <v>170966.13098897925</v>
+        <v>185139.52678867188</v>
       </c>
       <c r="AD14" s="8">
         <f t="shared" si="19"/>
-        <v>177772.01615978815</v>
+        <v>194855.35185936507</v>
       </c>
       <c r="AE14" s="8">
         <f t="shared" si="19"/>
-        <v>183360.5549251223</v>
+        <v>203141.13757048416</v>
       </c>
       <c r="AF14" s="8">
         <f t="shared" si="19"/>
-        <v>187030.06655009516</v>
+        <v>209487.18490038248</v>
       </c>
       <c r="AG14" s="8">
         <f t="shared" si="19"/>
-        <v>190772.99141283211</v>
+        <v>213679.2429097612</v>
       </c>
       <c r="AH14" s="8">
         <f t="shared" si="19"/>
-        <v>194590.79800814122</v>
+        <v>217955.16522244122</v>
       </c>
       <c r="AI14" s="8">
         <f t="shared" si="19"/>
-        <v>198484.98420302701</v>
+        <v>222316.62935591966</v>
       </c>
       <c r="AJ14" s="7">
         <f>AI14*($AL$19+1)</f>
-        <v>196500.13436099674</v>
+        <v>220093.46306236048</v>
       </c>
       <c r="AK14" s="7">
         <f t="shared" ref="AK14:CV14" si="20">AJ14*($AL$19+1)</f>
-        <v>194535.13301738678</v>
+        <v>217892.52843173686</v>
       </c>
       <c r="AL14" s="7">
         <f t="shared" si="20"/>
-        <v>192589.7816872129</v>
+        <v>215713.60314741949</v>
       </c>
       <c r="AM14" s="7">
         <f t="shared" si="20"/>
-        <v>190663.88387034077</v>
+        <v>213556.4671159453</v>
       </c>
       <c r="AN14" s="7">
         <f t="shared" si="20"/>
-        <v>188757.24503163737</v>
+        <v>211420.90244478584</v>
       </c>
       <c r="AO14" s="7">
         <f t="shared" si="20"/>
-        <v>186869.67258132101</v>
+        <v>209306.69342033798</v>
       </c>
       <c r="AP14" s="7">
         <f t="shared" si="20"/>
-        <v>185000.9758555078</v>
+        <v>207213.6264861346</v>
       </c>
       <c r="AQ14" s="7">
         <f t="shared" si="20"/>
-        <v>183150.96609695273</v>
+        <v>205141.49022127324</v>
       </c>
       <c r="AR14" s="7">
         <f t="shared" si="20"/>
-        <v>181319.45643598321</v>
+        <v>203090.0753190605</v>
       </c>
       <c r="AS14" s="7">
         <f t="shared" si="20"/>
-        <v>179506.26187162337</v>
+        <v>201059.17456586991</v>
       </c>
       <c r="AT14" s="7">
         <f t="shared" si="20"/>
-        <v>177711.19925290713</v>
+        <v>199048.58282021122</v>
       </c>
       <c r="AU14" s="7">
         <f t="shared" si="20"/>
-        <v>175934.08726037806</v>
+        <v>197058.09699200912</v>
       </c>
       <c r="AV14" s="7">
         <f t="shared" si="20"/>
-        <v>174174.74638777427</v>
+        <v>195087.51602208902</v>
       </c>
       <c r="AW14" s="7">
         <f t="shared" si="20"/>
-        <v>172432.99892389652</v>
+        <v>193136.64086186813</v>
       </c>
       <c r="AX14" s="7">
         <f t="shared" si="20"/>
-        <v>170708.66893465756</v>
+        <v>191205.27445324944</v>
       </c>
       <c r="AY14" s="7">
         <f t="shared" si="20"/>
-        <v>169001.58224531097</v>
+        <v>189293.22170871694</v>
       </c>
       <c r="AZ14" s="7">
         <f t="shared" si="20"/>
-        <v>167311.56642285787</v>
+        <v>187400.28949162978</v>
       </c>
       <c r="BA14" s="7">
         <f t="shared" si="20"/>
-        <v>165638.45075862927</v>
+        <v>185526.28659671347</v>
       </c>
       <c r="BB14" s="7">
         <f t="shared" si="20"/>
-        <v>163982.06625104297</v>
+        <v>183671.02373074632</v>
       </c>
       <c r="BC14" s="7">
         <f t="shared" si="20"/>
-        <v>162342.24558853253</v>
+        <v>181834.31349343885</v>
       </c>
       <c r="BD14" s="7">
         <f t="shared" si="20"/>
-        <v>160718.8231326472</v>
+        <v>180015.97035850445</v>
       </c>
       <c r="BE14" s="7">
         <f t="shared" si="20"/>
-        <v>159111.63490132074</v>
+        <v>178215.81065491939</v>
       </c>
       <c r="BF14" s="7">
         <f t="shared" si="20"/>
-        <v>157520.51855230753</v>
+        <v>176433.65254837018</v>
       </c>
       <c r="BG14" s="7">
         <f t="shared" si="20"/>
-        <v>155945.31336678445</v>
+        <v>174669.31602288649</v>
       </c>
       <c r="BH14" s="7">
         <f t="shared" si="20"/>
-        <v>154385.8602331166</v>
+        <v>172922.62286265762</v>
       </c>
       <c r="BI14" s="7">
         <f t="shared" si="20"/>
-        <v>152842.00163078544</v>
+        <v>171193.39663403103</v>
       </c>
       <c r="BJ14" s="7">
         <f t="shared" si="20"/>
-        <v>151313.58161447759</v>
+        <v>169481.46266769071</v>
       </c>
       <c r="BK14" s="7">
         <f t="shared" si="20"/>
-        <v>149800.4457983328</v>
+        <v>167786.6480410138</v>
       </c>
       <c r="BL14" s="7">
         <f t="shared" si="20"/>
-        <v>148302.44134034947</v>
+        <v>166108.78156060367</v>
       </c>
       <c r="BM14" s="7">
         <f t="shared" si="20"/>
-        <v>146819.41692694597</v>
+        <v>164447.69374499764</v>
       </c>
       <c r="BN14" s="7">
         <f t="shared" si="20"/>
-        <v>145351.2227576765</v>
+        <v>162803.21680754767</v>
       </c>
       <c r="BO14" s="7">
         <f t="shared" si="20"/>
-        <v>143897.71053009972</v>
+        <v>161175.18463947219</v>
       </c>
       <c r="BP14" s="7">
         <f t="shared" si="20"/>
-        <v>142458.73342479873</v>
+        <v>159563.43279307746</v>
       </c>
       <c r="BQ14" s="7">
         <f t="shared" si="20"/>
-        <v>141034.14609055076</v>
+        <v>157967.79846514668</v>
       </c>
       <c r="BR14" s="7">
         <f t="shared" si="20"/>
-        <v>139623.80462964525</v>
+        <v>156388.12048049521</v>
       </c>
       <c r="BS14" s="7">
         <f t="shared" si="20"/>
-        <v>138227.56658334879</v>
+        <v>154824.23927569026</v>
       </c>
       <c r="BT14" s="7">
         <f t="shared" si="20"/>
-        <v>136845.29091751529</v>
+        <v>153275.99688293334</v>
       </c>
       <c r="BU14" s="7">
         <f t="shared" si="20"/>
-        <v>135476.83800834013</v>
+        <v>151743.236914104</v>
       </c>
       <c r="BV14" s="7">
         <f t="shared" si="20"/>
-        <v>134122.06962825672</v>
+        <v>150225.80454496294</v>
       </c>
       <c r="BW14" s="7">
         <f t="shared" si="20"/>
-        <v>132780.84893197415</v>
+        <v>148723.54649951332</v>
       </c>
       <c r="BX14" s="7">
         <f t="shared" si="20"/>
-        <v>131453.0404426544</v>
+        <v>147236.31103451818</v>
       </c>
       <c r="BY14" s="7">
         <f t="shared" si="20"/>
-        <v>130138.51003822785</v>
+        <v>145763.947924173</v>
       </c>
       <c r="BZ14" s="7">
         <f t="shared" si="20"/>
-        <v>128837.12493784557</v>
+        <v>144306.30844493126</v>
       </c>
       <c r="CA14" s="7">
         <f t="shared" si="20"/>
-        <v>127548.75368846711</v>
+        <v>142863.24536048193</v>
       </c>
       <c r="CB14" s="7">
         <f t="shared" si="20"/>
-        <v>126273.26615158244</v>
+        <v>141434.6129068771</v>
       </c>
       <c r="CC14" s="7">
         <f t="shared" si="20"/>
-        <v>125010.53349006662</v>
+        <v>140020.26677780831</v>
       </c>
       <c r="CD14" s="7">
         <f t="shared" si="20"/>
-        <v>123760.42815516595</v>
+        <v>138620.06411003022</v>
       </c>
       <c r="CE14" s="7">
         <f t="shared" si="20"/>
-        <v>122522.8238736143</v>
+        <v>137233.86346892992</v>
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="20"/>
-        <v>121297.59563487815</v>
+        <v>135861.52483424061</v>
       </c>
       <c r="CG14" s="7">
         <f t="shared" si="20"/>
-        <v>120084.61967852936</v>
+        <v>134502.90958589822</v>
       </c>
       <c r="CH14" s="7">
         <f t="shared" si="20"/>
-        <v>118883.77348174407</v>
+        <v>133157.88049003924</v>
       </c>
       <c r="CI14" s="7">
         <f t="shared" si="20"/>
-        <v>117694.93574692663</v>
+        <v>131826.30168513884</v>
       </c>
       <c r="CJ14" s="7">
         <f t="shared" si="20"/>
-        <v>116517.98638945736</v>
+        <v>130508.03866828745</v>
       </c>
       <c r="CK14" s="7">
         <f t="shared" si="20"/>
-        <v>115352.80652556279</v>
+        <v>129202.95828160457</v>
       </c>
       <c r="CL14" s="7">
         <f t="shared" si="20"/>
-        <v>114199.27846030716</v>
+        <v>127910.92869878853</v>
       </c>
       <c r="CM14" s="7">
         <f t="shared" si="20"/>
-        <v>113057.28567570409</v>
+        <v>126631.81941180064</v>
       </c>
       <c r="CN14" s="7">
         <f t="shared" si="20"/>
-        <v>111926.71281894704</v>
+        <v>125365.50121768263</v>
       </c>
       <c r="CO14" s="7">
         <f t="shared" si="20"/>
-        <v>110807.44569075757</v>
+        <v>124111.8462055058</v>
       </c>
       <c r="CP14" s="7">
         <f t="shared" si="20"/>
-        <v>109699.37123384999</v>
+        <v>122870.72774345074</v>
       </c>
       <c r="CQ14" s="7">
         <f t="shared" si="20"/>
-        <v>108602.37752151149</v>
+        <v>121642.02046601623</v>
       </c>
       <c r="CR14" s="7">
         <f t="shared" si="20"/>
-        <v>107516.35374629637</v>
+        <v>120425.60026135607</v>
       </c>
       <c r="CS14" s="7">
         <f t="shared" si="20"/>
-        <v>106441.1902088334</v>
+        <v>119221.34425874251</v>
       </c>
       <c r="CT14" s="7">
         <f t="shared" si="20"/>
-        <v>105376.77830674507</v>
+        <v>118029.13081615508</v>
       </c>
       <c r="CU14" s="7">
         <f t="shared" si="20"/>
-        <v>104323.01052367761</v>
+        <v>116848.83950799353</v>
       </c>
       <c r="CV14" s="7">
         <f t="shared" si="20"/>
-        <v>103279.78041844083</v>
+        <v>115680.35111291359</v>
       </c>
       <c r="CW14" s="7">
         <f t="shared" ref="CW14:EQ14" si="21">CV14*($AL$19+1)</f>
-        <v>102246.98261425643</v>
+        <v>114523.54760178445</v>
       </c>
       <c r="CX14" s="7">
         <f t="shared" si="21"/>
-        <v>101224.51278811386</v>
+        <v>113378.31212576661</v>
       </c>
       <c r="CY14" s="7">
         <f t="shared" si="21"/>
-        <v>100212.26766023273</v>
+        <v>112244.52900450894</v>
       </c>
       <c r="CZ14" s="7">
         <f t="shared" si="21"/>
-        <v>99210.144983630395</v>
+        <v>111122.08371446385</v>
       </c>
       <c r="DA14" s="7">
         <f t="shared" si="21"/>
-        <v>98218.043533794087</v>
+        <v>110010.86287731922</v>
       </c>
       <c r="DB14" s="7">
         <f t="shared" si="21"/>
-        <v>97235.863098456146</v>
+        <v>108910.75424854603</v>
       </c>
       <c r="DC14" s="7">
         <f t="shared" si="21"/>
-        <v>96263.50446747159</v>
+        <v>107821.64670606056</v>
       </c>
       <c r="DD14" s="7">
         <f t="shared" si="21"/>
-        <v>95300.869422796866</v>
+        <v>106743.43023899996</v>
       </c>
       <c r="DE14" s="7">
         <f t="shared" si="21"/>
-        <v>94347.860728568892</v>
+        <v>105675.99593660996</v>
       </c>
       <c r="DF14" s="7">
         <f t="shared" si="21"/>
-        <v>93404.382121283197</v>
+        <v>104619.23597724386</v>
       </c>
       <c r="DG14" s="7">
         <f t="shared" si="21"/>
-        <v>92470.338300070362</v>
+        <v>103573.04361747143</v>
       </c>
       <c r="DH14" s="7">
         <f t="shared" si="21"/>
-        <v>91545.634917069663</v>
+        <v>102537.31318129672</v>
       </c>
       <c r="DI14" s="7">
         <f t="shared" si="21"/>
-        <v>90630.178567898969</v>
+        <v>101511.94004948375</v>
       </c>
       <c r="DJ14" s="7">
         <f t="shared" si="21"/>
-        <v>89723.876782219973</v>
+        <v>100496.82064898891</v>
       </c>
       <c r="DK14" s="7">
         <f t="shared" si="21"/>
-        <v>88826.638014397773</v>
+        <v>99491.852442499017</v>
       </c>
       <c r="DL14" s="7">
         <f t="shared" si="21"/>
-        <v>87938.371634253795</v>
+        <v>98496.933918074021</v>
       </c>
       <c r="DM14" s="7">
         <f t="shared" si="21"/>
-        <v>87058.987917911261</v>
+        <v>97511.964578893283</v>
       </c>
       <c r="DN14" s="7">
         <f t="shared" si="21"/>
-        <v>86188.39803873215</v>
+        <v>96536.844933104352</v>
       </c>
       <c r="DO14" s="7">
         <f t="shared" si="21"/>
-        <v>85326.514058344823</v>
+        <v>95571.476483773309</v>
       </c>
       <c r="DP14" s="7">
         <f t="shared" si="21"/>
-        <v>84473.248917761375</v>
+        <v>94615.761718935581</v>
       </c>
       <c r="DQ14" s="7">
         <f t="shared" si="21"/>
-        <v>83628.516428583767</v>
+        <v>93669.604101746227</v>
       </c>
       <c r="DR14" s="7">
         <f t="shared" si="21"/>
-        <v>82792.231264297923</v>
+        <v>92732.908060728761</v>
       </c>
       <c r="DS14" s="7">
         <f t="shared" si="21"/>
-        <v>81964.308951654937</v>
+        <v>91805.578980121471</v>
       </c>
       <c r="DT14" s="7">
         <f t="shared" si="21"/>
-        <v>81144.665862138383</v>
+        <v>90887.523190320251</v>
       </c>
       <c r="DU14" s="7">
         <f t="shared" si="21"/>
-        <v>80333.219203517001</v>
+        <v>89978.647958417045</v>
       </c>
       <c r="DV14" s="7">
         <f t="shared" si="21"/>
-        <v>79529.887011481827</v>
+        <v>89078.86147883287</v>
       </c>
       <c r="DW14" s="7">
         <f t="shared" si="21"/>
-        <v>78734.588141367014</v>
+        <v>88188.072864044545</v>
       </c>
       <c r="DX14" s="7">
         <f t="shared" si="21"/>
-        <v>77947.242259953346</v>
+        <v>87306.192135404097</v>
       </c>
       <c r="DY14" s="7">
         <f t="shared" si="21"/>
-        <v>77167.769837353815</v>
+        <v>86433.130214050048</v>
       </c>
       <c r="DZ14" s="7">
         <f t="shared" si="21"/>
-        <v>76396.092138980282</v>
+        <v>85568.798911909544</v>
       </c>
       <c r="EA14" s="7">
         <f t="shared" si="21"/>
-        <v>75632.131217590475</v>
+        <v>84713.110922790453</v>
       </c>
       <c r="EB14" s="7">
         <f t="shared" si="21"/>
-        <v>74875.809905414571</v>
+        <v>83865.979813562546</v>
       </c>
       <c r="EC14" s="7">
         <f t="shared" si="21"/>
-        <v>74127.051806360425</v>
+        <v>83027.320015426914</v>
       </c>
       <c r="ED14" s="7">
         <f t="shared" si="21"/>
-        <v>73385.781288296814</v>
+        <v>82197.046815272639</v>
       </c>
       <c r="EE14" s="7">
         <f t="shared" si="21"/>
-        <v>72651.923475413845</v>
+        <v>81375.076347119917</v>
       </c>
       <c r="EF14" s="7">
         <f t="shared" si="21"/>
-        <v>71925.4042406597</v>
+        <v>80561.325583648722</v>
       </c>
       <c r="EG14" s="7">
         <f t="shared" si="21"/>
-        <v>71206.150198253104</v>
+        <v>79755.712327812231</v>
       </c>
       <c r="EH14" s="7">
         <f t="shared" si="21"/>
-        <v>70494.08869627057</v>
+        <v>78958.155204534109</v>
       </c>
       <c r="EI14" s="7">
         <f t="shared" si="21"/>
-        <v>69789.147809307862</v>
+        <v>78168.573652488762</v>
       </c>
       <c r="EJ14" s="7">
         <f t="shared" si="21"/>
-        <v>69091.256331214783</v>
+        <v>77386.887915963875</v>
       </c>
       <c r="EK14" s="7">
         <f t="shared" si="21"/>
-        <v>68400.343767902639</v>
+        <v>76613.019036804239</v>
       </c>
       <c r="EL14" s="7">
         <f t="shared" si="21"/>
-        <v>67716.340330223611</v>
+        <v>75846.888846436195</v>
       </c>
       <c r="EM14" s="7">
         <f t="shared" si="21"/>
-        <v>67039.176926921369</v>
+        <v>75088.419957971826</v>
       </c>
       <c r="EN14" s="7">
         <f t="shared" si="21"/>
-        <v>66368.78515765215</v>
+        <v>74337.535758392114</v>
       </c>
       <c r="EO14" s="7">
         <f t="shared" si="21"/>
-        <v>65705.097306075622</v>
+        <v>73594.160400808192</v>
       </c>
       <c r="EP14" s="7">
         <f t="shared" si="21"/>
-        <v>65048.046333014863</v>
+        <v>72858.218796800109</v>
       </c>
       <c r="EQ14" s="7">
         <f t="shared" si="21"/>
-        <v>64397.565869684717</v>
+        <v>72129.636608832108</v>
       </c>
     </row>
     <row r="15" spans="1:147" x14ac:dyDescent="0.3">
@@ -2839,13 +2857,13 @@
         <v>24441</v>
       </c>
       <c r="P15" s="4">
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="Q15" s="4">
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="R15" s="4">
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="U15" s="4">
         <v>2462</v>
@@ -2860,48 +2878,37 @@
         <v>24489</v>
       </c>
       <c r="Y15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="Z15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="AA15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="AB15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="AC15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="AD15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="AE15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="AF15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="AG15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="AH15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
       <c r="AI15" s="4">
-        <f>24441</f>
-        <v>24441</v>
+        <v>24366</v>
       </c>
     </row>
     <row r="16" spans="1:147" x14ac:dyDescent="0.3">
@@ -2986,47 +2993,47 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" ref="Y16:AI16" si="24">Y14/Y15</f>
-        <v>4.1521214352931546</v>
+        <v>4.3121330719034727</v>
       </c>
       <c r="Z16" s="6">
         <f t="shared" si="24"/>
-        <v>5.5403068643017876</v>
+        <v>5.7175038214060576</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="24"/>
-        <v>6.1739849601427101</v>
+        <v>6.5661325861133149</v>
       </c>
       <c r="AB16" s="6">
         <f t="shared" si="24"/>
-        <v>6.6638737595857727</v>
+        <v>7.1614254272062867</v>
       </c>
       <c r="AC16" s="6">
         <f t="shared" si="24"/>
-        <v>6.9950546617969493</v>
+        <v>7.5982732819778329</v>
       </c>
       <c r="AD16" s="6">
         <f t="shared" si="24"/>
-        <v>7.2735164747673231</v>
+        <v>7.9970184625857783</v>
       </c>
       <c r="AE16" s="6">
         <f t="shared" si="24"/>
-        <v>7.502170734631247</v>
+        <v>8.3370736916393398</v>
       </c>
       <c r="AF16" s="6">
         <f t="shared" si="24"/>
-        <v>7.6523082750335565</v>
+        <v>8.5975205163088919</v>
       </c>
       <c r="AG16" s="6">
         <f t="shared" si="24"/>
-        <v>7.8054495075010069</v>
+        <v>8.7695659078125754</v>
       </c>
       <c r="AH16" s="6">
         <f t="shared" si="24"/>
-        <v>7.9616545152874769</v>
+        <v>8.9450531569581067</v>
       </c>
       <c r="AI16" s="6">
         <f t="shared" si="24"/>
-        <v>8.1209845834060399</v>
+        <v>9.1240511103964401</v>
       </c>
     </row>
     <row r="18" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -3072,15 +3079,15 @@
       </c>
       <c r="P18" s="9">
         <f t="shared" ref="P18" si="27">P3/L3-1</f>
-        <v>0.60000000000000009</v>
+        <v>0.5560252996005326</v>
       </c>
       <c r="Q18" s="9">
         <f t="shared" ref="Q18" si="28">Q3/M3-1</f>
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="R18" s="9">
         <f t="shared" ref="R18" si="29">R3/N3-1</f>
-        <v>0.39998982990516385</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="U18" s="9"/>
       <c r="V18" s="9">
@@ -3097,35 +3104,35 @@
       </c>
       <c r="Y18" s="9">
         <f t="shared" si="30"/>
-        <v>0.5311616358996758</v>
+        <v>0.54148823344597985</v>
       </c>
       <c r="Z18" s="9">
         <f t="shared" si="30"/>
-        <v>0.28000000000000003</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AA18" s="9">
         <f t="shared" si="30"/>
-        <v>0.12000000000000011</v>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AB18" s="9">
         <f t="shared" si="30"/>
-        <v>8.0000000000000071E-2</v>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="AC18" s="9">
         <f t="shared" si="30"/>
-        <v>5.0000000000000044E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AD18" s="9">
         <f t="shared" si="30"/>
-        <v>4.0000000000000036E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE18" s="9">
         <f t="shared" si="30"/>
-        <v>3.0000000000000027E-2</v>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF18" s="9">
         <f t="shared" si="30"/>
-        <v>2.0000000000000018E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG18" s="9">
         <f t="shared" si="30"/>
@@ -3198,15 +3205,15 @@
       </c>
       <c r="P19" s="10">
         <f t="shared" si="33"/>
-        <v>0.71999833555259651</v>
+        <v>0.72423678411740799</v>
       </c>
       <c r="Q19" s="10">
         <f t="shared" si="33"/>
-        <v>0.73000399065047605</v>
+        <v>0.73355656972086447</v>
       </c>
       <c r="R19" s="10">
         <f t="shared" si="33"/>
-        <v>0.72001162304996091</v>
+        <v>0.72965082382151836</v>
       </c>
       <c r="U19" s="10">
         <f t="shared" ref="U19:V19" si="34">U5/U3</f>
@@ -3226,7 +3233,7 @@
       </c>
       <c r="Y19" s="10">
         <f t="shared" si="35"/>
-        <v>0.69732548595679944</v>
+        <v>0.70217676422983366</v>
       </c>
       <c r="Z19" s="10">
         <f t="shared" si="35"/>
@@ -3258,11 +3265,11 @@
       </c>
       <c r="AG19" s="10">
         <f t="shared" si="35"/>
-        <v>0.72</v>
+        <v>0.71999999999999986</v>
       </c>
       <c r="AH19" s="10">
         <f t="shared" si="35"/>
-        <v>0.71999999999999986</v>
+        <v>0.72</v>
       </c>
       <c r="AI19" s="10">
         <f t="shared" si="35"/>
@@ -3321,11 +3328,11 @@
       </c>
       <c r="P20" s="10">
         <f t="shared" ref="P20" si="38">P6/L6-1</f>
-        <v>0.45016181229773466</v>
+        <v>0.38867313915857604</v>
       </c>
       <c r="Q20" s="10">
         <f t="shared" ref="Q20" si="39">Q6/M6-1</f>
-        <v>0.45014749262536879</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="R20" s="10">
         <f t="shared" ref="R20" si="40">R6/N6-1</f>
@@ -3346,7 +3353,7 @@
       </c>
       <c r="Y20" s="10">
         <f t="shared" si="41"/>
-        <v>0.43921325693046298</v>
+        <v>0.41133653399411485</v>
       </c>
       <c r="Z20" s="10">
         <f t="shared" si="41"/>
@@ -3366,7 +3373,7 @@
       </c>
       <c r="AD20" s="10">
         <f t="shared" si="41"/>
-        <v>4.0000000000000036E-2</v>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE20" s="10">
         <f t="shared" si="41"/>
@@ -3453,15 +3460,15 @@
       </c>
       <c r="P21" s="10">
         <f t="shared" si="44"/>
-        <v>2.1991511318242344E-2</v>
+        <v>2.4003594121044861E-2</v>
       </c>
       <c r="Q21" s="10">
         <f t="shared" si="44"/>
-        <v>2.0998422742907093E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="R21" s="10">
         <f t="shared" si="44"/>
-        <v>2.0994133991972832E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="U21" s="10">
         <f t="shared" ref="U21:V21" si="45">U7/U3</f>
@@ -3481,7 +3488,7 @@
       </c>
       <c r="Y21" s="10">
         <f t="shared" si="46"/>
-        <v>2.1815506576181611E-2</v>
+        <v>2.3370278145824413E-2</v>
       </c>
       <c r="Z21" s="10">
         <f t="shared" si="46"/>
@@ -3513,7 +3520,7 @@
       </c>
       <c r="AG21" s="10">
         <f t="shared" si="46"/>
-        <v>2.1000000000000001E-2</v>
+        <v>2.0999999999999998E-2</v>
       </c>
       <c r="AH21" s="10">
         <f t="shared" si="46"/>
@@ -3521,14 +3528,14 @@
       </c>
       <c r="AI21" s="10">
         <f t="shared" si="46"/>
-        <v>2.1000000000000001E-2</v>
+        <v>2.0999999999999998E-2</v>
       </c>
       <c r="AK21" t="s">
         <v>38</v>
       </c>
       <c r="AL21" s="4">
         <f>NPV(AL20,Y14:EQ14)</f>
-        <v>3278011.7097029299</v>
+        <v>3628131.0988831227</v>
       </c>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.3">
@@ -3589,15 +3596,15 @@
       </c>
       <c r="P22" s="10">
         <f t="shared" si="49"/>
-        <v>0.60477696404793613</v>
+        <v>0.60843334830883766</v>
       </c>
       <c r="Q22" s="10">
         <f t="shared" si="49"/>
-        <v>0.61558634057351347</v>
+        <v>0.62155456239367024</v>
       </c>
       <c r="R22" s="10">
         <f t="shared" si="49"/>
-        <v>0.60458020812523838</v>
+        <v>0.61547066322169319</v>
       </c>
       <c r="U22" s="10">
         <f t="shared" ref="U22:V22" si="50">U8/U3</f>
@@ -3617,54 +3624,54 @@
       </c>
       <c r="Y22" s="10">
         <f t="shared" si="51"/>
-        <v>0.58249254299041098</v>
+        <v>0.58820180748031947</v>
       </c>
       <c r="Z22" s="10">
         <f t="shared" si="51"/>
-        <v>0.60816265977518869</v>
+        <v>0.61188011672722142</v>
       </c>
       <c r="AA22" s="10">
         <f t="shared" si="51"/>
-        <v>0.60572951673345254</v>
+        <v>0.61188011672722142</v>
       </c>
       <c r="AB22" s="10">
         <f t="shared" si="51"/>
-        <v>0.60572951673345266</v>
+        <v>0.61267938171137526</v>
       </c>
       <c r="AC22" s="10">
         <f t="shared" si="51"/>
-        <v>0.60572951673345266</v>
+        <v>0.6134937271669284</v>
       </c>
       <c r="AD22" s="10">
         <f t="shared" si="51"/>
-        <v>0.60572951673345254</v>
+        <v>0.61512241807803458</v>
       </c>
       <c r="AE22" s="10">
         <f t="shared" si="51"/>
-        <v>0.60663505540594342</v>
+        <v>0.61673544849961082</v>
       </c>
       <c r="AF22" s="10">
         <f t="shared" si="51"/>
-        <v>0.60663505540594354</v>
+        <v>0.61753413346563391</v>
       </c>
       <c r="AG22" s="10">
         <f t="shared" si="51"/>
-        <v>0.60663505540594342</v>
+        <v>0.61753413346563379</v>
       </c>
       <c r="AH22" s="10">
         <f t="shared" si="51"/>
-        <v>0.60663505540594342</v>
+        <v>0.61753413346563391</v>
       </c>
       <c r="AI22" s="10">
         <f t="shared" si="51"/>
-        <v>0.60663505540594342</v>
+        <v>0.61753413346563391</v>
       </c>
       <c r="AK22" t="s">
         <v>39</v>
       </c>
       <c r="AL22" s="4">
         <f>Main!D8</f>
-        <v>34747</v>
+        <v>48325</v>
       </c>
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.3">
@@ -3725,15 +3732,15 @@
       </c>
       <c r="P23" s="10">
         <f t="shared" si="54"/>
-        <v>0.13999322722654928</v>
+        <v>0.15330385182336731</v>
       </c>
       <c r="Q23" s="10">
         <f t="shared" si="54"/>
-        <v>0.13998843825113336</v>
+        <v>0.13686457102380142</v>
       </c>
       <c r="R23" s="10">
         <f t="shared" si="54"/>
-        <v>0.1399934859207059</v>
+        <v>0.13286772992334561</v>
       </c>
       <c r="U23" s="10">
         <f t="shared" ref="U23:V23" si="55">U13/U12</f>
@@ -3753,7 +3760,7 @@
       </c>
       <c r="Y23" s="10">
         <f t="shared" si="56"/>
-        <v>0.14056571815718158</v>
+        <v>0.14101015182648152</v>
       </c>
       <c r="Z23" s="10">
         <f t="shared" si="56"/>
@@ -3789,7 +3796,7 @@
       </c>
       <c r="AH23" s="10">
         <f t="shared" si="56"/>
-        <v>0.14000000000000001</v>
+        <v>0.14000000000000004</v>
       </c>
       <c r="AI23" s="10">
         <f t="shared" si="56"/>
@@ -3800,12 +3807,12 @@
       </c>
       <c r="AL23" s="4">
         <f>AL21+AL22</f>
-        <v>3312758.7097029299</v>
+        <v>3676456.0988831227</v>
       </c>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C24" s="10">
         <f>C14/C3</f>
@@ -3861,15 +3868,15 @@
       </c>
       <c r="P24" s="10">
         <f t="shared" si="57"/>
-        <v>0.52837882822902793</v>
+        <v>0.56526110861519374</v>
       </c>
       <c r="Q24" s="10">
         <f t="shared" si="57"/>
-        <v>0.53714155407331399</v>
+        <v>0.54414194413689432</v>
       </c>
       <c r="R24" s="10">
         <f t="shared" si="57"/>
-        <v>0.52748669705609941</v>
+        <v>0.54105362445522043</v>
       </c>
       <c r="U24" s="10">
         <f t="shared" ref="U24:AI24" si="58">U14/U3</f>
@@ -3889,54 +3896,54 @@
       </c>
       <c r="Y24" s="10">
         <f t="shared" si="58"/>
-        <v>0.50788741416931915</v>
+        <v>0.52231879389891389</v>
       </c>
       <c r="Z24" s="10">
         <f t="shared" si="58"/>
-        <v>0.52944549153704479</v>
+        <v>0.53272933163464875</v>
       </c>
       <c r="AA24" s="10">
         <f t="shared" si="58"/>
-        <v>0.52678691522922161</v>
+        <v>0.53200039331369064</v>
       </c>
       <c r="AB24" s="10">
         <f t="shared" si="58"/>
-        <v>0.52646853182726505</v>
+        <v>0.53232306170465449</v>
       </c>
       <c r="AC24" s="10">
         <f t="shared" si="58"/>
-        <v>0.52631708718618342</v>
+        <v>0.53282531664467392</v>
       </c>
       <c r="AD24" s="10">
         <f t="shared" si="58"/>
-        <v>0.5262201146282669</v>
+        <v>0.53408298443494417</v>
       </c>
       <c r="AE24" s="10">
         <f t="shared" si="58"/>
-        <v>0.52695403810614005</v>
+        <v>0.53537852161315813</v>
       </c>
       <c r="AF24" s="10">
         <f t="shared" si="58"/>
-        <v>0.52696051988015224</v>
+        <v>0.53602284565423808</v>
       </c>
       <c r="AG24" s="10">
         <f t="shared" si="58"/>
-        <v>0.52696693810736006</v>
+        <v>0.53602865125887211</v>
       </c>
       <c r="AH24" s="10">
         <f t="shared" si="58"/>
-        <v>0.52697329341077193</v>
+        <v>0.53603439994581359</v>
       </c>
       <c r="AI24" s="10">
         <f t="shared" si="58"/>
-        <v>0.52697958640728759</v>
+        <v>0.53604009227307914</v>
       </c>
       <c r="AK24" t="s">
         <v>41</v>
       </c>
       <c r="AL24" s="11">
         <f>AL23/AI15</f>
-        <v>135.54104618071804</v>
+        <v>150.88467942555704</v>
       </c>
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.3">
@@ -3945,7 +3952,7 @@
       </c>
       <c r="AL25" s="11">
         <f>Main!D3</f>
-        <v>138.85</v>
+        <v>173.91</v>
       </c>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.3">
@@ -3954,7 +3961,7 @@
       </c>
       <c r="AL26" s="9">
         <f>AL24/AL25-1</f>
-        <v>-2.3831140218091185E-2</v>
+        <v>-0.13239791026647663</v>
       </c>
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.3">

--- a/Financial Analysis/NVDA.xlsx
+++ b/Financial Analysis/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AF800A-EB86-4389-9D3B-3107987B5CCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC07BC7-ABEF-44ED-BB68-3279ABCB0444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{07368E55-E692-488D-959E-E8519263B1F7}"/>
   </bookViews>
@@ -712,14 +712,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>173.91</v>
+        <v>185.54</v>
       </c>
       <c r="E3" s="3">
-        <v>45925</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45925</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="3">
         <v>45973</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>4237491.0599999996</v>
+        <v>4520867.6399999997</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -784,7 +784,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>4189166.0599999996</v>
+        <v>4472542.6399999997</v>
       </c>
     </row>
   </sheetData>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AL25" s="11">
         <f>Main!D3</f>
-        <v>173.91</v>
+        <v>185.54</v>
       </c>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.3">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="AL26" s="9">
         <f>AL24/AL25-1</f>
-        <v>-0.13239791026647663</v>
+        <v>-0.18678085897619356</v>
       </c>
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.3">

--- a/Financial Analysis/NVDA.xlsx
+++ b/Financial Analysis/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC07BC7-ABEF-44ED-BB68-3279ABCB0444}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1F3E34-62E2-4089-8FC3-02D339215891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{07368E55-E692-488D-959E-E8519263B1F7}"/>
   </bookViews>
@@ -712,14 +712,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>185.54</v>
+        <v>205.95</v>
       </c>
       <c r="E3" s="3">
-        <v>45937</v>
+        <v>45960</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45966</v>
       </c>
       <c r="G3" s="3">
         <v>45973</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>4520867.6399999997</v>
+        <v>5018177.7</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -784,7 +784,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>4472542.6399999997</v>
+        <v>4969852.7</v>
       </c>
     </row>
   </sheetData>
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AL25" s="11">
         <f>Main!D3</f>
-        <v>185.54</v>
+        <v>205.95</v>
       </c>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.3">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="AL26" s="9">
         <f>AL24/AL25-1</f>
-        <v>-0.18678085897619356</v>
+        <v>-0.26737227761322147</v>
       </c>
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.3">

--- a/Financial Analysis/NVDA.xlsx
+++ b/Financial Analysis/NVDA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1F3E34-62E2-4089-8FC3-02D339215891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECAC5A5-A240-452A-9685-DC55A2E37496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{07368E55-E692-488D-959E-E8519263B1F7}"/>
   </bookViews>
@@ -190,7 +190,7 @@
     <t>Net Margin</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -291,13 +291,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
@@ -315,7 +315,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11811000" y="0"/>
+          <a:off x="12534900" y="0"/>
           <a:ext cx="0" cy="6126480"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -712,17 +712,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>205.95</v>
+        <v>189.61</v>
       </c>
       <c r="E3" s="3">
-        <v>45960</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45966</v>
+        <v>46052</v>
       </c>
       <c r="G3" s="3">
-        <v>45973</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="4" spans="3:7" x14ac:dyDescent="0.3">
@@ -730,10 +730,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="3:7" x14ac:dyDescent="0.3">
@@ -742,7 +743,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>5018177.7</v>
+        <v>4612642.4700000007</v>
       </c>
     </row>
     <row r="6" spans="3:7" x14ac:dyDescent="0.3">
@@ -750,11 +751,11 @@
         <v>6</v>
       </c>
       <c r="D6" s="4">
-        <f>11639+45152</f>
-        <v>56791</v>
+        <f>11486+49122</f>
+        <v>60608</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
@@ -762,11 +763,11 @@
         <v>7</v>
       </c>
       <c r="D7" s="4">
-        <f>8466</f>
-        <v>8466</v>
+        <f>999+7468</f>
+        <v>8467</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
@@ -775,7 +776,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>48325</v>
+        <v>52141</v>
       </c>
     </row>
     <row r="9" spans="3:7" x14ac:dyDescent="0.3">
@@ -784,7 +785,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>4969852.7</v>
+        <v>4560501.4700000007</v>
       </c>
     </row>
   </sheetData>
@@ -999,12 +1000,11 @@
         <v>46743</v>
       </c>
       <c r="Q3" s="8">
-        <f>M3*1.52</f>
-        <v>53324.639999999999</v>
+        <v>57006</v>
       </c>
       <c r="R3" s="8">
-        <f>N3*1.45</f>
-        <v>57029.95</v>
+        <f>N3*1.65</f>
+        <v>64896.149999999994</v>
       </c>
       <c r="S3" s="8"/>
       <c r="U3" s="8">
@@ -1024,47 +1024,47 @@
       </c>
       <c r="Y3" s="8">
         <f>SUM(O3:R3)</f>
-        <v>201159.59000000003</v>
+        <v>212707.15</v>
       </c>
       <c r="Z3" s="8">
-        <f>Y3*1.3</f>
-        <v>261507.46700000003</v>
+        <f>Y3*1.35</f>
+        <v>287154.65250000003</v>
       </c>
       <c r="AA3" s="8">
-        <f>Z3*1.15</f>
-        <v>300733.58705000003</v>
+        <f>Z3*1.18</f>
+        <v>338842.48995000002</v>
       </c>
       <c r="AB3" s="8">
         <f>AA3*1.09</f>
-        <v>327799.60988450004</v>
+        <v>369338.31404550007</v>
       </c>
       <c r="AC3" s="8">
         <f>AB3*1.06</f>
-        <v>347467.58647757006</v>
+        <v>391498.61288823007</v>
       </c>
       <c r="AD3" s="8">
         <f>AC3*1.05</f>
-        <v>364840.96580144856</v>
+        <v>411073.5435326416</v>
       </c>
       <c r="AE3" s="8">
         <f>AD3*1.04</f>
-        <v>379434.60443350649</v>
+        <v>427516.4852739473</v>
       </c>
       <c r="AF3" s="8">
         <f>AE3*1.03</f>
-        <v>390817.6425665117</v>
+        <v>440341.97983216576</v>
       </c>
       <c r="AG3" s="8">
         <f t="shared" ref="AG3:AI3" si="0">AF3*1.02</f>
-        <v>398633.99541784194</v>
+        <v>449148.8194288091</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" si="0"/>
-        <v>406606.67532619881</v>
+        <v>458131.79581738531</v>
       </c>
       <c r="AI3" s="8">
         <f t="shared" si="0"/>
-        <v>414738.80883272277</v>
+        <v>467294.43173373304</v>
       </c>
     </row>
     <row r="4" spans="1:147" x14ac:dyDescent="0.3">
@@ -1114,7 +1114,7 @@
         <v>12890</v>
       </c>
       <c r="Q4" s="4">
-        <v>14208</v>
+        <v>15157</v>
       </c>
       <c r="R4" s="4">
         <v>15418</v>
@@ -1136,47 +1136,47 @@
       </c>
       <c r="Y4" s="4">
         <f>SUM(O4:R4)</f>
-        <v>59910</v>
+        <v>60859</v>
       </c>
       <c r="Z4" s="4">
         <f t="shared" ref="Z4:AI4" si="1">Z3-Z5</f>
-        <v>73222.090760000021</v>
+        <v>80403.302700000029</v>
       </c>
       <c r="AA4" s="4">
         <f t="shared" si="1"/>
-        <v>84205.404374000005</v>
+        <v>94875.897186000017</v>
       </c>
       <c r="AB4" s="4">
         <f t="shared" si="1"/>
-        <v>91783.890767660021</v>
+        <v>103414.72793274</v>
       </c>
       <c r="AC4" s="4">
         <f t="shared" si="1"/>
-        <v>97290.924213719612</v>
+        <v>109619.61160870444</v>
       </c>
       <c r="AD4" s="4">
         <f t="shared" si="1"/>
-        <v>102155.47042440559</v>
+        <v>115100.59218913969</v>
       </c>
       <c r="AE4" s="4">
         <f t="shared" si="1"/>
-        <v>106241.68924138183</v>
+        <v>119704.61587670527</v>
       </c>
       <c r="AF4" s="4">
         <f t="shared" si="1"/>
-        <v>109428.93991862331</v>
+        <v>123295.75435300643</v>
       </c>
       <c r="AG4" s="4">
         <f t="shared" si="1"/>
-        <v>111617.51871699578</v>
+        <v>125761.66944006656</v>
       </c>
       <c r="AH4" s="4">
         <f t="shared" si="1"/>
-        <v>113849.86909133568</v>
+        <v>128276.9028288679</v>
       </c>
       <c r="AI4" s="4">
         <f t="shared" si="1"/>
-        <v>116126.86647316237</v>
+        <v>130842.44088544528</v>
       </c>
     </row>
     <row r="5" spans="1:147" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1185,7 +1185,7 @@
         <v>20</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:R5" si="2">C3-C4</f>
+        <f t="shared" ref="C5:Q5" si="2">C3-C4</f>
         <v>5431</v>
       </c>
       <c r="D5" s="8">
@@ -1242,11 +1242,11 @@
       </c>
       <c r="Q5" s="8">
         <f t="shared" si="2"/>
-        <v>39116.639999999999</v>
+        <v>41849</v>
       </c>
       <c r="R5" s="8">
-        <f t="shared" si="2"/>
-        <v>41611.949999999997</v>
+        <f>R3*0.749</f>
+        <v>48607.216349999995</v>
       </c>
       <c r="U5" s="8">
         <f>U3-U4</f>
@@ -1266,47 +1266,47 @@
       </c>
       <c r="Y5" s="8">
         <f>Y3-Y4</f>
-        <v>141249.59000000003</v>
+        <v>151848.15</v>
       </c>
       <c r="Z5" s="8">
         <f>Z3*0.72</f>
-        <v>188285.37624000001</v>
+        <v>206751.3498</v>
       </c>
       <c r="AA5" s="8">
         <f t="shared" ref="AA5:AI5" si="3">AA3*0.72</f>
-        <v>216528.18267600003</v>
+        <v>243966.592764</v>
       </c>
       <c r="AB5" s="8">
         <f t="shared" si="3"/>
-        <v>236015.71911684002</v>
+        <v>265923.58611276007</v>
       </c>
       <c r="AC5" s="8">
         <f t="shared" si="3"/>
-        <v>250176.66226385045</v>
+        <v>281879.00127952563</v>
       </c>
       <c r="AD5" s="8">
         <f t="shared" si="3"/>
-        <v>262685.49537704297</v>
+        <v>295972.95134350192</v>
       </c>
       <c r="AE5" s="8">
         <f t="shared" si="3"/>
-        <v>273192.91519212467</v>
+        <v>307811.86939724203</v>
       </c>
       <c r="AF5" s="8">
         <f t="shared" si="3"/>
-        <v>281388.70264788839</v>
+        <v>317046.22547915933</v>
       </c>
       <c r="AG5" s="8">
         <f t="shared" si="3"/>
-        <v>287016.47670084616</v>
+        <v>323387.14998874255</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="3"/>
-        <v>292756.80623486312</v>
+        <v>329854.89298851741</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="3"/>
-        <v>298611.9423595604</v>
+        <v>336451.99084828777</v>
       </c>
     </row>
     <row r="6" spans="1:147" x14ac:dyDescent="0.3">
@@ -1356,8 +1356,7 @@
         <v>4291</v>
       </c>
       <c r="Q6" s="4">
-        <f>M6*1.4</f>
-        <v>4746</v>
+        <v>4705</v>
       </c>
       <c r="R6" s="4">
         <v>5200</v>
@@ -1379,47 +1378,47 @@
       </c>
       <c r="Y6" s="4">
         <f t="shared" ref="Y6:Y7" si="4">SUM(O6:R6)</f>
-        <v>18226</v>
+        <v>18185</v>
       </c>
       <c r="Z6" s="4">
         <f>Y6*1.25</f>
-        <v>22782.5</v>
+        <v>22731.25</v>
       </c>
       <c r="AA6" s="4">
         <f>Z6*1.15</f>
-        <v>26199.874999999996</v>
+        <v>26140.937499999996</v>
       </c>
       <c r="AB6" s="4">
         <f>AA6*1.08</f>
-        <v>28295.864999999998</v>
+        <v>28232.212499999998</v>
       </c>
       <c r="AC6" s="4">
         <f>AB6*1.05</f>
-        <v>29710.65825</v>
+        <v>29643.823124999999</v>
       </c>
       <c r="AD6" s="4">
         <f>AC6*1.03</f>
-        <v>30601.977997500002</v>
+        <v>30533.137818750001</v>
       </c>
       <c r="AE6" s="4">
         <f t="shared" ref="AE6:AI6" si="5">AD6*1.02</f>
-        <v>31214.017557450003</v>
+        <v>31143.800575125002</v>
       </c>
       <c r="AF6" s="4">
         <f t="shared" si="5"/>
-        <v>31838.297908599005</v>
+        <v>31766.676586627502</v>
       </c>
       <c r="AG6" s="4">
         <f t="shared" si="5"/>
-        <v>32475.063866770986</v>
+        <v>32402.010118360053</v>
       </c>
       <c r="AH6" s="4">
         <f t="shared" si="5"/>
-        <v>33124.565144106404</v>
+        <v>33050.050320727256</v>
       </c>
       <c r="AI6" s="4">
         <f t="shared" si="5"/>
-        <v>33787.056446988536</v>
+        <v>33711.051327141802</v>
       </c>
     </row>
     <row r="7" spans="1:147" x14ac:dyDescent="0.3">
@@ -1469,13 +1468,13 @@
         <v>1122</v>
       </c>
       <c r="Q7" s="4">
-        <f>Q3*0.023</f>
-        <v>1226.4667199999999</v>
+        <v>1134</v>
       </c>
       <c r="R7" s="4">
         <f>R3*0.023</f>
-        <v>1311.68885</v>
-      </c>
+        <v>1492.6114499999999</v>
+      </c>
+      <c r="S7" s="4"/>
       <c r="U7" s="4">
         <v>2166</v>
       </c>
@@ -1493,47 +1492,47 @@
       </c>
       <c r="Y7" s="4">
         <f t="shared" si="4"/>
-        <v>4701.1555699999999</v>
+        <v>4789.6114500000003</v>
       </c>
       <c r="Z7" s="4">
         <f>Z3*0.021</f>
-        <v>5491.6568070000012</v>
+        <v>6030.2477025000007</v>
       </c>
       <c r="AA7" s="4">
         <f t="shared" ref="AA7:AI7" si="6">AA3*0.021</f>
-        <v>6315.4053280500011</v>
+        <v>7115.6922889500011</v>
       </c>
       <c r="AB7" s="4">
         <f t="shared" si="6"/>
-        <v>6883.791807574501</v>
+        <v>7756.1045949555019</v>
       </c>
       <c r="AC7" s="4">
         <f t="shared" si="6"/>
-        <v>7296.819316028972</v>
+        <v>8221.4708706528327</v>
       </c>
       <c r="AD7" s="4">
         <f t="shared" si="6"/>
-        <v>7661.66028183042</v>
+        <v>8632.544414185475</v>
       </c>
       <c r="AE7" s="4">
         <f t="shared" si="6"/>
-        <v>7968.1266931036371</v>
+        <v>8977.8461907528945</v>
       </c>
       <c r="AF7" s="4">
         <f t="shared" si="6"/>
-        <v>8207.1704938967468</v>
+        <v>9247.1815764754811</v>
       </c>
       <c r="AG7" s="4">
         <f t="shared" si="6"/>
-        <v>8371.3139037746805</v>
+        <v>9432.1252080049926</v>
       </c>
       <c r="AH7" s="4">
         <f t="shared" si="6"/>
-        <v>8538.7401818501748</v>
+        <v>9620.7677121650922</v>
       </c>
       <c r="AI7" s="4">
         <f t="shared" si="6"/>
-        <v>8709.5149854871779</v>
+        <v>9813.1830664083936</v>
       </c>
     </row>
     <row r="8" spans="1:147" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1599,11 +1598,11 @@
       </c>
       <c r="Q8" s="8">
         <f t="shared" si="8"/>
-        <v>33144.173280000003</v>
+        <v>36010</v>
       </c>
       <c r="R8" s="8">
         <f t="shared" si="8"/>
-        <v>35100.261149999998</v>
+        <v>41914.604899999998</v>
       </c>
       <c r="U8" s="8">
         <f>U5-U6-U7</f>
@@ -1623,47 +1622,47 @@
       </c>
       <c r="Y8" s="8">
         <f t="shared" ref="Y8:AI8" si="9">Y5-Y6-Y7</f>
-        <v>118322.43443000002</v>
+        <v>128873.53855</v>
       </c>
       <c r="Z8" s="8">
         <f t="shared" si="9"/>
-        <v>160011.21943300002</v>
+        <v>177989.8520975</v>
       </c>
       <c r="AA8" s="8">
         <f t="shared" si="9"/>
-        <v>184012.90234795003</v>
+        <v>210709.96297505</v>
       </c>
       <c r="AB8" s="8">
         <f t="shared" si="9"/>
-        <v>200836.06230926552</v>
+        <v>229935.26901780456</v>
       </c>
       <c r="AC8" s="8">
         <f t="shared" si="9"/>
-        <v>213169.18469782147</v>
+        <v>244013.70728387282</v>
       </c>
       <c r="AD8" s="8">
         <f t="shared" si="9"/>
-        <v>224421.85709771255</v>
+        <v>256807.26911056644</v>
       </c>
       <c r="AE8" s="8">
         <f t="shared" si="9"/>
-        <v>234010.77094157104</v>
+        <v>267690.22263136419</v>
       </c>
       <c r="AF8" s="8">
         <f t="shared" si="9"/>
-        <v>241343.23424539264</v>
+        <v>276032.36731605633</v>
       </c>
       <c r="AG8" s="8">
         <f t="shared" si="9"/>
-        <v>246170.09893030048</v>
+        <v>281553.01466237748</v>
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="9"/>
-        <v>251093.50090890654</v>
+        <v>287184.07495562505</v>
       </c>
       <c r="AI8" s="8">
         <f t="shared" si="9"/>
-        <v>256115.37092708467</v>
+        <v>292927.75645473757</v>
       </c>
     </row>
     <row r="9" spans="1:147" x14ac:dyDescent="0.3">
@@ -1713,10 +1712,10 @@
         <v>-592</v>
       </c>
       <c r="Q9" s="4">
-        <v>-536</v>
+        <v>-624</v>
       </c>
       <c r="R9" s="4">
-        <v>-547</v>
+        <v>-660</v>
       </c>
       <c r="U9" s="4">
         <v>-29</v>
@@ -1735,47 +1734,47 @@
       </c>
       <c r="Y9" s="4">
         <f t="shared" ref="Y9:Y11" si="10">SUM(O9:R9)</f>
-        <v>-2190</v>
+        <v>-2391</v>
       </c>
       <c r="Z9" s="4">
         <f t="shared" ref="Z9:AI9" si="11">Y9*1.02</f>
-        <v>-2233.8000000000002</v>
+        <v>-2438.8200000000002</v>
       </c>
       <c r="AA9" s="4">
         <f t="shared" si="11"/>
-        <v>-2278.4760000000001</v>
+        <v>-2487.5964000000004</v>
       </c>
       <c r="AB9" s="4">
         <f t="shared" si="11"/>
-        <v>-2324.0455200000001</v>
+        <v>-2537.3483280000005</v>
       </c>
       <c r="AC9" s="4">
         <f t="shared" si="11"/>
-        <v>-2370.5264304000002</v>
+        <v>-2588.0952945600006</v>
       </c>
       <c r="AD9" s="4">
         <f t="shared" si="11"/>
-        <v>-2417.936959008</v>
+        <v>-2639.8572004512007</v>
       </c>
       <c r="AE9" s="4">
         <f t="shared" si="11"/>
-        <v>-2466.2956981881603</v>
+        <v>-2692.6543444602248</v>
       </c>
       <c r="AF9" s="4">
         <f t="shared" si="11"/>
-        <v>-2515.6216121519237</v>
+        <v>-2746.5074313494292</v>
       </c>
       <c r="AG9" s="4">
         <f t="shared" si="11"/>
-        <v>-2565.9340443949623</v>
+        <v>-2801.437579976418</v>
       </c>
       <c r="AH9" s="4">
         <f t="shared" si="11"/>
-        <v>-2617.2527252828613</v>
+        <v>-2857.4663315759462</v>
       </c>
       <c r="AI9" s="4">
         <f t="shared" si="11"/>
-        <v>-2669.5977797885184</v>
+        <v>-2914.615658207465</v>
       </c>
     </row>
     <row r="10" spans="1:147" x14ac:dyDescent="0.3">
@@ -1825,7 +1824,7 @@
         <v>62</v>
       </c>
       <c r="Q10" s="4">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="R10" s="4">
         <v>63</v>
@@ -1847,47 +1846,47 @@
       </c>
       <c r="Y10" s="4">
         <f t="shared" si="10"/>
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Z10" s="4">
         <f t="shared" ref="Z10:AI10" si="12">Y10*1.01</f>
-        <v>253.51</v>
+        <v>251.49</v>
       </c>
       <c r="AA10" s="4">
         <f t="shared" si="12"/>
-        <v>256.04509999999999</v>
+        <v>254.00490000000002</v>
       </c>
       <c r="AB10" s="4">
         <f t="shared" si="12"/>
-        <v>258.60555099999999</v>
+        <v>256.54494900000003</v>
       </c>
       <c r="AC10" s="4">
         <f t="shared" si="12"/>
-        <v>261.19160650999999</v>
+        <v>259.11039849000002</v>
       </c>
       <c r="AD10" s="4">
         <f t="shared" si="12"/>
-        <v>263.80352257509998</v>
+        <v>261.70150247490005</v>
       </c>
       <c r="AE10" s="4">
         <f t="shared" si="12"/>
-        <v>266.441557800851</v>
+        <v>264.31851749964903</v>
       </c>
       <c r="AF10" s="4">
         <f t="shared" si="12"/>
-        <v>269.10597337885952</v>
+        <v>266.96170267464555</v>
       </c>
       <c r="AG10" s="4">
         <f t="shared" si="12"/>
-        <v>271.79703311264814</v>
+        <v>269.63131970139199</v>
       </c>
       <c r="AH10" s="4">
         <f t="shared" si="12"/>
-        <v>274.51500344377462</v>
+        <v>272.32763289840591</v>
       </c>
       <c r="AI10" s="4">
         <f t="shared" si="12"/>
-        <v>277.26015347821237</v>
+        <v>275.05090922738998</v>
       </c>
     </row>
     <row r="11" spans="1:147" x14ac:dyDescent="0.3">
@@ -1938,7 +1937,7 @@
         <v>-2236</v>
       </c>
       <c r="Q11" s="4">
-        <v>0</v>
+        <v>-1363</v>
       </c>
       <c r="R11" s="4">
         <v>0</v>
@@ -1960,7 +1959,7 @@
       </c>
       <c r="Y11" s="4">
         <f t="shared" si="10"/>
-        <v>-2056</v>
+        <v>-3419</v>
       </c>
       <c r="Z11" s="4">
         <v>0</v>
@@ -2056,11 +2055,11 @@
       </c>
       <c r="Q12" s="8">
         <f t="shared" si="14"/>
-        <v>33617.173280000003</v>
+        <v>37936</v>
       </c>
       <c r="R12" s="8">
         <f t="shared" si="14"/>
-        <v>35584.261149999998</v>
+        <v>42511.604899999998</v>
       </c>
       <c r="U12" s="8">
         <f>U8-U9-U10-U11</f>
@@ -2080,47 +2079,47 @@
       </c>
       <c r="Y12" s="8">
         <f t="shared" ref="Y12:AI12" si="15">Y8-Y9-Y10-Y11</f>
-        <v>122317.43443000002</v>
+        <v>134434.53855</v>
       </c>
       <c r="Z12" s="8">
         <f t="shared" si="15"/>
-        <v>161991.509433</v>
+        <v>180177.18209750002</v>
       </c>
       <c r="AA12" s="8">
         <f t="shared" si="15"/>
-        <v>186035.33324795004</v>
+        <v>212943.55447505001</v>
       </c>
       <c r="AB12" s="8">
         <f t="shared" si="15"/>
-        <v>202901.50227826554</v>
+        <v>232216.07239680455</v>
       </c>
       <c r="AC12" s="8">
         <f t="shared" si="15"/>
-        <v>215278.51952171148</v>
+        <v>246342.69217994282</v>
       </c>
       <c r="AD12" s="8">
         <f t="shared" si="15"/>
-        <v>226575.99053414544</v>
+        <v>259185.42480854274</v>
       </c>
       <c r="AE12" s="8">
         <f t="shared" si="15"/>
-        <v>236210.62508195834</v>
+        <v>270118.55845832475</v>
       </c>
       <c r="AF12" s="8">
         <f t="shared" si="15"/>
-        <v>243589.74988416568</v>
+        <v>278511.91304473113</v>
       </c>
       <c r="AG12" s="8">
         <f t="shared" si="15"/>
-        <v>248464.2359415828</v>
+        <v>284084.82092265249</v>
       </c>
       <c r="AH12" s="8">
         <f t="shared" si="15"/>
-        <v>253436.23863074562</v>
+        <v>289769.21365430258</v>
       </c>
       <c r="AI12" s="8">
         <f t="shared" si="15"/>
-        <v>258507.70855339497</v>
+        <v>295567.32120371761</v>
       </c>
     </row>
     <row r="13" spans="1:147" x14ac:dyDescent="0.3">
@@ -2170,10 +2169,11 @@
         <v>4784</v>
       </c>
       <c r="Q13" s="4">
-        <v>4601</v>
+        <v>6026</v>
       </c>
       <c r="R13" s="4">
-        <v>4728</v>
+        <f>R12*0.15</f>
+        <v>6376.7407349999994</v>
       </c>
       <c r="U13" s="4">
         <v>189</v>
@@ -2192,47 +2192,47 @@
       </c>
       <c r="Y13" s="4">
         <f>SUM(O13:R13)</f>
-        <v>17248</v>
+        <v>20321.740734999999</v>
       </c>
       <c r="Z13" s="4">
         <f t="shared" ref="Z13:AI13" si="16">Z12*0.14</f>
-        <v>22678.811320620003</v>
+        <v>25224.805493650005</v>
       </c>
       <c r="AA13" s="4">
         <f t="shared" si="16"/>
-        <v>26044.946654713007</v>
+        <v>29812.097626507006</v>
       </c>
       <c r="AB13" s="4">
         <f t="shared" si="16"/>
-        <v>28406.210318957179</v>
+        <v>32510.25013555264</v>
       </c>
       <c r="AC13" s="4">
         <f t="shared" si="16"/>
-        <v>30138.992733039609</v>
+        <v>34487.976905192001</v>
       </c>
       <c r="AD13" s="4">
         <f t="shared" si="16"/>
-        <v>31720.638674780366</v>
+        <v>36285.959473195988</v>
       </c>
       <c r="AE13" s="4">
         <f t="shared" si="16"/>
-        <v>33069.487511474174</v>
+        <v>37816.598184165472</v>
       </c>
       <c r="AF13" s="4">
         <f t="shared" si="16"/>
-        <v>34102.564983783195</v>
+        <v>38991.667826262361</v>
       </c>
       <c r="AG13" s="4">
         <f t="shared" si="16"/>
-        <v>34784.993031821592</v>
+        <v>39771.874929171354</v>
       </c>
       <c r="AH13" s="4">
         <f t="shared" si="16"/>
-        <v>35481.073408304394</v>
+        <v>40567.689911602363</v>
       </c>
       <c r="AI13" s="4">
         <f t="shared" si="16"/>
-        <v>36191.079197475301</v>
+        <v>41379.42496852047</v>
       </c>
     </row>
     <row r="14" spans="1:147" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="Q14" s="8">
         <f t="shared" si="18"/>
-        <v>29016.173280000003</v>
+        <v>31910</v>
       </c>
       <c r="R14" s="8">
         <f t="shared" si="18"/>
-        <v>30856.261149999998</v>
+        <v>36134.864164999999</v>
       </c>
       <c r="U14" s="8">
         <f>U12-U13</f>
@@ -2322,495 +2322,495 @@
       </c>
       <c r="Y14" s="8">
         <f t="shared" ref="Y14:AI14" si="19">Y12-Y13</f>
-        <v>105069.43443000002</v>
+        <v>114112.797815</v>
       </c>
       <c r="Z14" s="8">
         <f t="shared" si="19"/>
-        <v>139312.69811237999</v>
+        <v>154952.37660385002</v>
       </c>
       <c r="AA14" s="8">
         <f t="shared" si="19"/>
-        <v>159990.38659323702</v>
+        <v>183131.45684854302</v>
       </c>
       <c r="AB14" s="8">
         <f t="shared" si="19"/>
-        <v>174495.29195930838</v>
+        <v>199705.82226125192</v>
       </c>
       <c r="AC14" s="8">
         <f t="shared" si="19"/>
-        <v>185139.52678867188</v>
+        <v>211854.71527475084</v>
       </c>
       <c r="AD14" s="8">
         <f t="shared" si="19"/>
-        <v>194855.35185936507</v>
+        <v>222899.46533534676</v>
       </c>
       <c r="AE14" s="8">
         <f t="shared" si="19"/>
-        <v>203141.13757048416</v>
+        <v>232301.96027415927</v>
       </c>
       <c r="AF14" s="8">
         <f t="shared" si="19"/>
-        <v>209487.18490038248</v>
+        <v>239520.24521846877</v>
       </c>
       <c r="AG14" s="8">
         <f t="shared" si="19"/>
-        <v>213679.2429097612</v>
+        <v>244312.94599348115</v>
       </c>
       <c r="AH14" s="8">
         <f t="shared" si="19"/>
-        <v>217955.16522244122</v>
+        <v>249201.52374270023</v>
       </c>
       <c r="AI14" s="8">
         <f t="shared" si="19"/>
-        <v>222316.62935591966</v>
+        <v>254187.89623519714</v>
       </c>
       <c r="AJ14" s="7">
         <f>AI14*($AL$19+1)</f>
-        <v>220093.46306236048</v>
+        <v>251646.01727284517</v>
       </c>
       <c r="AK14" s="7">
         <f t="shared" ref="AK14:CV14" si="20">AJ14*($AL$19+1)</f>
-        <v>217892.52843173686</v>
+        <v>249129.55710011671</v>
       </c>
       <c r="AL14" s="7">
         <f t="shared" si="20"/>
-        <v>215713.60314741949</v>
+        <v>246638.26152911555</v>
       </c>
       <c r="AM14" s="7">
         <f t="shared" si="20"/>
-        <v>213556.4671159453</v>
+        <v>244171.87891382439</v>
       </c>
       <c r="AN14" s="7">
         <f t="shared" si="20"/>
-        <v>211420.90244478584</v>
+        <v>241730.16012468614</v>
       </c>
       <c r="AO14" s="7">
         <f t="shared" si="20"/>
-        <v>209306.69342033798</v>
+        <v>239312.85852343927</v>
       </c>
       <c r="AP14" s="7">
         <f t="shared" si="20"/>
-        <v>207213.6264861346</v>
+        <v>236919.72993820487</v>
       </c>
       <c r="AQ14" s="7">
         <f t="shared" si="20"/>
-        <v>205141.49022127324</v>
+        <v>234550.53263882283</v>
       </c>
       <c r="AR14" s="7">
         <f t="shared" si="20"/>
-        <v>203090.0753190605</v>
+        <v>232205.0273124346</v>
       </c>
       <c r="AS14" s="7">
         <f t="shared" si="20"/>
-        <v>201059.17456586991</v>
+        <v>229882.97703931024</v>
       </c>
       <c r="AT14" s="7">
         <f t="shared" si="20"/>
-        <v>199048.58282021122</v>
+        <v>227584.14726891712</v>
       </c>
       <c r="AU14" s="7">
         <f t="shared" si="20"/>
-        <v>197058.09699200912</v>
+        <v>225308.30579622794</v>
       </c>
       <c r="AV14" s="7">
         <f t="shared" si="20"/>
-        <v>195087.51602208902</v>
+        <v>223055.22273826567</v>
       </c>
       <c r="AW14" s="7">
         <f t="shared" si="20"/>
-        <v>193136.64086186813</v>
+        <v>220824.67051088301</v>
       </c>
       <c r="AX14" s="7">
         <f t="shared" si="20"/>
-        <v>191205.27445324944</v>
+        <v>218616.42380577416</v>
       </c>
       <c r="AY14" s="7">
         <f t="shared" si="20"/>
-        <v>189293.22170871694</v>
+        <v>216430.25956771642</v>
       </c>
       <c r="AZ14" s="7">
         <f t="shared" si="20"/>
-        <v>187400.28949162978</v>
+        <v>214265.95697203925</v>
       </c>
       <c r="BA14" s="7">
         <f t="shared" si="20"/>
-        <v>185526.28659671347</v>
+        <v>212123.29740231886</v>
       </c>
       <c r="BB14" s="7">
         <f t="shared" si="20"/>
-        <v>183671.02373074632</v>
+        <v>210002.06442829568</v>
       </c>
       <c r="BC14" s="7">
         <f t="shared" si="20"/>
-        <v>181834.31349343885</v>
+        <v>207902.04378401273</v>
       </c>
       <c r="BD14" s="7">
         <f t="shared" si="20"/>
-        <v>180015.97035850445</v>
+        <v>205823.02334617259</v>
       </c>
       <c r="BE14" s="7">
         <f t="shared" si="20"/>
-        <v>178215.81065491939</v>
+        <v>203764.79311271085</v>
       </c>
       <c r="BF14" s="7">
         <f t="shared" si="20"/>
-        <v>176433.65254837018</v>
+        <v>201727.14518158374</v>
       </c>
       <c r="BG14" s="7">
         <f t="shared" si="20"/>
-        <v>174669.31602288649</v>
+        <v>199709.87372976789</v>
       </c>
       <c r="BH14" s="7">
         <f t="shared" si="20"/>
-        <v>172922.62286265762</v>
+        <v>197712.77499247022</v>
       </c>
       <c r="BI14" s="7">
         <f t="shared" si="20"/>
-        <v>171193.39663403103</v>
+        <v>195735.64724254553</v>
       </c>
       <c r="BJ14" s="7">
         <f t="shared" si="20"/>
-        <v>169481.46266769071</v>
+        <v>193778.29077012007</v>
       </c>
       <c r="BK14" s="7">
         <f t="shared" si="20"/>
-        <v>167786.6480410138</v>
+        <v>191840.50786241886</v>
       </c>
       <c r="BL14" s="7">
         <f t="shared" si="20"/>
-        <v>166108.78156060367</v>
+        <v>189922.10278379466</v>
       </c>
       <c r="BM14" s="7">
         <f t="shared" si="20"/>
-        <v>164447.69374499764</v>
+        <v>188022.88175595671</v>
       </c>
       <c r="BN14" s="7">
         <f t="shared" si="20"/>
-        <v>162803.21680754767</v>
+        <v>186142.65293839714</v>
       </c>
       <c r="BO14" s="7">
         <f t="shared" si="20"/>
-        <v>161175.18463947219</v>
+        <v>184281.22640901315</v>
       </c>
       <c r="BP14" s="7">
         <f t="shared" si="20"/>
-        <v>159563.43279307746</v>
+        <v>182438.41414492301</v>
       </c>
       <c r="BQ14" s="7">
         <f t="shared" si="20"/>
-        <v>157967.79846514668</v>
+        <v>180614.03000347377</v>
       </c>
       <c r="BR14" s="7">
         <f t="shared" si="20"/>
-        <v>156388.12048049521</v>
+        <v>178807.88970343902</v>
       </c>
       <c r="BS14" s="7">
         <f t="shared" si="20"/>
-        <v>154824.23927569026</v>
+        <v>177019.81080640462</v>
       </c>
       <c r="BT14" s="7">
         <f t="shared" si="20"/>
-        <v>153275.99688293334</v>
+        <v>175249.61269834058</v>
       </c>
       <c r="BU14" s="7">
         <f t="shared" si="20"/>
-        <v>151743.236914104</v>
+        <v>173497.11657135718</v>
       </c>
       <c r="BV14" s="7">
         <f t="shared" si="20"/>
-        <v>150225.80454496294</v>
+        <v>171762.14540564362</v>
       </c>
       <c r="BW14" s="7">
         <f t="shared" si="20"/>
-        <v>148723.54649951332</v>
+        <v>170044.52395158718</v>
       </c>
       <c r="BX14" s="7">
         <f t="shared" si="20"/>
-        <v>147236.31103451818</v>
+        <v>168344.07871207129</v>
       </c>
       <c r="BY14" s="7">
         <f t="shared" si="20"/>
-        <v>145763.947924173</v>
+        <v>166660.63792495057</v>
       </c>
       <c r="BZ14" s="7">
         <f t="shared" si="20"/>
-        <v>144306.30844493126</v>
+        <v>164994.03154570106</v>
       </c>
       <c r="CA14" s="7">
         <f t="shared" si="20"/>
-        <v>142863.24536048193</v>
+        <v>163344.09123024406</v>
       </c>
       <c r="CB14" s="7">
         <f t="shared" si="20"/>
-        <v>141434.6129068771</v>
+        <v>161710.65031794162</v>
       </c>
       <c r="CC14" s="7">
         <f t="shared" si="20"/>
-        <v>140020.26677780831</v>
+        <v>160093.5438147622</v>
       </c>
       <c r="CD14" s="7">
         <f t="shared" si="20"/>
-        <v>138620.06411003022</v>
+        <v>158492.60837661457</v>
       </c>
       <c r="CE14" s="7">
         <f t="shared" si="20"/>
-        <v>137233.86346892992</v>
+        <v>156907.68229284842</v>
       </c>
       <c r="CF14" s="7">
         <f t="shared" si="20"/>
-        <v>135861.52483424061</v>
+        <v>155338.60546991994</v>
       </c>
       <c r="CG14" s="7">
         <f t="shared" si="20"/>
-        <v>134502.90958589822</v>
+        <v>153785.21941522075</v>
       </c>
       <c r="CH14" s="7">
         <f t="shared" si="20"/>
-        <v>133157.88049003924</v>
+        <v>152247.36722106853</v>
       </c>
       <c r="CI14" s="7">
         <f t="shared" si="20"/>
-        <v>131826.30168513884</v>
+        <v>150724.89354885786</v>
       </c>
       <c r="CJ14" s="7">
         <f t="shared" si="20"/>
-        <v>130508.03866828745</v>
+        <v>149217.64461336928</v>
       </c>
       <c r="CK14" s="7">
         <f t="shared" si="20"/>
-        <v>129202.95828160457</v>
+        <v>147725.46816723558</v>
       </c>
       <c r="CL14" s="7">
         <f t="shared" si="20"/>
-        <v>127910.92869878853</v>
+        <v>146248.21348556323</v>
       </c>
       <c r="CM14" s="7">
         <f t="shared" si="20"/>
-        <v>126631.81941180064</v>
+        <v>144785.73135070759</v>
       </c>
       <c r="CN14" s="7">
         <f t="shared" si="20"/>
-        <v>125365.50121768263</v>
+        <v>143337.8740372005</v>
       </c>
       <c r="CO14" s="7">
         <f t="shared" si="20"/>
-        <v>124111.8462055058</v>
+        <v>141904.49529682848</v>
       </c>
       <c r="CP14" s="7">
         <f t="shared" si="20"/>
-        <v>122870.72774345074</v>
+        <v>140485.4503438602</v>
       </c>
       <c r="CQ14" s="7">
         <f t="shared" si="20"/>
-        <v>121642.02046601623</v>
+        <v>139080.59584042159</v>
       </c>
       <c r="CR14" s="7">
         <f t="shared" si="20"/>
-        <v>120425.60026135607</v>
+        <v>137689.78988201739</v>
       </c>
       <c r="CS14" s="7">
         <f t="shared" si="20"/>
-        <v>119221.34425874251</v>
+        <v>136312.89198319722</v>
       </c>
       <c r="CT14" s="7">
         <f t="shared" si="20"/>
-        <v>118029.13081615508</v>
+        <v>134949.76306336524</v>
       </c>
       <c r="CU14" s="7">
         <f t="shared" si="20"/>
-        <v>116848.83950799353</v>
+        <v>133600.2654327316</v>
       </c>
       <c r="CV14" s="7">
         <f t="shared" si="20"/>
-        <v>115680.35111291359</v>
+        <v>132264.26277840429</v>
       </c>
       <c r="CW14" s="7">
         <f t="shared" ref="CW14:EQ14" si="21">CV14*($AL$19+1)</f>
-        <v>114523.54760178445</v>
+        <v>130941.62015062023</v>
       </c>
       <c r="CX14" s="7">
         <f t="shared" si="21"/>
-        <v>113378.31212576661</v>
+        <v>129632.20394911403</v>
       </c>
       <c r="CY14" s="7">
         <f t="shared" si="21"/>
-        <v>112244.52900450894</v>
+        <v>128335.88190962288</v>
       </c>
       <c r="CZ14" s="7">
         <f t="shared" si="21"/>
-        <v>111122.08371446385</v>
+        <v>127052.52309052665</v>
       </c>
       <c r="DA14" s="7">
         <f t="shared" si="21"/>
-        <v>110010.86287731922</v>
+        <v>125781.99785962138</v>
       </c>
       <c r="DB14" s="7">
         <f t="shared" si="21"/>
-        <v>108910.75424854603</v>
+        <v>124524.17788102516</v>
       </c>
       <c r="DC14" s="7">
         <f t="shared" si="21"/>
-        <v>107821.64670606056</v>
+        <v>123278.93610221491</v>
       </c>
       <c r="DD14" s="7">
         <f t="shared" si="21"/>
-        <v>106743.43023899996</v>
+        <v>122046.14674119276</v>
       </c>
       <c r="DE14" s="7">
         <f t="shared" si="21"/>
-        <v>105675.99593660996</v>
+        <v>120825.68527378084</v>
       </c>
       <c r="DF14" s="7">
         <f t="shared" si="21"/>
-        <v>104619.23597724386</v>
+        <v>119617.42842104303</v>
       </c>
       <c r="DG14" s="7">
         <f t="shared" si="21"/>
-        <v>103573.04361747143</v>
+        <v>118421.25413683261</v>
       </c>
       <c r="DH14" s="7">
         <f t="shared" si="21"/>
-        <v>102537.31318129672</v>
+        <v>117237.04159546428</v>
       </c>
       <c r="DI14" s="7">
         <f t="shared" si="21"/>
-        <v>101511.94004948375</v>
+        <v>116064.67117950963</v>
       </c>
       <c r="DJ14" s="7">
         <f t="shared" si="21"/>
-        <v>100496.82064898891</v>
+        <v>114904.02446771454</v>
       </c>
       <c r="DK14" s="7">
         <f t="shared" si="21"/>
-        <v>99491.852442499017</v>
+        <v>113754.98422303739</v>
       </c>
       <c r="DL14" s="7">
         <f t="shared" si="21"/>
-        <v>98496.933918074021</v>
+        <v>112617.43438080701</v>
       </c>
       <c r="DM14" s="7">
         <f t="shared" si="21"/>
-        <v>97511.964578893283</v>
+        <v>111491.26003699894</v>
       </c>
       <c r="DN14" s="7">
         <f t="shared" si="21"/>
-        <v>96536.844933104352</v>
+        <v>110376.34743662894</v>
       </c>
       <c r="DO14" s="7">
         <f t="shared" si="21"/>
-        <v>95571.476483773309</v>
+        <v>109272.58396226265</v>
       </c>
       <c r="DP14" s="7">
         <f t="shared" si="21"/>
-        <v>94615.761718935581</v>
+        <v>108179.85812264003</v>
       </c>
       <c r="DQ14" s="7">
         <f t="shared" si="21"/>
-        <v>93669.604101746227</v>
+        <v>107098.05954141363</v>
       </c>
       <c r="DR14" s="7">
         <f t="shared" si="21"/>
-        <v>92732.908060728761</v>
+        <v>106027.0789459995</v>
       </c>
       <c r="DS14" s="7">
         <f t="shared" si="21"/>
-        <v>91805.578980121471</v>
+        <v>104966.8081565395</v>
       </c>
       <c r="DT14" s="7">
         <f t="shared" si="21"/>
-        <v>90887.523190320251</v>
+        <v>103917.1400749741</v>
       </c>
       <c r="DU14" s="7">
         <f t="shared" si="21"/>
-        <v>89978.647958417045</v>
+        <v>102877.96867422436</v>
       </c>
       <c r="DV14" s="7">
         <f t="shared" si="21"/>
-        <v>89078.86147883287</v>
+        <v>101849.18898748212</v>
       </c>
       <c r="DW14" s="7">
         <f t="shared" si="21"/>
-        <v>88188.072864044545</v>
+        <v>100830.69709760729</v>
       </c>
       <c r="DX14" s="7">
         <f t="shared" si="21"/>
-        <v>87306.192135404097</v>
+        <v>99822.390126631217</v>
       </c>
       <c r="DY14" s="7">
         <f t="shared" si="21"/>
-        <v>86433.130214050048</v>
+        <v>98824.166225364897</v>
       </c>
       <c r="DZ14" s="7">
         <f t="shared" si="21"/>
-        <v>85568.798911909544</v>
+        <v>97835.924563111243</v>
       </c>
       <c r="EA14" s="7">
         <f t="shared" si="21"/>
-        <v>84713.110922790453</v>
+        <v>96857.565317480126</v>
       </c>
       <c r="EB14" s="7">
         <f t="shared" si="21"/>
-        <v>83865.979813562546</v>
+        <v>95888.989664305322</v>
       </c>
       <c r="EC14" s="7">
         <f t="shared" si="21"/>
-        <v>83027.320015426914</v>
+        <v>94930.099767662265</v>
       </c>
       <c r="ED14" s="7">
         <f t="shared" si="21"/>
-        <v>82197.046815272639</v>
+        <v>93980.798769985646</v>
       </c>
       <c r="EE14" s="7">
         <f t="shared" si="21"/>
-        <v>81375.076347119917</v>
+        <v>93040.990782285793</v>
       </c>
       <c r="EF14" s="7">
         <f t="shared" si="21"/>
-        <v>80561.325583648722</v>
+        <v>92110.580874462932</v>
       </c>
       <c r="EG14" s="7">
         <f t="shared" si="21"/>
-        <v>79755.712327812231</v>
+        <v>91189.475065718303</v>
       </c>
       <c r="EH14" s="7">
         <f t="shared" si="21"/>
-        <v>78958.155204534109</v>
+        <v>90277.580315061117</v>
       </c>
       <c r="EI14" s="7">
         <f t="shared" si="21"/>
-        <v>78168.573652488762</v>
+        <v>89374.804511910508</v>
       </c>
       <c r="EJ14" s="7">
         <f t="shared" si="21"/>
-        <v>77386.887915963875</v>
+        <v>88481.0564667914</v>
       </c>
       <c r="EK14" s="7">
         <f t="shared" si="21"/>
-        <v>76613.019036804239</v>
+        <v>87596.245902123483</v>
       </c>
       <c r="EL14" s="7">
         <f t="shared" si="21"/>
-        <v>75846.888846436195</v>
+        <v>86720.283443102249</v>
       </c>
       <c r="EM14" s="7">
         <f t="shared" si="21"/>
-        <v>75088.419957971826</v>
+        <v>85853.080608671225</v>
       </c>
       <c r="EN14" s="7">
         <f t="shared" si="21"/>
-        <v>74337.535758392114</v>
+        <v>84994.549802584515</v>
       </c>
       <c r="EO14" s="7">
         <f t="shared" si="21"/>
-        <v>73594.160400808192</v>
+        <v>84144.60430455867</v>
       </c>
       <c r="EP14" s="7">
         <f t="shared" si="21"/>
-        <v>72858.218796800109</v>
+        <v>83303.158261513076</v>
       </c>
       <c r="EQ14" s="7">
         <f t="shared" si="21"/>
-        <v>72129.636608832108</v>
+        <v>82470.126678897941</v>
       </c>
     </row>
     <row r="15" spans="1:147" x14ac:dyDescent="0.3">
@@ -2860,10 +2860,12 @@
         <v>24366</v>
       </c>
       <c r="Q15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="R15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="U15" s="4">
         <v>2462</v>
@@ -2878,37 +2880,48 @@
         <v>24489</v>
       </c>
       <c r="Y15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="Z15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="AA15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="AB15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="AC15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="AD15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="AE15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="AF15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="AG15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="AH15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
       <c r="AI15" s="4">
-        <v>24366</v>
+        <f>24327</f>
+        <v>24327</v>
       </c>
     </row>
     <row r="16" spans="1:147" x14ac:dyDescent="0.3">
@@ -2993,47 +3006,47 @@
       </c>
       <c r="Y16" s="6">
         <f t="shared" ref="Y16:AI16" si="24">Y14/Y15</f>
-        <v>4.3121330719034727</v>
+        <v>4.6907879235006371</v>
       </c>
       <c r="Z16" s="6">
         <f t="shared" si="24"/>
-        <v>5.7175038214060576</v>
+        <v>6.3695637194824686</v>
       </c>
       <c r="AA16" s="6">
         <f t="shared" si="24"/>
-        <v>6.5661325861133149</v>
+        <v>7.52790960038406</v>
       </c>
       <c r="AB16" s="6">
         <f t="shared" si="24"/>
-        <v>7.1614254272062867</v>
+        <v>8.2092252337424227</v>
       </c>
       <c r="AC16" s="6">
         <f t="shared" si="24"/>
-        <v>7.5982732819778329</v>
+        <v>8.7086247903461516</v>
       </c>
       <c r="AD16" s="6">
         <f t="shared" si="24"/>
-        <v>7.9970184625857783</v>
+        <v>9.162636795961145</v>
       </c>
       <c r="AE16" s="6">
         <f t="shared" si="24"/>
-        <v>8.3370736916393398</v>
+        <v>9.5491412946174723</v>
       </c>
       <c r="AF16" s="6">
         <f t="shared" si="24"/>
-        <v>8.5975205163088919</v>
+        <v>9.8458603698963607</v>
       </c>
       <c r="AG16" s="6">
         <f t="shared" si="24"/>
-        <v>8.7695659078125754</v>
+        <v>10.042871952706093</v>
       </c>
       <c r="AH16" s="6">
         <f t="shared" si="24"/>
-        <v>8.9450531569581067</v>
+        <v>10.243824710926141</v>
       </c>
       <c r="AI16" s="6">
         <f t="shared" si="24"/>
-        <v>9.1240511103964401</v>
+        <v>10.448797477502247</v>
       </c>
     </row>
     <row r="18" spans="1:38" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -3083,11 +3096,11 @@
       </c>
       <c r="Q18" s="9">
         <f t="shared" ref="Q18" si="28">Q3/M3-1</f>
-        <v>0.52</v>
+        <v>0.62493586454592109</v>
       </c>
       <c r="R18" s="9">
         <f t="shared" ref="R18" si="29">R3/N3-1</f>
-        <v>0.44999999999999996</v>
+        <v>0.64999999999999991</v>
       </c>
       <c r="U18" s="9"/>
       <c r="V18" s="9">
@@ -3104,15 +3117,15 @@
       </c>
       <c r="Y18" s="9">
         <f t="shared" si="30"/>
-        <v>0.54148823344597985</v>
+        <v>0.62997731748622576</v>
       </c>
       <c r="Z18" s="9">
         <f t="shared" si="30"/>
-        <v>0.30000000000000004</v>
+        <v>0.35000000000000009</v>
       </c>
       <c r="AA18" s="9">
         <f t="shared" si="30"/>
-        <v>0.14999999999999991</v>
+        <v>0.17999999999999994</v>
       </c>
       <c r="AB18" s="9">
         <f t="shared" si="30"/>
@@ -3209,11 +3222,11 @@
       </c>
       <c r="Q19" s="10">
         <f t="shared" si="33"/>
-        <v>0.73355656972086447</v>
+        <v>0.7341157071185489</v>
       </c>
       <c r="R19" s="10">
         <f t="shared" si="33"/>
-        <v>0.72965082382151836</v>
+        <v>0.749</v>
       </c>
       <c r="U19" s="10">
         <f t="shared" ref="U19:V19" si="34">U5/U3</f>
@@ -3233,7 +3246,7 @@
       </c>
       <c r="Y19" s="10">
         <f t="shared" si="35"/>
-        <v>0.70217676422983366</v>
+        <v>0.71388361886283558</v>
       </c>
       <c r="Z19" s="10">
         <f t="shared" si="35"/>
@@ -3245,7 +3258,7 @@
       </c>
       <c r="AB19" s="10">
         <f t="shared" si="35"/>
-        <v>0.72</v>
+        <v>0.72000000000000008</v>
       </c>
       <c r="AC19" s="10">
         <f t="shared" si="35"/>
@@ -3253,7 +3266,7 @@
       </c>
       <c r="AD19" s="10">
         <f t="shared" si="35"/>
-        <v>0.72</v>
+        <v>0.71999999999999986</v>
       </c>
       <c r="AE19" s="10">
         <f t="shared" si="35"/>
@@ -3265,7 +3278,7 @@
       </c>
       <c r="AG19" s="10">
         <f t="shared" si="35"/>
-        <v>0.71999999999999986</v>
+        <v>0.72</v>
       </c>
       <c r="AH19" s="10">
         <f t="shared" si="35"/>
@@ -3332,7 +3345,7 @@
       </c>
       <c r="Q20" s="10">
         <f t="shared" ref="Q20" si="39">Q6/M6-1</f>
-        <v>0.39999999999999991</v>
+        <v>0.38790560471976399</v>
       </c>
       <c r="R20" s="10">
         <f t="shared" ref="R20" si="40">R6/N6-1</f>
@@ -3353,7 +3366,7 @@
       </c>
       <c r="Y20" s="10">
         <f t="shared" si="41"/>
-        <v>0.41133653399411485</v>
+        <v>0.40816168499303074</v>
       </c>
       <c r="Z20" s="10">
         <f t="shared" si="41"/>
@@ -3464,7 +3477,7 @@
       </c>
       <c r="Q21" s="10">
         <f t="shared" si="44"/>
-        <v>2.3E-2</v>
+        <v>1.9892642879696873E-2</v>
       </c>
       <c r="R21" s="10">
         <f t="shared" si="44"/>
@@ -3488,7 +3501,7 @@
       </c>
       <c r="Y21" s="10">
         <f t="shared" si="46"/>
-        <v>2.3370278145824413E-2</v>
+        <v>2.2517397511085079E-2</v>
       </c>
       <c r="Z21" s="10">
         <f t="shared" si="46"/>
@@ -3504,11 +3517,11 @@
       </c>
       <c r="AC21" s="10">
         <f t="shared" si="46"/>
-        <v>2.1000000000000001E-2</v>
+        <v>2.1000000000000005E-2</v>
       </c>
       <c r="AD21" s="10">
         <f t="shared" si="46"/>
-        <v>2.1000000000000001E-2</v>
+        <v>2.1000000000000005E-2</v>
       </c>
       <c r="AE21" s="10">
         <f t="shared" si="46"/>
@@ -3520,7 +3533,7 @@
       </c>
       <c r="AG21" s="10">
         <f t="shared" si="46"/>
-        <v>2.0999999999999998E-2</v>
+        <v>2.1000000000000005E-2</v>
       </c>
       <c r="AH21" s="10">
         <f t="shared" si="46"/>
@@ -3535,7 +3548,7 @@
       </c>
       <c r="AL21" s="4">
         <f>NPV(AL20,Y14:EQ14)</f>
-        <v>3628131.0988831227</v>
+        <v>4139181.0896443203</v>
       </c>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.3">
@@ -3600,11 +3613,11 @@
       </c>
       <c r="Q22" s="10">
         <f t="shared" si="49"/>
-        <v>0.62155456239367024</v>
+        <v>0.63168789250254365</v>
       </c>
       <c r="R22" s="10">
         <f t="shared" si="49"/>
-        <v>0.61547066322169319</v>
+        <v>0.64587198007894153</v>
       </c>
       <c r="U22" s="10">
         <f t="shared" ref="U22:V22" si="50">U8/U3</f>
@@ -3624,54 +3637,54 @@
       </c>
       <c r="Y22" s="10">
         <f t="shared" si="51"/>
-        <v>0.58820180748031947</v>
+        <v>0.60587309147811907</v>
       </c>
       <c r="Z22" s="10">
         <f t="shared" si="51"/>
-        <v>0.61188011672722142</v>
+        <v>0.61983969456145238</v>
       </c>
       <c r="AA22" s="10">
         <f t="shared" si="51"/>
-        <v>0.61188011672722142</v>
+        <v>0.62185224469972056</v>
       </c>
       <c r="AB22" s="10">
         <f t="shared" si="51"/>
-        <v>0.61267938171137526</v>
+        <v>0.62256002227128282</v>
       </c>
       <c r="AC22" s="10">
         <f t="shared" si="51"/>
-        <v>0.6134937271669284</v>
+        <v>0.62328115413664797</v>
       </c>
       <c r="AD22" s="10">
         <f t="shared" si="51"/>
-        <v>0.61512241807803458</v>
+        <v>0.62472341786737839</v>
       </c>
       <c r="AE22" s="10">
         <f t="shared" si="51"/>
-        <v>0.61673544849961082</v>
+        <v>0.62615181367762129</v>
       </c>
       <c r="AF22" s="10">
         <f t="shared" si="51"/>
-        <v>0.61753413346563391</v>
+        <v>0.62685907762249871</v>
       </c>
       <c r="AG22" s="10">
         <f t="shared" si="51"/>
-        <v>0.61753413346563379</v>
+        <v>0.62685907762249871</v>
       </c>
       <c r="AH22" s="10">
         <f t="shared" si="51"/>
-        <v>0.61753413346563391</v>
+        <v>0.62685907762249871</v>
       </c>
       <c r="AI22" s="10">
         <f t="shared" si="51"/>
-        <v>0.61753413346563391</v>
+        <v>0.62685907762249871</v>
       </c>
       <c r="AK22" t="s">
         <v>39</v>
       </c>
       <c r="AL22" s="4">
         <f>Main!D8</f>
-        <v>48325</v>
+        <v>52141</v>
       </c>
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.3">
@@ -3736,11 +3749,11 @@
       </c>
       <c r="Q23" s="10">
         <f t="shared" si="54"/>
-        <v>0.13686457102380142</v>
+        <v>0.15884647827920709</v>
       </c>
       <c r="R23" s="10">
         <f t="shared" si="54"/>
-        <v>0.13286772992334561</v>
+        <v>0.15</v>
       </c>
       <c r="U23" s="10">
         <f t="shared" ref="U23:V23" si="55">U13/U12</f>
@@ -3760,7 +3773,7 @@
       </c>
       <c r="Y23" s="10">
         <f t="shared" si="56"/>
-        <v>0.14101015182648152</v>
+        <v>0.15116458132105515</v>
       </c>
       <c r="Z23" s="10">
         <f t="shared" si="56"/>
@@ -3796,7 +3809,7 @@
       </c>
       <c r="AH23" s="10">
         <f t="shared" si="56"/>
-        <v>0.14000000000000004</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AI23" s="10">
         <f t="shared" si="56"/>
@@ -3807,7 +3820,7 @@
       </c>
       <c r="AL23" s="4">
         <f>AL21+AL22</f>
-        <v>3676456.0988831227</v>
+        <v>4191322.0896443203</v>
       </c>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.3">
@@ -3872,11 +3885,11 @@
       </c>
       <c r="Q24" s="10">
         <f t="shared" si="57"/>
-        <v>0.54414194413689432</v>
+        <v>0.55976563870469775</v>
       </c>
       <c r="R24" s="10">
         <f t="shared" si="57"/>
-        <v>0.54105362445522043</v>
+        <v>0.55681059916497366</v>
       </c>
       <c r="U24" s="10">
         <f t="shared" ref="U24:AI24" si="58">U14/U3</f>
@@ -3896,54 +3909,54 @@
       </c>
       <c r="Y24" s="10">
         <f t="shared" si="58"/>
-        <v>0.52231879389891389</v>
+        <v>0.53647842968607307</v>
       </c>
       <c r="Z24" s="10">
         <f t="shared" si="58"/>
-        <v>0.53272933163464875</v>
+        <v>0.53961297598634594</v>
       </c>
       <c r="AA24" s="10">
         <f t="shared" si="58"/>
-        <v>0.53200039331369064</v>
+        <v>0.5404619027429709</v>
       </c>
       <c r="AB24" s="10">
         <f t="shared" si="58"/>
-        <v>0.53232306170465449</v>
+        <v>0.54071244348792225</v>
       </c>
       <c r="AC24" s="10">
         <f t="shared" si="58"/>
-        <v>0.53282531664467392</v>
+        <v>0.54113784391678998</v>
       </c>
       <c r="AD24" s="10">
         <f t="shared" si="58"/>
-        <v>0.53408298443494417</v>
+        <v>0.5422374386340123</v>
       </c>
       <c r="AE24" s="10">
         <f t="shared" si="58"/>
-        <v>0.53537852161315813</v>
+        <v>0.54337544463414789</v>
       </c>
       <c r="AF24" s="10">
         <f t="shared" si="58"/>
-        <v>0.53602284565423808</v>
+        <v>0.54394142777338828</v>
       </c>
       <c r="AG24" s="10">
         <f t="shared" si="58"/>
-        <v>0.53602865125887211</v>
+        <v>0.54394653937681159</v>
       </c>
       <c r="AH24" s="10">
         <f t="shared" si="58"/>
-        <v>0.53603439994581359</v>
+        <v>0.54395160086647598</v>
       </c>
       <c r="AI24" s="10">
         <f t="shared" si="58"/>
-        <v>0.53604009227307914</v>
+        <v>0.54395661273369256</v>
       </c>
       <c r="AK24" t="s">
         <v>41</v>
       </c>
       <c r="AL24" s="11">
         <f>AL23/AI15</f>
-        <v>150.88467942555704</v>
+        <v>172.29095612464835</v>
       </c>
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.3">
@@ -3952,7 +3965,7 @@
       </c>
       <c r="AL25" s="11">
         <f>Main!D3</f>
-        <v>205.95</v>
+        <v>189.61</v>
       </c>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.3">
@@ -3961,7 +3974,7 @@
       </c>
       <c r="AL26" s="9">
         <f>AL24/AL25-1</f>
-        <v>-0.26737227761322147</v>
+        <v>-9.1340350589903863E-2</v>
       </c>
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.3">

--- a/Financial Analysis/NVDA.xlsx
+++ b/Financial Analysis/NVDA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ECAC5A5-A240-452A-9685-DC55A2E37496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FCB5AB-593C-4196-8D25-E083209C1391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{07368E55-E692-488D-959E-E8519263B1F7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{07368E55-E692-488D-959E-E8519263B1F7}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -288,6 +288,61 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>122741</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{292E1E2A-A045-6363-7F84-C5894A757BC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5897880" y="525780"/>
+          <a:ext cx="7772400" cy="3620321"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -719,7 +774,7 @@
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>46052</v>
+        <v>46069</v>
       </c>
       <c r="G3" s="3">
         <v>46065</v>
@@ -790,6 +845,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
